--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -30,6 +30,12 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Valor Despesa Empenhada</t>
+  </si>
+  <si>
+    <t>Valor Despesa Liquidada</t>
+  </si>
+  <si>
     <t>Valor Pago Financeiro</t>
   </si>
   <si>
@@ -198,6 +204,12 @@
     <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
   </si>
   <si>
+    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
     <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
   </si>
   <si>
@@ -222,9 +234,6 @@
     <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
   </si>
   <si>
-    <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
-  </si>
-  <si>
     <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
   </si>
   <si>
@@ -238,9 +247,6 @@
   </si>
   <si>
     <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
   </si>
   <si>
     <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
@@ -269,7 +275,6 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -622,20 +627,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="3" max="3" width="33.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
-    <col min="5" max="5" width="21.28515625" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
-    <col min="7" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="4" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.42578125" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -648,17 +653,23 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>2022</v>
       </c>
@@ -666,22 +677,28 @@
         <v>1071</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="6">
+        <v>41468457.479999997</v>
+      </c>
+      <c r="E2" s="6">
+        <v>36393685.240000002</v>
+      </c>
+      <c r="F2" s="6">
         <v>35762406.770000003</v>
       </c>
-      <c r="E2" s="6">
+      <c r="G2" s="6">
         <v>4065417.18</v>
       </c>
-      <c r="F2" s="6">
+      <c r="H2" s="6">
         <v>2244249.52</v>
       </c>
-      <c r="G2" s="7">
+      <c r="I2" s="7">
         <v>6309666.7000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2022</v>
       </c>
@@ -689,22 +706,28 @@
         <v>1081</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3" s="6">
+        <v>1222668188.4300001</v>
+      </c>
+      <c r="E3" s="6">
+        <v>1218515083.1300001</v>
+      </c>
+      <c r="F3" s="6">
         <v>998941873.86000001</v>
       </c>
-      <c r="E3" s="6">
+      <c r="G3" s="6">
         <v>14711108.9</v>
       </c>
-      <c r="F3" s="6">
+      <c r="H3" s="6">
         <v>5367326.43</v>
       </c>
-      <c r="G3" s="7">
+      <c r="I3" s="7">
         <v>20078435.329999998</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>2022</v>
       </c>
@@ -712,22 +735,28 @@
         <v>1101</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6">
+        <v>12148887.189999999</v>
+      </c>
+      <c r="E4" s="6">
+        <v>11844528.199999999</v>
+      </c>
+      <c r="F4" s="6">
         <v>11757162.48</v>
       </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
         <v>36247.74</v>
       </c>
-      <c r="G4" s="7">
+      <c r="I4" s="7">
         <v>36247.74</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>2022</v>
       </c>
@@ -735,22 +764,28 @@
         <v>1191</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6">
+        <v>1539130234.2</v>
+      </c>
+      <c r="E5" s="6">
+        <v>1488234890.6900001</v>
+      </c>
+      <c r="F5" s="6">
         <v>1475159288.6900001</v>
       </c>
-      <c r="E5" s="6">
+      <c r="G5" s="6">
         <v>10728442.75</v>
       </c>
-      <c r="F5" s="6">
+      <c r="H5" s="6">
         <v>69971290.959999993</v>
       </c>
-      <c r="G5" s="7">
+      <c r="I5" s="7">
         <v>80699733.709999993</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>2022</v>
       </c>
@@ -758,22 +793,28 @@
         <v>1221</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="6">
+        <v>91983736.400000006</v>
+      </c>
+      <c r="E6" s="6">
+        <v>76448925.219999999</v>
+      </c>
+      <c r="F6" s="6">
         <v>75856018.969999999</v>
       </c>
-      <c r="E6" s="6">
+      <c r="G6" s="6">
         <v>467.76</v>
       </c>
-      <c r="F6" s="6">
+      <c r="H6" s="6">
         <v>10588548.640000001</v>
       </c>
-      <c r="G6" s="7">
+      <c r="I6" s="7">
         <v>10589016.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>2022</v>
       </c>
@@ -781,22 +822,28 @@
         <v>1231</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="6">
+        <v>196292319.50999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>192693183.61000001</v>
+      </c>
+      <c r="F7" s="6">
         <v>183911092.06</v>
       </c>
-      <c r="E7" s="6">
+      <c r="G7" s="6">
         <v>926349.93</v>
       </c>
-      <c r="F7" s="6">
+      <c r="H7" s="6">
         <v>4138969.75</v>
       </c>
-      <c r="G7" s="7">
+      <c r="I7" s="7">
         <v>5065319.68</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>2022</v>
       </c>
@@ -804,22 +851,28 @@
         <v>1251</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="6">
+        <v>12979474804.25</v>
+      </c>
+      <c r="E8" s="6">
+        <v>12773110420.68</v>
+      </c>
+      <c r="F8" s="6">
         <v>12732571407.309999</v>
       </c>
-      <c r="E8" s="6">
+      <c r="G8" s="6">
         <v>41558515.399999999</v>
       </c>
-      <c r="F8" s="6">
+      <c r="H8" s="6">
         <v>216807656.75</v>
       </c>
-      <c r="G8" s="7">
+      <c r="I8" s="7">
         <v>258366172.15000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>2022</v>
       </c>
@@ -827,22 +880,28 @@
         <v>1261</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="6">
+        <v>16633018692.76</v>
+      </c>
+      <c r="E9" s="6">
+        <v>16079912253.18</v>
+      </c>
+      <c r="F9" s="6">
         <v>15837680952.16</v>
       </c>
-      <c r="E9" s="6">
+      <c r="G9" s="6">
         <v>585170446.71000004</v>
       </c>
-      <c r="F9" s="6">
+      <c r="H9" s="6">
         <v>757153016.96000004</v>
       </c>
-      <c r="G9" s="7">
+      <c r="I9" s="7">
         <v>1342323463.6700001</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>2022</v>
       </c>
@@ -850,22 +909,28 @@
         <v>1271</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="6">
+        <v>71925491.400000006</v>
+      </c>
+      <c r="E10" s="6">
+        <v>70589799.609999999</v>
+      </c>
+      <c r="F10" s="6">
         <v>69678332.780000001</v>
       </c>
-      <c r="E10" s="6">
+      <c r="G10" s="6">
         <v>20181416.68</v>
       </c>
-      <c r="F10" s="6">
+      <c r="H10" s="6">
         <v>10134142.550000001</v>
       </c>
-      <c r="G10" s="7">
+      <c r="I10" s="7">
         <v>30315559.23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>2022</v>
       </c>
@@ -873,22 +938,28 @@
         <v>1301</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D11" s="6">
+        <v>600547625.35000002</v>
+      </c>
+      <c r="E11" s="6">
+        <v>522164709.56</v>
+      </c>
+      <c r="F11" s="6">
         <v>444238275.32999998</v>
       </c>
-      <c r="E11" s="6">
+      <c r="G11" s="6">
         <v>18353119.530000001</v>
       </c>
-      <c r="F11" s="6">
+      <c r="H11" s="6">
         <v>36819044.670000002</v>
       </c>
-      <c r="G11" s="7">
+      <c r="I11" s="7">
         <v>55172164.200000003</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>2022</v>
       </c>
@@ -896,22 +967,28 @@
         <v>1371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" s="6">
+        <v>181795255.09999999</v>
+      </c>
+      <c r="E12" s="6">
+        <v>176679835.12</v>
+      </c>
+      <c r="F12" s="6">
         <v>172435676.13</v>
       </c>
-      <c r="E12" s="6">
+      <c r="G12" s="6">
         <v>4368130.43</v>
       </c>
-      <c r="F12" s="6">
+      <c r="H12" s="6">
         <v>4287377.26</v>
       </c>
-      <c r="G12" s="7">
+      <c r="I12" s="7">
         <v>8655507.6899999995</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>2022</v>
       </c>
@@ -919,22 +996,28 @@
         <v>1401</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6">
+        <v>1617069712.1900001</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1550882048.6300001</v>
+      </c>
+      <c r="F13" s="6">
         <v>1547930780.0799999</v>
       </c>
-      <c r="E13" s="6">
+      <c r="G13" s="6">
         <v>4065273.59</v>
       </c>
-      <c r="F13" s="6">
+      <c r="H13" s="6">
         <v>42151132.619999997</v>
       </c>
-      <c r="G13" s="7">
+      <c r="I13" s="7">
         <v>46216406.210000001</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>2022</v>
       </c>
@@ -942,22 +1025,28 @@
         <v>1451</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6">
+        <v>3393511812.1300001</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3264360914.02</v>
+      </c>
+      <c r="F14" s="6">
         <v>3238880805.1700001</v>
       </c>
-      <c r="E14" s="6">
+      <c r="G14" s="6">
         <v>13141756.77</v>
       </c>
-      <c r="F14" s="6">
+      <c r="H14" s="6">
         <v>89952770.890000001</v>
       </c>
-      <c r="G14" s="7">
+      <c r="I14" s="7">
         <v>103094527.66</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>2022</v>
       </c>
@@ -965,22 +1054,28 @@
         <v>1481</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D15" s="6">
+        <v>152723547.84</v>
+      </c>
+      <c r="E15" s="6">
+        <v>140202461.59999999</v>
+      </c>
+      <c r="F15" s="6">
         <v>128851499.22</v>
       </c>
-      <c r="E15" s="6">
+      <c r="G15" s="6">
         <v>5411868.7000000002</v>
       </c>
-      <c r="F15" s="6">
+      <c r="H15" s="6">
         <v>11509155.9</v>
       </c>
-      <c r="G15" s="7">
+      <c r="I15" s="7">
         <v>16921024.600000001</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>2022</v>
       </c>
@@ -988,22 +1083,28 @@
         <v>1491</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="6">
+        <v>1612507669.4200001</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1582583713.78</v>
+      </c>
+      <c r="F16" s="6">
         <v>1572502930.45</v>
       </c>
-      <c r="E16" s="6">
+      <c r="G16" s="6">
         <v>1541639.23</v>
       </c>
-      <c r="F16" s="6">
+      <c r="H16" s="6">
         <v>16627368.43</v>
       </c>
-      <c r="G16" s="7">
+      <c r="I16" s="7">
         <v>18169007.66</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>2022</v>
       </c>
@@ -1011,22 +1112,28 @@
         <v>1501</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6">
+        <v>352650653.12</v>
+      </c>
+      <c r="E17" s="6">
+        <v>315037665.91000003</v>
+      </c>
+      <c r="F17" s="6">
         <v>301346762.92000002</v>
       </c>
-      <c r="E17" s="6">
+      <c r="G17" s="6">
         <v>19114485.82</v>
       </c>
-      <c r="F17" s="6">
+      <c r="H17" s="6">
         <v>77403990.659999996</v>
       </c>
-      <c r="G17" s="7">
+      <c r="I17" s="7">
         <v>96518476.480000004</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>2022</v>
       </c>
@@ -1034,22 +1141,28 @@
         <v>1511</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" s="6">
+        <v>3185868726.6500001</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3092549019.4699998</v>
+      </c>
+      <c r="F18" s="6">
         <v>3072423500.1500001</v>
       </c>
-      <c r="E18" s="6">
+      <c r="G18" s="6">
         <v>18094662.5</v>
       </c>
-      <c r="F18" s="6">
+      <c r="H18" s="6">
         <v>61379561.549999997</v>
       </c>
-      <c r="G18" s="7">
+      <c r="I18" s="7">
         <v>79474224.049999997</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>2022</v>
       </c>
@@ -1057,22 +1170,28 @@
         <v>1521</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D19" s="6">
+        <v>55665667.369999997</v>
+      </c>
+      <c r="E19" s="6">
+        <v>55392655.649999999</v>
+      </c>
+      <c r="F19" s="6">
         <v>55212108.020000003</v>
       </c>
-      <c r="E19" s="6">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6">
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
         <v>239632.61</v>
       </c>
-      <c r="G19" s="7">
+      <c r="I19" s="7">
         <v>239632.61</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>2022</v>
       </c>
@@ -1080,22 +1199,28 @@
         <v>1541</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D20" s="6">
+        <v>17601666.309999999</v>
+      </c>
+      <c r="E20" s="6">
+        <v>17148601.559999999</v>
+      </c>
+      <c r="F20" s="6">
         <v>16887894.920000002</v>
       </c>
-      <c r="E20" s="6">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
         <v>256633.48</v>
       </c>
-      <c r="G20" s="7">
+      <c r="I20" s="7">
         <v>256633.48</v>
       </c>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>2022</v>
       </c>
@@ -1103,22 +1228,28 @@
         <v>1631</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="6">
+        <v>63665749.640000001</v>
+      </c>
+      <c r="E21" s="6">
+        <v>39924754.939999998</v>
+      </c>
+      <c r="F21" s="6">
         <v>39409640.609999999</v>
       </c>
-      <c r="E21" s="6">
+      <c r="G21" s="6">
         <v>475922.2</v>
       </c>
-      <c r="F21" s="6">
+      <c r="H21" s="6">
         <v>24058202.100000001</v>
       </c>
-      <c r="G21" s="7">
+      <c r="I21" s="7">
         <v>24534124.300000001</v>
       </c>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>2022</v>
       </c>
@@ -1126,22 +1257,28 @@
         <v>1911</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22" s="6">
+        <v>12201752803.83</v>
+      </c>
+      <c r="E22" s="6">
+        <v>11477276512.18</v>
+      </c>
+      <c r="F22" s="6">
         <v>11477261273.860001</v>
       </c>
-      <c r="E22" s="6">
+      <c r="G22" s="6">
         <v>557959.56999999995</v>
       </c>
-      <c r="F22" s="6">
+      <c r="H22" s="6">
         <v>85266341.890000001</v>
       </c>
-      <c r="G22" s="7">
+      <c r="I22" s="7">
         <v>85824301.459999993</v>
       </c>
     </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>2022</v>
       </c>
@@ -1149,22 +1286,28 @@
         <v>1915</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D23" s="6">
+        <v>1045679146.33</v>
+      </c>
+      <c r="E23" s="6">
         <v>525455877.98000002</v>
       </c>
-      <c r="E23" s="6">
-        <v>0</v>
-      </c>
       <c r="F23" s="6">
+        <v>525455877.98000002</v>
+      </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6">
         <v>28198078.120000001</v>
       </c>
-      <c r="G23" s="7">
+      <c r="I23" s="7">
         <v>28198078.120000001</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>2022</v>
       </c>
@@ -1172,22 +1315,28 @@
         <v>1916</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24" s="6">
+        <v>5700229349.9499998</v>
+      </c>
+      <c r="E24" s="6">
+        <v>5577199638.6700001</v>
+      </c>
+      <c r="F24" s="6">
         <v>5517860023.2700005</v>
       </c>
-      <c r="E24" s="6">
+      <c r="G24" s="6">
         <v>28843343.77</v>
       </c>
-      <c r="F24" s="6">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7">
+      <c r="H24" s="6">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7">
         <v>28843343.77</v>
       </c>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>2022</v>
       </c>
@@ -1195,22 +1344,28 @@
         <v>1941</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" s="6">
         <v>201288736.28</v>
       </c>
       <c r="E25" s="6">
-        <v>0</v>
+        <v>201288736.28</v>
       </c>
       <c r="F25" s="6">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+        <v>201288736.28</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <v>0</v>
+      </c>
+      <c r="I25" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>2022</v>
       </c>
@@ -1218,22 +1373,28 @@
         <v>2011</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="6">
+        <v>1536739486.1400001</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1341247986.54</v>
+      </c>
+      <c r="F26" s="6">
         <v>1307994655.9000001</v>
       </c>
-      <c r="E26" s="6">
+      <c r="G26" s="6">
         <v>423878.41</v>
       </c>
-      <c r="F26" s="6">
+      <c r="H26" s="6">
         <v>127022888.48999999</v>
       </c>
-      <c r="G26" s="7">
+      <c r="I26" s="7">
         <v>127446766.90000001</v>
       </c>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>2022</v>
       </c>
@@ -1241,22 +1402,28 @@
         <v>2041</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D27" s="6">
+        <v>6761105.25</v>
+      </c>
+      <c r="E27" s="6">
+        <v>5938379.5999999996</v>
+      </c>
+      <c r="F27" s="6">
         <v>5925515.5999999996</v>
       </c>
-      <c r="E27" s="6">
+      <c r="G27" s="6">
         <v>4598.79</v>
       </c>
-      <c r="F27" s="6">
+      <c r="H27" s="6">
         <v>1296981.73</v>
       </c>
-      <c r="G27" s="7">
+      <c r="I27" s="7">
         <v>1301580.52</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>2022</v>
       </c>
@@ -1264,22 +1431,28 @@
         <v>2061</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D28" s="6">
+        <v>64511960.770000003</v>
+      </c>
+      <c r="E28" s="6">
+        <v>58152640.770000003</v>
+      </c>
+      <c r="F28" s="6">
         <v>56790483.530000001</v>
       </c>
-      <c r="E28" s="6">
+      <c r="G28" s="6">
         <v>141507.04999999999</v>
       </c>
-      <c r="F28" s="6">
+      <c r="H28" s="6">
         <v>1655021.81</v>
       </c>
-      <c r="G28" s="7">
+      <c r="I28" s="7">
         <v>1796528.86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>2022</v>
       </c>
@@ -1287,22 +1460,28 @@
         <v>2071</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D29" s="6">
+        <v>455083279.95999998</v>
+      </c>
+      <c r="E29" s="6">
+        <v>442616854.91000003</v>
+      </c>
+      <c r="F29" s="6">
         <v>429159889.94999999</v>
       </c>
-      <c r="E29" s="6">
+      <c r="G29" s="6">
         <v>50484697.07</v>
       </c>
-      <c r="F29" s="6">
+      <c r="H29" s="6">
         <v>12791969.369999999</v>
       </c>
-      <c r="G29" s="7">
+      <c r="I29" s="7">
         <v>63276666.439999998</v>
       </c>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>2022</v>
       </c>
@@ -1310,22 +1489,28 @@
         <v>2091</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" s="6">
+        <v>41540382.170000002</v>
+      </c>
+      <c r="E30" s="6">
+        <v>41283632.969999999</v>
+      </c>
+      <c r="F30" s="6">
         <v>40766476.920000002</v>
       </c>
-      <c r="E30" s="6">
+      <c r="G30" s="6">
         <v>27692.5</v>
       </c>
-      <c r="F30" s="6">
+      <c r="H30" s="6">
         <v>11647.71</v>
       </c>
-      <c r="G30" s="7">
+      <c r="I30" s="7">
         <v>39340.21</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>2022</v>
       </c>
@@ -1333,22 +1518,28 @@
         <v>2101</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D31" s="6">
+        <v>195536444.94999999</v>
+      </c>
+      <c r="E31" s="6">
+        <v>190876690.88999999</v>
+      </c>
+      <c r="F31" s="6">
         <v>183865965.58000001</v>
       </c>
-      <c r="E31" s="6">
+      <c r="G31" s="6">
         <v>1981216.45</v>
       </c>
-      <c r="F31" s="6">
+      <c r="H31" s="6">
         <v>3389073.5</v>
       </c>
-      <c r="G31" s="7">
+      <c r="I31" s="7">
         <v>5370289.9500000002</v>
       </c>
     </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>2022</v>
       </c>
@@ -1356,22 +1547,28 @@
         <v>2121</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D32" s="6">
+        <v>2732447147.5300002</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2675654178.8200002</v>
+      </c>
+      <c r="F32" s="6">
         <v>2000806584.1099999</v>
       </c>
-      <c r="E32" s="6">
+      <c r="G32" s="6">
         <v>94866365.349999994</v>
       </c>
-      <c r="F32" s="6">
+      <c r="H32" s="6">
         <v>67386629.629999995</v>
       </c>
-      <c r="G32" s="7">
+      <c r="I32" s="7">
         <v>162252994.97999999</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>2022</v>
       </c>
@@ -1379,22 +1576,28 @@
         <v>2151</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D33" s="6">
+        <v>54848300.420000002</v>
+      </c>
+      <c r="E33" s="6">
+        <v>50479779.700000003</v>
+      </c>
+      <c r="F33" s="6">
         <v>50120409.799999997</v>
       </c>
-      <c r="E33" s="6">
+      <c r="G33" s="6">
         <v>4125</v>
       </c>
-      <c r="F33" s="6">
+      <c r="H33" s="6">
         <v>6086840.5099999998</v>
       </c>
-      <c r="G33" s="7">
+      <c r="I33" s="7">
         <v>6090965.5099999998</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>2022</v>
       </c>
@@ -1402,22 +1605,28 @@
         <v>2161</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D34" s="6">
+        <v>16628991.48</v>
+      </c>
+      <c r="E34" s="6">
+        <v>15101587.529999999</v>
+      </c>
+      <c r="F34" s="6">
         <v>14946425.029999999</v>
       </c>
-      <c r="E34" s="6">
+      <c r="G34" s="6">
         <v>15535.07</v>
       </c>
-      <c r="F34" s="6">
+      <c r="H34" s="6">
         <v>2608678.6800000002</v>
       </c>
-      <c r="G34" s="7">
+      <c r="I34" s="7">
         <v>2624213.75</v>
       </c>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>2022</v>
       </c>
@@ -1425,22 +1634,28 @@
         <v>2171</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D35" s="6">
+        <v>4662678.05</v>
+      </c>
+      <c r="E35" s="6">
+        <v>4296034.1900000004</v>
+      </c>
+      <c r="F35" s="6">
         <v>4144793.59</v>
       </c>
-      <c r="E35" s="6">
+      <c r="G35" s="6">
         <v>67.5</v>
       </c>
-      <c r="F35" s="6">
+      <c r="H35" s="6">
         <v>13446.09</v>
       </c>
-      <c r="G35" s="7">
+      <c r="I35" s="7">
         <v>13513.59</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>2022</v>
       </c>
@@ -1448,22 +1663,28 @@
         <v>2181</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D36" s="6">
+        <v>44939828.32</v>
+      </c>
+      <c r="E36" s="6">
+        <v>43912375.759999998</v>
+      </c>
+      <c r="F36" s="6">
         <v>43171411.159999996</v>
       </c>
-      <c r="E36" s="6">
-        <v>0</v>
-      </c>
-      <c r="F36" s="6">
+      <c r="G36" s="6">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6">
         <v>418535.58</v>
       </c>
-      <c r="G36" s="7">
+      <c r="I36" s="7">
         <v>418535.58</v>
       </c>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>2022</v>
       </c>
@@ -1471,22 +1692,28 @@
         <v>2201</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D37" s="6">
+        <v>24595717.43</v>
+      </c>
+      <c r="E37" s="6">
+        <v>20047336.039999999</v>
+      </c>
+      <c r="F37" s="6">
         <v>19187028.920000002</v>
       </c>
-      <c r="E37" s="6">
-        <v>0</v>
-      </c>
-      <c r="F37" s="6">
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6">
         <v>934662.77</v>
       </c>
-      <c r="G37" s="7">
+      <c r="I37" s="7">
         <v>934662.77</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>2022</v>
       </c>
@@ -1494,22 +1721,28 @@
         <v>2211</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D38" s="6">
+        <v>20189976.399999999</v>
+      </c>
+      <c r="E38" s="6">
+        <v>19470842.739999998</v>
+      </c>
+      <c r="F38" s="6">
         <v>18947352.890000001</v>
       </c>
-      <c r="E38" s="6">
+      <c r="G38" s="6">
         <v>140686.89000000001</v>
       </c>
-      <c r="F38" s="6">
+      <c r="H38" s="6">
         <v>756689.71</v>
       </c>
-      <c r="G38" s="7">
+      <c r="I38" s="7">
         <v>897376.6</v>
       </c>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>2022</v>
       </c>
@@ -1517,22 +1750,28 @@
         <v>2241</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D39" s="6">
+        <v>69270924.790000007</v>
+      </c>
+      <c r="E39" s="6">
+        <v>64810240.329999998</v>
+      </c>
+      <c r="F39" s="6">
         <v>64595191.740000002</v>
       </c>
-      <c r="E39" s="6">
+      <c r="G39" s="6">
         <v>10437314.16</v>
       </c>
-      <c r="F39" s="6">
+      <c r="H39" s="6">
         <v>1573915.38</v>
       </c>
-      <c r="G39" s="7">
+      <c r="I39" s="7">
         <v>12011229.539999999</v>
       </c>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>2022</v>
       </c>
@@ -1540,22 +1779,28 @@
         <v>2251</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D40" s="6">
+        <v>32289616.850000001</v>
+      </c>
+      <c r="E40" s="6">
+        <v>30153432.18</v>
+      </c>
+      <c r="F40" s="6">
         <v>29578426.34</v>
       </c>
-      <c r="E40" s="6">
-        <v>0</v>
-      </c>
-      <c r="F40" s="6">
+      <c r="G40" s="6">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6">
         <v>671682.59</v>
       </c>
-      <c r="G40" s="7">
+      <c r="I40" s="7">
         <v>671682.59</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>2022</v>
       </c>
@@ -1563,22 +1808,28 @@
         <v>2261</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D41" s="6">
+        <v>319786910.27999997</v>
+      </c>
+      <c r="E41" s="6">
+        <v>263858227.88</v>
+      </c>
+      <c r="F41" s="6">
         <v>252638336.78</v>
       </c>
-      <c r="E41" s="6">
+      <c r="G41" s="6">
         <v>101930917.98999999</v>
       </c>
-      <c r="F41" s="6">
+      <c r="H41" s="6">
         <v>47063914.030000001</v>
       </c>
-      <c r="G41" s="7">
+      <c r="I41" s="7">
         <v>148994832.02000001</v>
       </c>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>2022</v>
       </c>
@@ -1586,22 +1837,28 @@
         <v>2271</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D42" s="6">
+        <v>2277629071.1900001</v>
+      </c>
+      <c r="E42" s="6">
+        <v>2165324017.21</v>
+      </c>
+      <c r="F42" s="6">
         <v>2143497567.5699999</v>
       </c>
-      <c r="E42" s="6">
+      <c r="G42" s="6">
         <v>3753299.71</v>
       </c>
-      <c r="F42" s="6">
+      <c r="H42" s="6">
         <v>42680567.960000001</v>
       </c>
-      <c r="G42" s="7">
+      <c r="I42" s="7">
         <v>46433867.670000002</v>
       </c>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>2022</v>
       </c>
@@ -1609,22 +1866,28 @@
         <v>2281</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D43" s="6">
+        <v>7453421.7699999996</v>
+      </c>
+      <c r="E43" s="6">
+        <v>7042060.9900000002</v>
+      </c>
+      <c r="F43" s="6">
         <v>6627633.6699999999</v>
       </c>
-      <c r="E43" s="6">
+      <c r="G43" s="6">
         <v>7006</v>
       </c>
-      <c r="F43" s="6">
+      <c r="H43" s="6">
         <v>1513188.14</v>
       </c>
-      <c r="G43" s="7">
+      <c r="I43" s="7">
         <v>1520194.14</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>2022</v>
       </c>
@@ -1632,22 +1895,28 @@
         <v>2301</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D44" s="6">
+        <v>2009831554.49</v>
+      </c>
+      <c r="E44" s="6">
+        <v>1273629898.99</v>
+      </c>
+      <c r="F44" s="6">
         <v>1248196121.5999999</v>
       </c>
-      <c r="E44" s="6">
+      <c r="G44" s="6">
         <v>3419688.86</v>
       </c>
-      <c r="F44" s="6">
+      <c r="H44" s="6">
         <v>168251149.94</v>
       </c>
-      <c r="G44" s="7">
+      <c r="I44" s="7">
         <v>171670838.80000001</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>2022</v>
       </c>
@@ -1655,22 +1924,28 @@
         <v>2311</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D45" s="6">
+        <v>434351243.76999998</v>
+      </c>
+      <c r="E45" s="6">
+        <v>412467573.12</v>
+      </c>
+      <c r="F45" s="6">
         <v>403987795.94</v>
       </c>
-      <c r="E45" s="6">
+      <c r="G45" s="6">
         <v>1669347.22</v>
       </c>
-      <c r="F45" s="6">
+      <c r="H45" s="6">
         <v>67683789.959999993</v>
       </c>
-      <c r="G45" s="7">
+      <c r="I45" s="7">
         <v>69353137.180000007</v>
       </c>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>2022</v>
       </c>
@@ -1678,22 +1953,28 @@
         <v>2321</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D46" s="6">
+        <v>333195770.75999999</v>
+      </c>
+      <c r="E46" s="6">
+        <v>296763683.45999998</v>
+      </c>
+      <c r="F46" s="6">
         <v>290862823.01999998</v>
       </c>
-      <c r="E46" s="6">
+      <c r="G46" s="6">
         <v>255386.81</v>
       </c>
-      <c r="F46" s="6">
+      <c r="H46" s="6">
         <v>25746888.77</v>
       </c>
-      <c r="G46" s="7">
+      <c r="I46" s="7">
         <v>26002275.579999998</v>
       </c>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>2022</v>
       </c>
@@ -1701,22 +1982,28 @@
         <v>2331</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D47" s="6">
+        <v>26902206.649999999</v>
+      </c>
+      <c r="E47" s="6">
+        <v>26685069.710000001</v>
+      </c>
+      <c r="F47" s="6">
         <v>26064598.710000001</v>
       </c>
-      <c r="E47" s="6">
+      <c r="G47" s="6">
         <v>333694.71999999997</v>
       </c>
-      <c r="F47" s="6">
+      <c r="H47" s="6">
         <v>520848.74</v>
       </c>
-      <c r="G47" s="7">
+      <c r="I47" s="7">
         <v>854543.46</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>2022</v>
       </c>
@@ -1724,22 +2011,28 @@
         <v>2351</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D48" s="6">
+        <v>464167620.30000001</v>
+      </c>
+      <c r="E48" s="6">
+        <v>430024005.97000003</v>
+      </c>
+      <c r="F48" s="6">
         <v>419107102.61000001</v>
       </c>
-      <c r="E48" s="6">
+      <c r="G48" s="6">
         <v>380901.69</v>
       </c>
-      <c r="F48" s="6">
+      <c r="H48" s="6">
         <v>13513330.289999999</v>
       </c>
-      <c r="G48" s="7">
+      <c r="I48" s="7">
         <v>13894231.98</v>
       </c>
     </row>
-    <row r="49" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>2022</v>
       </c>
@@ -1747,22 +2040,28 @@
         <v>2371</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D49" s="6">
+        <v>265147788.61000001</v>
+      </c>
+      <c r="E49" s="6">
+        <v>260504964.97</v>
+      </c>
+      <c r="F49" s="6">
         <v>260025427.44</v>
       </c>
-      <c r="E49" s="6">
+      <c r="G49" s="6">
         <v>11259.94</v>
       </c>
-      <c r="F49" s="6">
+      <c r="H49" s="6">
         <v>7021591.4299999997</v>
       </c>
-      <c r="G49" s="7">
+      <c r="I49" s="7">
         <v>7032851.3700000001</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>2022</v>
       </c>
@@ -1770,22 +2069,28 @@
         <v>2421</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D50" s="6">
+        <v>53060472.469999999</v>
+      </c>
+      <c r="E50" s="6">
+        <v>46263655.960000001</v>
+      </c>
+      <c r="F50" s="6">
         <v>45692556.630000003</v>
       </c>
-      <c r="E50" s="6">
+      <c r="G50" s="6">
         <v>976681.46</v>
       </c>
-      <c r="F50" s="6">
+      <c r="H50" s="6">
         <v>14019630.84</v>
       </c>
-      <c r="G50" s="7">
+      <c r="I50" s="7">
         <v>14996312.300000001</v>
       </c>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>2022</v>
       </c>
@@ -1793,22 +2098,28 @@
         <v>2431</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D51" s="6">
+        <v>6030203.9800000004</v>
+      </c>
+      <c r="E51" s="6">
+        <v>5910378.0199999996</v>
+      </c>
+      <c r="F51" s="6">
         <v>5805259.6699999999</v>
       </c>
-      <c r="E51" s="6">
-        <v>0</v>
-      </c>
-      <c r="F51" s="6">
+      <c r="G51" s="6">
+        <v>0</v>
+      </c>
+      <c r="H51" s="6">
         <v>23921.89</v>
       </c>
-      <c r="G51" s="7">
+      <c r="I51" s="7">
         <v>23921.89</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>2022</v>
       </c>
@@ -1816,22 +2127,28 @@
         <v>2441</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D52" s="6">
+        <v>15948670.24</v>
+      </c>
+      <c r="E52" s="6">
+        <v>15099248.76</v>
+      </c>
+      <c r="F52" s="6">
         <v>15008695.060000001</v>
       </c>
-      <c r="E52" s="6">
-        <v>0</v>
-      </c>
-      <c r="F52" s="6">
+      <c r="G52" s="6">
+        <v>0</v>
+      </c>
+      <c r="H52" s="6">
         <v>744776.36</v>
       </c>
-      <c r="G52" s="7">
+      <c r="I52" s="7">
         <v>744776.36</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>2022</v>
       </c>
@@ -1839,359 +2156,439 @@
         <v>2461</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="6">
+        <v>3998282.31</v>
+      </c>
+      <c r="E53" s="6">
+        <v>2913330.3</v>
+      </c>
+      <c r="F53" s="6">
         <v>2891473.26</v>
       </c>
-      <c r="E53" s="6">
+      <c r="G53" s="6">
         <v>114.72</v>
       </c>
-      <c r="F53" s="6">
+      <c r="H53" s="6">
         <v>64611.25</v>
       </c>
-      <c r="G53" s="7">
+      <c r="I53" s="7">
         <v>64725.97</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>2022</v>
       </c>
       <c r="B54" s="4">
+        <v>3041</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="6">
+        <v>368437125.56999999</v>
+      </c>
+      <c r="E54" s="6">
+        <v>368437125.56999999</v>
+      </c>
+      <c r="F54" s="6">
+        <v>368437125.56999999</v>
+      </c>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="7"/>
+    </row>
+    <row r="55" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B55" s="4">
+        <v>3051</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D55" s="6">
+        <v>119899404.19</v>
+      </c>
+      <c r="E55" s="6">
+        <v>119899404.19</v>
+      </c>
+      <c r="F55" s="6">
+        <v>119899404.19</v>
+      </c>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="7"/>
+    </row>
+    <row r="56" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B56" s="4">
         <v>4091</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6">
-        <v>0</v>
-      </c>
-      <c r="G54" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B55" s="4">
+      <c r="C56" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B57" s="4">
         <v>4101</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="C57" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" s="6">
+        <v>17493925.289999999</v>
+      </c>
+      <c r="E57" s="6">
         <v>16080240.210000001</v>
       </c>
-      <c r="E55" s="6">
-        <v>0</v>
-      </c>
-      <c r="F55" s="6">
+      <c r="F57" s="6">
+        <v>16080240.210000001</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6">
         <v>517189.73</v>
       </c>
-      <c r="G55" s="7">
+      <c r="I57" s="7">
         <v>517189.73</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B56" s="4">
+    <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B58" s="4">
         <v>4141</v>
       </c>
-      <c r="C56" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C58" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="6">
+        <v>31245732.350000001</v>
+      </c>
+      <c r="E58" s="6">
         <v>13353865.57</v>
       </c>
-      <c r="E56" s="6">
+      <c r="F58" s="6">
+        <v>13353865.57</v>
+      </c>
+      <c r="G58" s="6">
         <v>1574.5</v>
       </c>
-      <c r="F56" s="6">
+      <c r="H58" s="6">
         <v>5560409.71</v>
       </c>
-      <c r="G56" s="7">
+      <c r="I58" s="7">
         <v>5561984.21</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B57" s="4">
+    <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B59" s="4">
         <v>4251</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C59" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" s="6">
+        <v>207531660.90000001</v>
+      </c>
+      <c r="E59" s="6">
+        <v>189241489.69999999</v>
+      </c>
+      <c r="F59" s="6">
         <v>187462418.97999999</v>
       </c>
-      <c r="E57" s="6">
+      <c r="G59" s="6">
         <v>98887758.569999993</v>
       </c>
-      <c r="F57" s="6">
+      <c r="H59" s="6">
         <v>4684458.53</v>
       </c>
-      <c r="G57" s="7">
+      <c r="I59" s="7">
         <v>103572217.09999999</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B58" s="4">
+    <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B60" s="4">
         <v>4291</v>
       </c>
-      <c r="C58" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C60" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="6">
+        <v>10255262090.27</v>
+      </c>
+      <c r="E60" s="6">
+        <v>9575510065.2199993</v>
+      </c>
+      <c r="F60" s="6">
         <v>9231614379.4599991</v>
       </c>
-      <c r="E58" s="6">
+      <c r="G60" s="6">
         <v>554014631.27999997</v>
       </c>
-      <c r="F58" s="6">
+      <c r="H60" s="6">
         <v>786454402.17999995</v>
       </c>
-      <c r="G58" s="7">
+      <c r="I60" s="7">
         <v>1340469033.46</v>
       </c>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B59" s="4">
+    <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B61" s="4">
         <v>4331</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C61" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D61" s="6">
+        <v>147406.89000000001</v>
+      </c>
+      <c r="E61" s="6">
+        <v>147406.89000000001</v>
+      </c>
+      <c r="F61" s="6">
         <v>143721.71</v>
       </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="7"/>
-    </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B60" s="4">
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="7"/>
+    </row>
+    <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B62" s="4">
         <v>4341</v>
       </c>
-      <c r="C60" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D60" s="6">
+      <c r="C62" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D62" s="6">
+        <v>2866852.09</v>
+      </c>
+      <c r="E62" s="6">
+        <v>2778584.69</v>
+      </c>
+      <c r="F62" s="6">
         <v>2557135.6800000002</v>
       </c>
-      <c r="E60" s="6">
-        <v>0</v>
-      </c>
-      <c r="F60" s="6">
+      <c r="G62" s="6">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6">
         <v>129135.76</v>
       </c>
-      <c r="G60" s="7">
+      <c r="I62" s="7">
         <v>129135.76</v>
       </c>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B61" s="4">
+    <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B63" s="4">
         <v>4381</v>
       </c>
-      <c r="C61" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="C63" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="6">
+        <v>140227334.65000001</v>
+      </c>
+      <c r="E63" s="6">
+        <v>53251682.009999998</v>
+      </c>
+      <c r="F63" s="6">
         <v>52665792.689999998</v>
       </c>
-      <c r="E61" s="6">
-        <v>0</v>
-      </c>
-      <c r="F61" s="6">
+      <c r="G63" s="6">
+        <v>0</v>
+      </c>
+      <c r="H63" s="6">
         <v>5954269.9000000004</v>
       </c>
-      <c r="G61" s="7">
+      <c r="I63" s="7">
         <v>5954269.9000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B62" s="4">
-        <v>4421</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D62" s="6">
-        <v>1278479.27</v>
-      </c>
-      <c r="E62" s="6">
-        <v>0</v>
-      </c>
-      <c r="F62" s="6">
-        <v>0</v>
-      </c>
-      <c r="G62" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B63" s="4">
+    <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B64" s="4">
         <v>4451</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C64" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="6">
+        <v>11107774.68</v>
+      </c>
+      <c r="E64" s="6">
+        <v>10032800.23</v>
+      </c>
+      <c r="F64" s="6">
         <v>9730140.4499999993</v>
       </c>
-      <c r="E63" s="6">
-        <v>0</v>
-      </c>
-      <c r="F63" s="6">
+      <c r="G64" s="6">
+        <v>0</v>
+      </c>
+      <c r="H64" s="6">
         <v>2888273.21</v>
       </c>
-      <c r="G63" s="7">
+      <c r="I64" s="7">
         <v>2888273.21</v>
       </c>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B64" s="4">
+    <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B65" s="4">
         <v>4491</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C65" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" s="6">
+        <v>12198756.32</v>
+      </c>
+      <c r="E65" s="6">
+        <v>12198756.32</v>
+      </c>
+      <c r="F65" s="6">
         <v>9336561.1600000001</v>
       </c>
-      <c r="E64" s="6">
-        <v>0</v>
-      </c>
-      <c r="F64" s="6">
-        <v>0</v>
-      </c>
-      <c r="G64" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B65" s="4">
+      <c r="G65" s="6">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6">
+        <v>0</v>
+      </c>
+      <c r="I65" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B66" s="4">
         <v>4541</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D65" s="6">
+      <c r="C66" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D66" s="6">
+        <v>315895.03000000003</v>
+      </c>
+      <c r="E66" s="6">
         <v>315480.44</v>
       </c>
-      <c r="E65" s="6">
-        <v>0</v>
-      </c>
-      <c r="F65" s="6">
-        <v>0</v>
-      </c>
-      <c r="G65" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B66" s="4">
+      <c r="F66" s="6">
+        <v>315480.44</v>
+      </c>
+      <c r="G66" s="6">
+        <v>0</v>
+      </c>
+      <c r="H66" s="6">
+        <v>0</v>
+      </c>
+      <c r="I66" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B67" s="4">
         <v>4551</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D66" s="6">
+      <c r="C67" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D67" s="6">
+        <v>161975565.86000001</v>
+      </c>
+      <c r="E67" s="6">
+        <v>161973985.31</v>
+      </c>
+      <c r="F67" s="6">
         <v>155079704.44999999</v>
       </c>
-      <c r="E66" s="6">
+      <c r="G67" s="6">
         <v>12273523.84</v>
       </c>
-      <c r="F66" s="6">
-        <v>0</v>
-      </c>
-      <c r="G66" s="7">
+      <c r="H67" s="6">
+        <v>0</v>
+      </c>
+      <c r="I67" s="7">
         <v>12273523.84</v>
       </c>
     </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B67" s="4">
+    <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B68" s="4">
         <v>4601</v>
       </c>
-      <c r="C67" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D67" s="6">
+      <c r="C68" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D68" s="6">
+        <v>464551.64</v>
+      </c>
+      <c r="E68" s="6">
+        <v>419551.64</v>
+      </c>
+      <c r="F68" s="6">
         <v>239551.64</v>
       </c>
-      <c r="E67" s="6">
+      <c r="G68" s="6">
         <v>80000</v>
       </c>
-      <c r="F67" s="6">
+      <c r="H68" s="6">
         <v>80000</v>
       </c>
-      <c r="G67" s="7">
+      <c r="I68" s="7">
         <v>160000</v>
       </c>
     </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B68" s="4">
-        <v>4631</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D68" s="6">
-        <v>238193664.03999999</v>
-      </c>
-      <c r="E68" s="6">
-        <v>275729.74</v>
-      </c>
-      <c r="F68" s="6">
-        <v>15778864.880000001</v>
-      </c>
-      <c r="G68" s="7">
-        <v>16054594.619999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>2022</v>
       </c>
@@ -2199,22 +2596,28 @@
         <v>4691</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D69" s="6">
+        <v>25338987.879999999</v>
+      </c>
+      <c r="E69" s="6">
+        <v>11474135.710000001</v>
+      </c>
+      <c r="F69" s="6">
         <v>9347783.0199999996</v>
       </c>
-      <c r="E69" s="6">
+      <c r="G69" s="6">
         <v>1094891.98</v>
       </c>
-      <c r="F69" s="6">
+      <c r="H69" s="6">
         <v>4039900.86</v>
       </c>
-      <c r="G69" s="7">
+      <c r="I69" s="7">
         <v>5134792.84</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>2022</v>
       </c>
@@ -2222,22 +2625,28 @@
         <v>4701</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D70" s="6">
-        <v>0</v>
+        <v>3542540.26</v>
       </c>
       <c r="E70" s="6">
-        <v>0</v>
+        <v>4264.26</v>
       </c>
       <c r="F70" s="6">
         <v>0</v>
       </c>
-      <c r="G70" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G70" s="6">
+        <v>0</v>
+      </c>
+      <c r="H70" s="6">
+        <v>0</v>
+      </c>
+      <c r="I70" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>2022</v>
       </c>
@@ -2245,22 +2654,28 @@
         <v>4711</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D71" s="6">
+        <v>15325406751.49</v>
+      </c>
+      <c r="E71" s="6">
+        <v>15323499427.6</v>
+      </c>
+      <c r="F71" s="6">
         <v>15328734230.09</v>
       </c>
-      <c r="E71" s="6">
-        <v>0</v>
-      </c>
-      <c r="F71" s="6">
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6">
         <v>79198.5</v>
       </c>
-      <c r="G71" s="7">
+      <c r="I71" s="7">
         <v>79198.5</v>
       </c>
     </row>
-    <row r="72" spans="1:7" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15270" windowHeight="8355"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\html_portal\portal_despesa_empenho\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\OneDrive\Documents\html\portal_despesa_empenho\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F62A7574-6FEF-4A33-ADC8-5B1FFA9201A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="orgao" sheetId="1" r:id="rId1"/>
@@ -19,15 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>Ano de Exercício</t>
   </si>
   <si>
-    <t>Unidade Orçamentária - Código</t>
-  </si>
-  <si>
-    <t>Unidade Orçamentária - Nome</t>
+    <t>Unidade Orçamentária - Código/Nome</t>
+  </si>
+  <si>
+    <t>Unidade Orçamentária - Sigla</t>
   </si>
   <si>
     <t>Valor Despesa Empenhada</t>
@@ -48,220 +49,424 @@
     <t>Valor Pago RP</t>
   </si>
   <si>
-    <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>ADVOCACIA GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE FAZENDA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
-  </si>
-  <si>
-    <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
-  </si>
-  <si>
-    <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE GOVERNO</t>
-  </si>
-  <si>
-    <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>CONTROLADORIA-GERAL DO ESTADO</t>
-  </si>
-  <si>
-    <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>SECRETARIA-GERAL</t>
-  </si>
-  <si>
-    <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
-  </si>
-  <si>
-    <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
-  </si>
-  <si>
-    <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
-  </si>
-  <si>
-    <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO JOAO PINHEIRO</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HELENA ANTIPOFF</t>
-  </si>
-  <si>
-    <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE ARTE DE OURO PRETO</t>
-  </si>
-  <si>
-    <t>FUNDACAO CLOVIS SALGADO</t>
-  </si>
-  <si>
-    <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
-  </si>
-  <si>
-    <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO EZEQUIEL DIAS</t>
-  </si>
-  <si>
-    <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
-  </si>
-  <si>
-    <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
-  </si>
-  <si>
-    <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
-  </si>
-  <si>
-    <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
-  </si>
-  <si>
-    <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE HABITACAO</t>
-  </si>
-  <si>
-    <t>FUNDO PENITENCIARIO ESTADUAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SAUDE</t>
-  </si>
-  <si>
-    <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
-  </si>
-  <si>
-    <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE CULTURA</t>
-  </si>
-  <si>
-    <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
-  </si>
-  <si>
-    <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+    <t>1071 - GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>GABINETE MILITAR</t>
+  </si>
+  <si>
+    <t>1081 - ADVOCACIA GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>1101 - OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>OGE</t>
+  </si>
+  <si>
+    <t>1191 - SECRETARIA DE ESTADO DE FAZENDA</t>
+  </si>
+  <si>
+    <t>SEF</t>
+  </si>
+  <si>
+    <t>1221 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+  </si>
+  <si>
+    <t>SEDE</t>
+  </si>
+  <si>
+    <t>1231 - SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+  </si>
+  <si>
+    <t>SEAPA</t>
+  </si>
+  <si>
+    <t>1251 - POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PMMG</t>
+  </si>
+  <si>
+    <t>1261 - SECRETARIA DE ESTADO DE EDUCACAO</t>
+  </si>
+  <si>
+    <t>SEE</t>
+  </si>
+  <si>
+    <t>1271 - SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+  </si>
+  <si>
+    <t>SECULT</t>
+  </si>
+  <si>
+    <t>1301 - SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
+  </si>
+  <si>
+    <t>SEINFRA</t>
+  </si>
+  <si>
+    <t>1371 - SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+  </si>
+  <si>
+    <t>SEMAD</t>
+  </si>
+  <si>
+    <t>1401 - CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>CBMMG</t>
+  </si>
+  <si>
+    <t>1451 - SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+  </si>
+  <si>
+    <t>SEJUSP</t>
+  </si>
+  <si>
+    <t>1481 - SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+  </si>
+  <si>
+    <t>SEDESE</t>
+  </si>
+  <si>
+    <t>1491 - SECRETARIA DE ESTADO DE GOVERNO</t>
+  </si>
+  <si>
+    <t>SEGOV</t>
+  </si>
+  <si>
+    <t>1501 - SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>SEPLAG</t>
+  </si>
+  <si>
+    <t>1511 - POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>PCMG</t>
+  </si>
+  <si>
+    <t>1521 - CONTROLADORIA-GERAL DO ESTADO</t>
+  </si>
+  <si>
+    <t>CGE</t>
+  </si>
+  <si>
+    <t>1541 - ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>ESP MG</t>
+  </si>
+  <si>
+    <t>1631 - SECRETARIA-GERAL</t>
+  </si>
+  <si>
+    <t>SEC. GERAL</t>
+  </si>
+  <si>
+    <t>1911 - EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+  </si>
+  <si>
+    <t>EGE - SEF</t>
+  </si>
+  <si>
+    <t>1915 - PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+  </si>
+  <si>
+    <t>PARTICIPAÇÃO EMPRESAS</t>
+  </si>
+  <si>
+    <t>1916 - GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+  </si>
+  <si>
+    <t>GDPE - SEF</t>
+  </si>
+  <si>
+    <t>1941 - EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+  </si>
+  <si>
+    <t>EGE-SEPLAG</t>
+  </si>
+  <si>
+    <t>2011 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSEMG</t>
+  </si>
+  <si>
+    <t>2041 - LOTERIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>LEMG</t>
+  </si>
+  <si>
+    <t>2061 - FUNDACAO JOAO PINHEIRO</t>
+  </si>
+  <si>
+    <t>FJP</t>
+  </si>
+  <si>
+    <t>2071 - FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAPEMIG</t>
+  </si>
+  <si>
+    <t>2091 - FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t>FEAM</t>
+  </si>
+  <si>
+    <t>2101 - INSTITUTO ESTADUAL DE FLORESTAS</t>
+  </si>
+  <si>
+    <t>IEF</t>
+  </si>
+  <si>
+    <t>2121 - INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPSM</t>
+  </si>
+  <si>
+    <t>2151 - FUNDACAO HELENA ANTIPOFF</t>
+  </si>
+  <si>
+    <t>FHA</t>
+  </si>
+  <si>
+    <t>2161 - FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+  </si>
+  <si>
+    <t>FUCAM</t>
+  </si>
+  <si>
+    <t>2171 - FUNDACAO DE ARTE DE OURO PRETO</t>
+  </si>
+  <si>
+    <t>FAOP</t>
+  </si>
+  <si>
+    <t>2181 - FUNDACAO CLOVIS SALGADO</t>
+  </si>
+  <si>
+    <t>FCS</t>
+  </si>
+  <si>
+    <t>2201 - INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IEPHA</t>
+  </si>
+  <si>
+    <t>2211 - FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+  </si>
+  <si>
+    <t>TV MINAS</t>
+  </si>
+  <si>
+    <t>2241 - INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+  </si>
+  <si>
+    <t>IGAM</t>
+  </si>
+  <si>
+    <t>2251 - JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>JUCEMG</t>
+  </si>
+  <si>
+    <t>2261 - FUNDACAO EZEQUIEL DIAS</t>
+  </si>
+  <si>
+    <t>FUNED</t>
+  </si>
+  <si>
+    <t>2271 - FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FHEMIG</t>
+  </si>
+  <si>
+    <t>2281 - FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UTRAMIG</t>
+  </si>
+  <si>
+    <t>2301 - DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>DER-MG</t>
+  </si>
+  <si>
+    <t>2311 - UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>UNIMONTES</t>
+  </si>
+  <si>
+    <t>2321 - FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>HEMOMINAS</t>
+  </si>
+  <si>
+    <t>2331 - INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IPEMMG</t>
+  </si>
+  <si>
+    <t>2351 - UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>UEMG</t>
+  </si>
+  <si>
+    <t>2371 - INSTITUTO MINEIRO DE AGROPECUARIA</t>
+  </si>
+  <si>
+    <t>IMA</t>
+  </si>
+  <si>
+    <t>2421 - INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>IDENE</t>
+  </si>
+  <si>
+    <t>2431 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DE BELO HORIZONTE</t>
+  </si>
+  <si>
+    <t>AGÊNCIA RMBH</t>
+  </si>
+  <si>
+    <t>2441 - AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+  </si>
+  <si>
+    <t>ARSAE -MG</t>
+  </si>
+  <si>
+    <t>2461 - AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+  </si>
+  <si>
+    <t>ARMVA</t>
+  </si>
+  <si>
+    <t>3041 - EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EMATER</t>
+  </si>
+  <si>
+    <t>3051 - EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>EPAMIG</t>
+  </si>
+  <si>
+    <t>4101 - FUNDO ESTADUAL DE HABITACAO</t>
+  </si>
+  <si>
+    <t>FEH</t>
+  </si>
+  <si>
+    <t>4141 - FUNDO PENITENCIARIO ESTADUAL</t>
+  </si>
+  <si>
+    <t>FPE</t>
+  </si>
+  <si>
+    <t>4251 - FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+  </si>
+  <si>
+    <t>FEAS</t>
+  </si>
+  <si>
+    <t>4291 - FUNDO ESTADUAL DE SAUDE</t>
+  </si>
+  <si>
+    <t>FES</t>
+  </si>
+  <si>
+    <t>4331 - FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+  </si>
+  <si>
+    <t>FDM</t>
+  </si>
+  <si>
+    <t>4341 - FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+  </si>
+  <si>
+    <t>FHIDRO</t>
+  </si>
+  <si>
+    <t>4381 - FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+  </si>
+  <si>
+    <t>FUNTRANS</t>
+  </si>
+  <si>
+    <t>4451 - FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+  </si>
+  <si>
+    <t>FEPDC</t>
+  </si>
+  <si>
+    <t>4491 - FUNDO ESTADUAL DE CULTURA</t>
+  </si>
+  <si>
+    <t>FEC</t>
+  </si>
+  <si>
+    <t>4541 - FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FAHMEMG</t>
+  </si>
+  <si>
+    <t>4551 - FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FUNAPEC</t>
+  </si>
+  <si>
+    <t>4601 - FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+  </si>
+  <si>
+    <t>FEI</t>
+  </si>
+  <si>
+    <t>4691 - FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FESP-MG</t>
+  </si>
+  <si>
+    <t>4701 - FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FET-MG</t>
+  </si>
+  <si>
+    <t>4711 - FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+  </si>
+  <si>
+    <t>FFP - MG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###,###,###,##0.00"/>
   </numFmts>
@@ -375,39 +580,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -440,9 +645,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -475,6 +697,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -536,13 +775,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -551,6 +783,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -615,24 +854,44 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I72"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="119.28515625" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
     <col min="4" max="6" width="17.28515625" customWidth="1"/>
     <col min="7" max="7" width="21.28515625" customWidth="1"/>
     <col min="8" max="8" width="25.140625" customWidth="1"/>
@@ -640,14 +899,14 @@
     <col min="10" max="10" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="45.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -673,11 +932,11 @@
       <c r="A2" s="4">
         <v>2022</v>
       </c>
-      <c r="B2" s="4">
-        <v>1071</v>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="6">
         <v>41468457.479999997</v>
@@ -702,11 +961,11 @@
       <c r="A3" s="4">
         <v>2022</v>
       </c>
-      <c r="B3" s="4">
-        <v>1081</v>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6">
         <v>1222668188.4300001</v>
@@ -731,11 +990,11 @@
       <c r="A4" s="4">
         <v>2022</v>
       </c>
-      <c r="B4" s="4">
-        <v>1101</v>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6">
         <v>12148887.189999999</v>
@@ -760,11 +1019,11 @@
       <c r="A5" s="4">
         <v>2022</v>
       </c>
-      <c r="B5" s="4">
-        <v>1191</v>
+      <c r="B5" s="5" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6">
         <v>1539130234.2</v>
@@ -789,11 +1048,11 @@
       <c r="A6" s="4">
         <v>2022</v>
       </c>
-      <c r="B6" s="4">
-        <v>1221</v>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6">
         <v>91983736.400000006</v>
@@ -818,11 +1077,11 @@
       <c r="A7" s="4">
         <v>2022</v>
       </c>
-      <c r="B7" s="4">
-        <v>1231</v>
+      <c r="B7" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6">
         <v>196292319.50999999</v>
@@ -847,11 +1106,11 @@
       <c r="A8" s="4">
         <v>2022</v>
       </c>
-      <c r="B8" s="4">
-        <v>1251</v>
+      <c r="B8" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6">
         <v>12979474804.25</v>
@@ -876,11 +1135,11 @@
       <c r="A9" s="4">
         <v>2022</v>
       </c>
-      <c r="B9" s="4">
-        <v>1261</v>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D9" s="6">
         <v>16633018692.76</v>
@@ -905,11 +1164,11 @@
       <c r="A10" s="4">
         <v>2022</v>
       </c>
-      <c r="B10" s="4">
-        <v>1271</v>
+      <c r="B10" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6">
         <v>71925491.400000006</v>
@@ -934,11 +1193,11 @@
       <c r="A11" s="4">
         <v>2022</v>
       </c>
-      <c r="B11" s="4">
-        <v>1301</v>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D11" s="6">
         <v>600547625.35000002</v>
@@ -963,11 +1222,11 @@
       <c r="A12" s="4">
         <v>2022</v>
       </c>
-      <c r="B12" s="4">
-        <v>1371</v>
+      <c r="B12" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D12" s="6">
         <v>181795255.09999999</v>
@@ -992,11 +1251,11 @@
       <c r="A13" s="4">
         <v>2022</v>
       </c>
-      <c r="B13" s="4">
-        <v>1401</v>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D13" s="6">
         <v>1617069712.1900001</v>
@@ -1021,11 +1280,11 @@
       <c r="A14" s="4">
         <v>2022</v>
       </c>
-      <c r="B14" s="4">
-        <v>1451</v>
+      <c r="B14" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D14" s="6">
         <v>3393511812.1300001</v>
@@ -1050,11 +1309,11 @@
       <c r="A15" s="4">
         <v>2022</v>
       </c>
-      <c r="B15" s="4">
-        <v>1481</v>
+      <c r="B15" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6">
         <v>152723547.84</v>
@@ -1079,11 +1338,11 @@
       <c r="A16" s="4">
         <v>2022</v>
       </c>
-      <c r="B16" s="4">
-        <v>1491</v>
+      <c r="B16" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D16" s="6">
         <v>1612507669.4200001</v>
@@ -1108,11 +1367,11 @@
       <c r="A17" s="4">
         <v>2022</v>
       </c>
-      <c r="B17" s="4">
-        <v>1501</v>
+      <c r="B17" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6">
         <v>352650653.12</v>
@@ -1137,11 +1396,11 @@
       <c r="A18" s="4">
         <v>2022</v>
       </c>
-      <c r="B18" s="4">
-        <v>1511</v>
+      <c r="B18" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D18" s="6">
         <v>3185868726.6500001</v>
@@ -1166,11 +1425,11 @@
       <c r="A19" s="4">
         <v>2022</v>
       </c>
-      <c r="B19" s="4">
-        <v>1521</v>
+      <c r="B19" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D19" s="6">
         <v>55665667.369999997</v>
@@ -1195,11 +1454,11 @@
       <c r="A20" s="4">
         <v>2022</v>
       </c>
-      <c r="B20" s="4">
-        <v>1541</v>
+      <c r="B20" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D20" s="6">
         <v>17601666.309999999</v>
@@ -1224,11 +1483,11 @@
       <c r="A21" s="4">
         <v>2022</v>
       </c>
-      <c r="B21" s="4">
-        <v>1631</v>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D21" s="6">
         <v>63665749.640000001</v>
@@ -1253,11 +1512,11 @@
       <c r="A22" s="4">
         <v>2022</v>
       </c>
-      <c r="B22" s="4">
-        <v>1911</v>
+      <c r="B22" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D22" s="6">
         <v>12201752803.83</v>
@@ -1282,11 +1541,11 @@
       <c r="A23" s="4">
         <v>2022</v>
       </c>
-      <c r="B23" s="4">
-        <v>1915</v>
+      <c r="B23" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D23" s="6">
         <v>1045679146.33</v>
@@ -1311,11 +1570,11 @@
       <c r="A24" s="4">
         <v>2022</v>
       </c>
-      <c r="B24" s="4">
-        <v>1916</v>
+      <c r="B24" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="D24" s="6">
         <v>5700229349.9499998</v>
@@ -1340,11 +1599,11 @@
       <c r="A25" s="4">
         <v>2022</v>
       </c>
-      <c r="B25" s="4">
-        <v>1941</v>
+      <c r="B25" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D25" s="6">
         <v>201288736.28</v>
@@ -1369,11 +1628,11 @@
       <c r="A26" s="4">
         <v>2022</v>
       </c>
-      <c r="B26" s="4">
-        <v>2011</v>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D26" s="6">
         <v>1536739486.1400001</v>
@@ -1398,11 +1657,11 @@
       <c r="A27" s="4">
         <v>2022</v>
       </c>
-      <c r="B27" s="4">
-        <v>2041</v>
+      <c r="B27" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D27" s="6">
         <v>6761105.25</v>
@@ -1427,11 +1686,11 @@
       <c r="A28" s="4">
         <v>2022</v>
       </c>
-      <c r="B28" s="4">
-        <v>2061</v>
+      <c r="B28" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D28" s="6">
         <v>64511960.770000003</v>
@@ -1456,11 +1715,11 @@
       <c r="A29" s="4">
         <v>2022</v>
       </c>
-      <c r="B29" s="4">
-        <v>2071</v>
+      <c r="B29" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D29" s="6">
         <v>455083279.95999998</v>
@@ -1485,11 +1744,11 @@
       <c r="A30" s="4">
         <v>2022</v>
       </c>
-      <c r="B30" s="4">
-        <v>2091</v>
+      <c r="B30" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="D30" s="6">
         <v>41540382.170000002</v>
@@ -1514,11 +1773,11 @@
       <c r="A31" s="4">
         <v>2022</v>
       </c>
-      <c r="B31" s="4">
-        <v>2101</v>
+      <c r="B31" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D31" s="6">
         <v>195536444.94999999</v>
@@ -1543,11 +1802,11 @@
       <c r="A32" s="4">
         <v>2022</v>
       </c>
-      <c r="B32" s="4">
-        <v>2121</v>
+      <c r="B32" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D32" s="6">
         <v>2732447147.5300002</v>
@@ -1572,11 +1831,11 @@
       <c r="A33" s="4">
         <v>2022</v>
       </c>
-      <c r="B33" s="4">
-        <v>2151</v>
+      <c r="B33" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D33" s="6">
         <v>54848300.420000002</v>
@@ -1601,11 +1860,11 @@
       <c r="A34" s="4">
         <v>2022</v>
       </c>
-      <c r="B34" s="4">
-        <v>2161</v>
+      <c r="B34" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="D34" s="6">
         <v>16628991.48</v>
@@ -1630,11 +1889,11 @@
       <c r="A35" s="4">
         <v>2022</v>
       </c>
-      <c r="B35" s="4">
-        <v>2171</v>
+      <c r="B35" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="D35" s="6">
         <v>4662678.05</v>
@@ -1659,11 +1918,11 @@
       <c r="A36" s="4">
         <v>2022</v>
       </c>
-      <c r="B36" s="4">
-        <v>2181</v>
+      <c r="B36" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="D36" s="6">
         <v>44939828.32</v>
@@ -1688,11 +1947,11 @@
       <c r="A37" s="4">
         <v>2022</v>
       </c>
-      <c r="B37" s="4">
-        <v>2201</v>
+      <c r="B37" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D37" s="6">
         <v>24595717.43</v>
@@ -1717,11 +1976,11 @@
       <c r="A38" s="4">
         <v>2022</v>
       </c>
-      <c r="B38" s="4">
-        <v>2211</v>
+      <c r="B38" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="D38" s="6">
         <v>20189976.399999999</v>
@@ -1746,11 +2005,11 @@
       <c r="A39" s="4">
         <v>2022</v>
       </c>
-      <c r="B39" s="4">
-        <v>2241</v>
+      <c r="B39" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="D39" s="6">
         <v>69270924.790000007</v>
@@ -1775,11 +2034,11 @@
       <c r="A40" s="4">
         <v>2022</v>
       </c>
-      <c r="B40" s="4">
-        <v>2251</v>
+      <c r="B40" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="D40" s="6">
         <v>32289616.850000001</v>
@@ -1804,11 +2063,11 @@
       <c r="A41" s="4">
         <v>2022</v>
       </c>
-      <c r="B41" s="4">
-        <v>2261</v>
+      <c r="B41" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="D41" s="6">
         <v>319786910.27999997</v>
@@ -1833,11 +2092,11 @@
       <c r="A42" s="4">
         <v>2022</v>
       </c>
-      <c r="B42" s="4">
-        <v>2271</v>
+      <c r="B42" s="5" t="s">
+        <v>89</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D42" s="6">
         <v>2277629071.1900001</v>
@@ -1862,11 +2121,11 @@
       <c r="A43" s="4">
         <v>2022</v>
       </c>
-      <c r="B43" s="4">
-        <v>2281</v>
+      <c r="B43" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="D43" s="6">
         <v>7453421.7699999996</v>
@@ -1891,11 +2150,11 @@
       <c r="A44" s="4">
         <v>2022</v>
       </c>
-      <c r="B44" s="4">
-        <v>2301</v>
+      <c r="B44" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D44" s="6">
         <v>2009831554.49</v>
@@ -1920,11 +2179,11 @@
       <c r="A45" s="4">
         <v>2022</v>
       </c>
-      <c r="B45" s="4">
-        <v>2311</v>
+      <c r="B45" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D45" s="6">
         <v>434351243.76999998</v>
@@ -1949,11 +2208,11 @@
       <c r="A46" s="4">
         <v>2022</v>
       </c>
-      <c r="B46" s="4">
-        <v>2321</v>
+      <c r="B46" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="D46" s="6">
         <v>333195770.75999999</v>
@@ -1978,11 +2237,11 @@
       <c r="A47" s="4">
         <v>2022</v>
       </c>
-      <c r="B47" s="4">
-        <v>2331</v>
+      <c r="B47" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="D47" s="6">
         <v>26902206.649999999</v>
@@ -2007,11 +2266,11 @@
       <c r="A48" s="4">
         <v>2022</v>
       </c>
-      <c r="B48" s="4">
-        <v>2351</v>
+      <c r="B48" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="D48" s="6">
         <v>464167620.30000001</v>
@@ -2036,11 +2295,11 @@
       <c r="A49" s="4">
         <v>2022</v>
       </c>
-      <c r="B49" s="4">
-        <v>2371</v>
+      <c r="B49" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="D49" s="6">
         <v>265147788.61000001</v>
@@ -2065,11 +2324,11 @@
       <c r="A50" s="4">
         <v>2022</v>
       </c>
-      <c r="B50" s="4">
-        <v>2421</v>
+      <c r="B50" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D50" s="6">
         <v>53060472.469999999</v>
@@ -2094,11 +2353,11 @@
       <c r="A51" s="4">
         <v>2022</v>
       </c>
-      <c r="B51" s="4">
-        <v>2431</v>
+      <c r="B51" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="D51" s="6">
         <v>6030203.9800000004</v>
@@ -2123,11 +2382,11 @@
       <c r="A52" s="4">
         <v>2022</v>
       </c>
-      <c r="B52" s="4">
-        <v>2441</v>
+      <c r="B52" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="D52" s="6">
         <v>15948670.24</v>
@@ -2152,11 +2411,11 @@
       <c r="A53" s="4">
         <v>2022</v>
       </c>
-      <c r="B53" s="4">
-        <v>2461</v>
+      <c r="B53" s="5" t="s">
+        <v>111</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="D53" s="6">
         <v>3998282.31</v>
@@ -2181,11 +2440,11 @@
       <c r="A54" s="4">
         <v>2022</v>
       </c>
-      <c r="B54" s="4">
-        <v>3041</v>
+      <c r="B54" s="5" t="s">
+        <v>113</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D54" s="6">
         <v>368437125.56999999</v>
@@ -2204,11 +2463,11 @@
       <c r="A55" s="4">
         <v>2022</v>
       </c>
-      <c r="B55" s="4">
-        <v>3051</v>
+      <c r="B55" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="D55" s="6">
         <v>119899404.19</v>
@@ -2227,269 +2486,275 @@
       <c r="A56" s="4">
         <v>2022</v>
       </c>
-      <c r="B56" s="4">
-        <v>4091</v>
+      <c r="B56" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
+        <v>118</v>
+      </c>
+      <c r="D56" s="6">
+        <v>17493925.289999999</v>
+      </c>
+      <c r="E56" s="6">
+        <v>16080240.210000001</v>
+      </c>
+      <c r="F56" s="6">
+        <v>16080240.210000001</v>
+      </c>
       <c r="G56" s="6">
         <v>0</v>
       </c>
       <c r="H56" s="6">
-        <v>0</v>
+        <v>517189.73</v>
       </c>
       <c r="I56" s="7">
-        <v>0</v>
+        <v>517189.73</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>2022</v>
       </c>
-      <c r="B57" s="4">
-        <v>4101</v>
+      <c r="B57" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="D57" s="6">
-        <v>17493925.289999999</v>
+        <v>31245732.350000001</v>
       </c>
       <c r="E57" s="6">
-        <v>16080240.210000001</v>
+        <v>13353865.57</v>
       </c>
       <c r="F57" s="6">
-        <v>16080240.210000001</v>
+        <v>13353865.57</v>
       </c>
       <c r="G57" s="6">
-        <v>0</v>
+        <v>1574.5</v>
       </c>
       <c r="H57" s="6">
-        <v>517189.73</v>
+        <v>5560409.71</v>
       </c>
       <c r="I57" s="7">
-        <v>517189.73</v>
+        <v>5561984.21</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>2022</v>
       </c>
-      <c r="B58" s="4">
-        <v>4141</v>
+      <c r="B58" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="D58" s="6">
-        <v>31245732.350000001</v>
+        <v>207531660.90000001</v>
       </c>
       <c r="E58" s="6">
-        <v>13353865.57</v>
+        <v>189241489.69999999</v>
       </c>
       <c r="F58" s="6">
-        <v>13353865.57</v>
+        <v>187462418.97999999</v>
       </c>
       <c r="G58" s="6">
-        <v>1574.5</v>
+        <v>98887758.569999993</v>
       </c>
       <c r="H58" s="6">
-        <v>5560409.71</v>
+        <v>4684458.53</v>
       </c>
       <c r="I58" s="7">
-        <v>5561984.21</v>
+        <v>103572217.09999999</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>2022</v>
       </c>
-      <c r="B59" s="4">
-        <v>4251</v>
+      <c r="B59" s="5" t="s">
+        <v>123</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="D59" s="6">
-        <v>207531660.90000001</v>
+        <v>10255262090.27</v>
       </c>
       <c r="E59" s="6">
-        <v>189241489.69999999</v>
+        <v>9575510065.2199993</v>
       </c>
       <c r="F59" s="6">
-        <v>187462418.97999999</v>
+        <v>9231614379.4599991</v>
       </c>
       <c r="G59" s="6">
-        <v>98887758.569999993</v>
+        <v>554014631.27999997</v>
       </c>
       <c r="H59" s="6">
-        <v>4684458.53</v>
+        <v>786454402.17999995</v>
       </c>
       <c r="I59" s="7">
-        <v>103572217.09999999</v>
+        <v>1340469033.46</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>2022</v>
       </c>
-      <c r="B60" s="4">
-        <v>4291</v>
+      <c r="B60" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="D60" s="6">
-        <v>10255262090.27</v>
+        <v>147406.89000000001</v>
       </c>
       <c r="E60" s="6">
-        <v>9575510065.2199993</v>
+        <v>147406.89000000001</v>
       </c>
       <c r="F60" s="6">
-        <v>9231614379.4599991</v>
-      </c>
-      <c r="G60" s="6">
-        <v>554014631.27999997</v>
-      </c>
-      <c r="H60" s="6">
-        <v>786454402.17999995</v>
-      </c>
-      <c r="I60" s="7">
-        <v>1340469033.46</v>
-      </c>
+        <v>143721.71</v>
+      </c>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="7"/>
     </row>
     <row r="61" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>2022</v>
       </c>
-      <c r="B61" s="4">
-        <v>4331</v>
+      <c r="B61" s="5" t="s">
+        <v>127</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="D61" s="6">
-        <v>147406.89000000001</v>
+        <v>2866852.09</v>
       </c>
       <c r="E61" s="6">
-        <v>147406.89000000001</v>
+        <v>2778584.69</v>
       </c>
       <c r="F61" s="6">
-        <v>143721.71</v>
-      </c>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="7"/>
+        <v>2557135.6800000002</v>
+      </c>
+      <c r="G61" s="6">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6">
+        <v>129135.76</v>
+      </c>
+      <c r="I61" s="7">
+        <v>129135.76</v>
+      </c>
     </row>
     <row r="62" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>2022</v>
       </c>
-      <c r="B62" s="4">
-        <v>4341</v>
+      <c r="B62" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="D62" s="6">
-        <v>2866852.09</v>
+        <v>140227334.65000001</v>
       </c>
       <c r="E62" s="6">
-        <v>2778584.69</v>
+        <v>53251682.009999998</v>
       </c>
       <c r="F62" s="6">
-        <v>2557135.6800000002</v>
+        <v>52665792.689999998</v>
       </c>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" s="6">
-        <v>129135.76</v>
+        <v>5954269.9000000004</v>
       </c>
       <c r="I62" s="7">
-        <v>129135.76</v>
+        <v>5954269.9000000004</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>2022</v>
       </c>
-      <c r="B63" s="4">
-        <v>4381</v>
+      <c r="B63" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="D63" s="6">
-        <v>140227334.65000001</v>
+        <v>11107774.68</v>
       </c>
       <c r="E63" s="6">
-        <v>53251682.009999998</v>
+        <v>10032800.23</v>
       </c>
       <c r="F63" s="6">
-        <v>52665792.689999998</v>
+        <v>9730140.4499999993</v>
       </c>
       <c r="G63" s="6">
         <v>0</v>
       </c>
       <c r="H63" s="6">
-        <v>5954269.9000000004</v>
+        <v>2888273.21</v>
       </c>
       <c r="I63" s="7">
-        <v>5954269.9000000004</v>
+        <v>2888273.21</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>2022</v>
       </c>
-      <c r="B64" s="4">
-        <v>4451</v>
+      <c r="B64" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D64" s="6">
-        <v>11107774.68</v>
+        <v>12198756.32</v>
       </c>
       <c r="E64" s="6">
-        <v>10032800.23</v>
+        <v>12198756.32</v>
       </c>
       <c r="F64" s="6">
-        <v>9730140.4499999993</v>
+        <v>9336561.1600000001</v>
       </c>
       <c r="G64" s="6">
         <v>0</v>
       </c>
       <c r="H64" s="6">
-        <v>2888273.21</v>
+        <v>0</v>
       </c>
       <c r="I64" s="7">
-        <v>2888273.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>2022</v>
       </c>
-      <c r="B65" s="4">
-        <v>4491</v>
+      <c r="B65" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="D65" s="6">
-        <v>12198756.32</v>
+        <v>315895.03000000003</v>
       </c>
       <c r="E65" s="6">
-        <v>12198756.32</v>
+        <v>315480.44</v>
       </c>
       <c r="F65" s="6">
-        <v>9336561.1600000001</v>
+        <v>315480.44</v>
       </c>
       <c r="G65" s="6">
         <v>0</v>
@@ -2505,177 +2770,148 @@
       <c r="A66" s="4">
         <v>2022</v>
       </c>
-      <c r="B66" s="4">
-        <v>4541</v>
+      <c r="B66" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="D66" s="6">
-        <v>315895.03000000003</v>
+        <v>161975565.86000001</v>
       </c>
       <c r="E66" s="6">
-        <v>315480.44</v>
+        <v>161973985.31</v>
       </c>
       <c r="F66" s="6">
-        <v>315480.44</v>
+        <v>155079704.44999999</v>
       </c>
       <c r="G66" s="6">
-        <v>0</v>
+        <v>12273523.84</v>
       </c>
       <c r="H66" s="6">
         <v>0</v>
       </c>
       <c r="I66" s="7">
-        <v>0</v>
+        <v>12273523.84</v>
       </c>
     </row>
     <row r="67" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>2022</v>
       </c>
-      <c r="B67" s="4">
-        <v>4551</v>
+      <c r="B67" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="D67" s="6">
-        <v>161975565.86000001</v>
+        <v>464551.64</v>
       </c>
       <c r="E67" s="6">
-        <v>161973985.31</v>
+        <v>419551.64</v>
       </c>
       <c r="F67" s="6">
-        <v>155079704.44999999</v>
+        <v>239551.64</v>
       </c>
       <c r="G67" s="6">
-        <v>12273523.84</v>
+        <v>80000</v>
       </c>
       <c r="H67" s="6">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I67" s="7">
-        <v>12273523.84</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="68" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>2022</v>
       </c>
-      <c r="B68" s="4">
-        <v>4601</v>
+      <c r="B68" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D68" s="6">
-        <v>464551.64</v>
+        <v>25338987.879999999</v>
       </c>
       <c r="E68" s="6">
-        <v>419551.64</v>
+        <v>11474135.710000001</v>
       </c>
       <c r="F68" s="6">
-        <v>239551.64</v>
+        <v>9347783.0199999996</v>
       </c>
       <c r="G68" s="6">
-        <v>80000</v>
+        <v>1094891.98</v>
       </c>
       <c r="H68" s="6">
-        <v>80000</v>
+        <v>4039900.86</v>
       </c>
       <c r="I68" s="7">
-        <v>160000</v>
+        <v>5134792.84</v>
       </c>
     </row>
     <row r="69" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>2022</v>
       </c>
-      <c r="B69" s="4">
-        <v>4691</v>
+      <c r="B69" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="D69" s="6">
-        <v>25338987.879999999</v>
+        <v>3542540.26</v>
       </c>
       <c r="E69" s="6">
-        <v>11474135.710000001</v>
+        <v>4264.26</v>
       </c>
       <c r="F69" s="6">
-        <v>9347783.0199999996</v>
+        <v>0</v>
       </c>
       <c r="G69" s="6">
-        <v>1094891.98</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6">
-        <v>4039900.86</v>
+        <v>0</v>
       </c>
       <c r="I69" s="7">
-        <v>5134792.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>2022</v>
       </c>
-      <c r="B70" s="4">
-        <v>4701</v>
+      <c r="B70" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="D70" s="6">
-        <v>3542540.26</v>
+        <v>15325406751.49</v>
       </c>
       <c r="E70" s="6">
-        <v>4264.26</v>
+        <v>15323499427.6</v>
       </c>
       <c r="F70" s="6">
-        <v>0</v>
+        <v>15328734230.09</v>
       </c>
       <c r="G70" s="6">
         <v>0</v>
       </c>
       <c r="H70" s="6">
-        <v>0</v>
+        <v>79198.5</v>
       </c>
       <c r="I70" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" s="1" customFormat="1" ht="19.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B71" s="4">
-        <v>4711</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D71" s="6">
-        <v>15325406751.49</v>
-      </c>
-      <c r="E71" s="6">
-        <v>15323499427.6</v>
-      </c>
-      <c r="F71" s="6">
-        <v>15328734230.09</v>
-      </c>
-      <c r="G71" s="6">
-        <v>0</v>
-      </c>
-      <c r="H71" s="6">
         <v>79198.5</v>
       </c>
-      <c r="I71" s="7">
-        <v>79198.5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="71" spans="1:9" s="1" customFormat="1" ht="28.7" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,25 +840,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3051</v>
+        <v>3151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>119899404.19</v>
+        <v>15789557.36</v>
       </c>
       <c r="F12" t="n">
-        <v>119899404.19</v>
+        <v>15789557.36</v>
       </c>
       <c r="G12" t="n">
-        <v>119899404.19</v>
+        <v>15789557.36</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -870,35 +870,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>17601666.31</v>
+        <v>119899404.19</v>
       </c>
       <c r="F13" t="n">
-        <v>17148601.56</v>
+        <v>119899404.19</v>
       </c>
       <c r="G13" t="n">
-        <v>16887894.92</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>256633.48</v>
-      </c>
-      <c r="J13" t="n">
-        <v>256633.48</v>
-      </c>
+        <v>119899404.19</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -906,34 +900,34 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>315895.03</v>
+        <v>17601666.31</v>
       </c>
       <c r="F14" t="n">
-        <v>315480.44</v>
+        <v>17148601.56</v>
       </c>
       <c r="G14" t="n">
-        <v>315480.44</v>
+        <v>16887894.92</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>256633.48</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>256633.48</v>
       </c>
     </row>
     <row r="15">
@@ -942,34 +936,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4662678.05</v>
+        <v>315895.03</v>
       </c>
       <c r="F15" t="n">
-        <v>4296034.19</v>
+        <v>315480.44</v>
       </c>
       <c r="G15" t="n">
-        <v>4144793.59</v>
+        <v>315480.44</v>
       </c>
       <c r="H15" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>13446.09</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>13513.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -978,34 +972,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>455083279.96</v>
+        <v>4662678.05</v>
       </c>
       <c r="F16" t="n">
-        <v>442616854.91</v>
+        <v>4296034.19</v>
       </c>
       <c r="G16" t="n">
-        <v>429159889.95</v>
+        <v>4144793.59</v>
       </c>
       <c r="H16" t="n">
-        <v>50484697.07</v>
+        <v>67.5</v>
       </c>
       <c r="I16" t="n">
-        <v>12791969.37</v>
+        <v>13446.09</v>
       </c>
       <c r="J16" t="n">
-        <v>63276666.44</v>
+        <v>13513.59</v>
       </c>
     </row>
     <row r="17">
@@ -1014,34 +1008,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44939828.32</v>
+        <v>455083279.96</v>
       </c>
       <c r="F17" t="n">
-        <v>43912375.76</v>
+        <v>442616854.91</v>
       </c>
       <c r="G17" t="n">
-        <v>43171411.16</v>
+        <v>429159889.95</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>50484697.07</v>
       </c>
       <c r="I17" t="n">
-        <v>418535.58</v>
+        <v>12791969.37</v>
       </c>
       <c r="J17" t="n">
-        <v>418535.58</v>
+        <v>63276666.44</v>
       </c>
     </row>
     <row r="18">
@@ -1050,29 +1044,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>147406.89</v>
+        <v>44939828.32</v>
       </c>
       <c r="F18" t="n">
-        <v>147406.89</v>
+        <v>43912375.76</v>
       </c>
       <c r="G18" t="n">
-        <v>143721.71</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+        <v>43171411.16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>418535.58</v>
+      </c>
+      <c r="J18" t="n">
+        <v>418535.58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1080,35 +1080,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>41540382.17</v>
+        <v>147406.89</v>
       </c>
       <c r="F19" t="n">
-        <v>41283632.97</v>
+        <v>147406.89</v>
       </c>
       <c r="G19" t="n">
-        <v>40766476.92</v>
-      </c>
-      <c r="H19" t="n">
-        <v>27692.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11647.71</v>
-      </c>
-      <c r="J19" t="n">
-        <v>39340.21</v>
-      </c>
+        <v>143721.71</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1116,34 +1110,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>207531660.9</v>
+        <v>41540382.17</v>
       </c>
       <c r="F20" t="n">
-        <v>189241489.7</v>
+        <v>41283632.97</v>
       </c>
       <c r="G20" t="n">
-        <v>187462418.98</v>
+        <v>40766476.92</v>
       </c>
       <c r="H20" t="n">
-        <v>98887758.56999999</v>
+        <v>27692.5</v>
       </c>
       <c r="I20" t="n">
-        <v>4684458.53</v>
+        <v>11647.71</v>
       </c>
       <c r="J20" t="n">
-        <v>103572217.1</v>
+        <v>39340.21</v>
       </c>
     </row>
     <row r="21">
@@ -1152,34 +1146,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12198756.32</v>
+        <v>207531660.9</v>
       </c>
       <c r="F21" t="n">
-        <v>12198756.32</v>
+        <v>189241489.7</v>
       </c>
       <c r="G21" t="n">
-        <v>9336561.16</v>
+        <v>187462418.98</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>98887758.56999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4684458.53</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>103572217.1</v>
       </c>
     </row>
     <row r="22">
@@ -1188,34 +1182,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17493925.29</v>
+        <v>12198756.32</v>
       </c>
       <c r="F22" t="n">
-        <v>16080240.21</v>
+        <v>12198756.32</v>
       </c>
       <c r="G22" t="n">
-        <v>16080240.21</v>
+        <v>9336561.16</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>517189.73</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>517189.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1224,34 +1218,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>464551.64</v>
+        <v>17493925.29</v>
       </c>
       <c r="F23" t="n">
-        <v>419551.64</v>
+        <v>16080240.21</v>
       </c>
       <c r="G23" t="n">
-        <v>239551.64</v>
+        <v>16080240.21</v>
       </c>
       <c r="H23" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>80000</v>
+        <v>517189.73</v>
       </c>
       <c r="J23" t="n">
-        <v>160000</v>
+        <v>517189.73</v>
       </c>
     </row>
     <row r="24">
@@ -1260,34 +1254,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11107774.68</v>
+        <v>464551.64</v>
       </c>
       <c r="F24" t="n">
-        <v>10032800.23</v>
+        <v>419551.64</v>
       </c>
       <c r="G24" t="n">
-        <v>9730140.449999999</v>
+        <v>239551.64</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I24" t="n">
-        <v>2888273.21</v>
+        <v>80000</v>
       </c>
       <c r="J24" t="n">
-        <v>2888273.21</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="25">
@@ -1620,34 +1614,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2161</v>
+        <v>4631</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>16628991.48</v>
+        <v>386159674.85</v>
       </c>
       <c r="F34" t="n">
-        <v>15101587.53</v>
+        <v>248996997.66</v>
       </c>
       <c r="G34" t="n">
-        <v>14946425.03</v>
+        <v>238193664.04</v>
       </c>
       <c r="H34" t="n">
-        <v>15535.07</v>
+        <v>275729.74</v>
       </c>
       <c r="I34" t="n">
-        <v>2608678.68</v>
+        <v>15778864.88</v>
       </c>
       <c r="J34" t="n">
-        <v>2624213.75</v>
+        <v>16054594.62</v>
       </c>
     </row>
     <row r="35">
@@ -1656,34 +1650,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4551</v>
+        <v>2161</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>161975565.86</v>
+        <v>16628991.48</v>
       </c>
       <c r="F35" t="n">
-        <v>161973985.31</v>
+        <v>15101587.53</v>
       </c>
       <c r="G35" t="n">
-        <v>155079704.45</v>
+        <v>14946425.03</v>
       </c>
       <c r="H35" t="n">
-        <v>12273523.84</v>
+        <v>15535.07</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2608678.68</v>
       </c>
       <c r="J35" t="n">
-        <v>12273523.84</v>
+        <v>2624213.75</v>
       </c>
     </row>
     <row r="36">
@@ -1692,34 +1686,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2261</v>
+        <v>4551</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>319786910.28</v>
+        <v>161975565.86</v>
       </c>
       <c r="F36" t="n">
-        <v>263858227.88</v>
+        <v>161973985.31</v>
       </c>
       <c r="G36" t="n">
-        <v>252638336.78</v>
+        <v>155079704.45</v>
       </c>
       <c r="H36" t="n">
-        <v>101930917.99</v>
+        <v>12273523.84</v>
       </c>
       <c r="I36" t="n">
-        <v>47063914.03</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>148994832.02</v>
+        <v>12273523.84</v>
       </c>
     </row>
     <row r="37">
@@ -1728,34 +1722,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4381</v>
+        <v>4421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>140227334.65</v>
+        <v>1278479.27</v>
       </c>
       <c r="F37" t="n">
-        <v>53251682.01</v>
+        <v>1278479.27</v>
       </c>
       <c r="G37" t="n">
-        <v>52665792.69</v>
+        <v>1278479.27</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5954269.9</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>5954269.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1764,34 +1758,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1071</v>
+        <v>2261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>41468457.48</v>
+        <v>319786910.28</v>
       </c>
       <c r="F38" t="n">
-        <v>36393685.24</v>
+        <v>263858227.88</v>
       </c>
       <c r="G38" t="n">
-        <v>35762406.77</v>
+        <v>252638336.78</v>
       </c>
       <c r="H38" t="n">
-        <v>4065417.18</v>
+        <v>101930917.99</v>
       </c>
       <c r="I38" t="n">
-        <v>2244249.52</v>
+        <v>47063914.03</v>
       </c>
       <c r="J38" t="n">
-        <v>6309666.7</v>
+        <v>148994832.02</v>
       </c>
     </row>
     <row r="39">
@@ -1800,34 +1794,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1916</v>
+        <v>4381</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5700229349.95</v>
+        <v>140227334.65</v>
       </c>
       <c r="F39" t="n">
-        <v>5577199638.67</v>
+        <v>53251682.01</v>
       </c>
       <c r="G39" t="n">
-        <v>5517860023.27</v>
+        <v>52665792.69</v>
       </c>
       <c r="H39" t="n">
-        <v>28843343.77</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>5954269.9</v>
       </c>
       <c r="J39" t="n">
-        <v>28843343.77</v>
+        <v>5954269.9</v>
       </c>
     </row>
     <row r="40">
@@ -1836,34 +1830,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2321</v>
+        <v>1071</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>333195770.76</v>
+        <v>41468457.48</v>
       </c>
       <c r="F40" t="n">
-        <v>296763683.46</v>
+        <v>36393685.24</v>
       </c>
       <c r="G40" t="n">
-        <v>290862823.02</v>
+        <v>35762406.77</v>
       </c>
       <c r="H40" t="n">
-        <v>255386.81</v>
+        <v>4065417.18</v>
       </c>
       <c r="I40" t="n">
-        <v>25746888.77</v>
+        <v>2244249.52</v>
       </c>
       <c r="J40" t="n">
-        <v>26002275.58</v>
+        <v>6309666.7</v>
       </c>
     </row>
     <row r="41">
@@ -1872,34 +1866,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2421</v>
+        <v>1916</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53060472.47</v>
+        <v>5700229349.95</v>
       </c>
       <c r="F41" t="n">
-        <v>46263655.96</v>
+        <v>5577199638.67</v>
       </c>
       <c r="G41" t="n">
-        <v>45692556.63</v>
+        <v>5517860023.27</v>
       </c>
       <c r="H41" t="n">
-        <v>976681.46</v>
+        <v>28843343.77</v>
       </c>
       <c r="I41" t="n">
-        <v>14019630.84</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>14996312.3</v>
+        <v>28843343.77</v>
       </c>
     </row>
     <row r="42">
@@ -1908,34 +1902,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2101</v>
+        <v>2321</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>195536444.95</v>
+        <v>333195770.76</v>
       </c>
       <c r="F42" t="n">
-        <v>190876690.89</v>
+        <v>296763683.46</v>
       </c>
       <c r="G42" t="n">
-        <v>183865965.58</v>
+        <v>290862823.02</v>
       </c>
       <c r="H42" t="n">
-        <v>1981216.45</v>
+        <v>255386.81</v>
       </c>
       <c r="I42" t="n">
-        <v>3389073.5</v>
+        <v>25746888.77</v>
       </c>
       <c r="J42" t="n">
-        <v>5370289.95</v>
+        <v>26002275.58</v>
       </c>
     </row>
     <row r="43">
@@ -1944,34 +1938,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2201</v>
+        <v>2421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>24595717.43</v>
+        <v>53060472.47</v>
       </c>
       <c r="F43" t="n">
-        <v>20047336.04</v>
+        <v>46263655.96</v>
       </c>
       <c r="G43" t="n">
-        <v>19187028.92</v>
+        <v>45692556.63</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>976681.46</v>
       </c>
       <c r="I43" t="n">
-        <v>934662.77</v>
+        <v>14019630.84</v>
       </c>
       <c r="J43" t="n">
-        <v>934662.77</v>
+        <v>14996312.3</v>
       </c>
     </row>
     <row r="44">
@@ -1980,34 +1974,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2241</v>
+        <v>2101</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>69270924.79000001</v>
+        <v>195536444.95</v>
       </c>
       <c r="F44" t="n">
-        <v>64810240.33</v>
+        <v>190876690.89</v>
       </c>
       <c r="G44" t="n">
-        <v>64595191.74</v>
+        <v>183865965.58</v>
       </c>
       <c r="H44" t="n">
-        <v>10437314.16</v>
+        <v>1981216.45</v>
       </c>
       <c r="I44" t="n">
-        <v>1573915.38</v>
+        <v>3389073.5</v>
       </c>
       <c r="J44" t="n">
-        <v>12011229.54</v>
+        <v>5370289.95</v>
       </c>
     </row>
     <row r="45">
@@ -2016,34 +2010,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2371</v>
+        <v>2201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>265147788.61</v>
+        <v>24595717.43</v>
       </c>
       <c r="F45" t="n">
-        <v>260504964.97</v>
+        <v>20047336.04</v>
       </c>
       <c r="G45" t="n">
-        <v>260025427.44</v>
+        <v>19187028.92</v>
       </c>
       <c r="H45" t="n">
-        <v>11259.94</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>7021591.43</v>
+        <v>934662.77</v>
       </c>
       <c r="J45" t="n">
-        <v>7032851.37</v>
+        <v>934662.77</v>
       </c>
     </row>
     <row r="46">
@@ -2052,34 +2046,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2331</v>
+        <v>2241</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>26902206.65</v>
+        <v>69270924.79000001</v>
       </c>
       <c r="F46" t="n">
-        <v>26685069.71</v>
+        <v>64810240.33</v>
       </c>
       <c r="G46" t="n">
-        <v>26064598.71</v>
+        <v>64595191.74</v>
       </c>
       <c r="H46" t="n">
-        <v>333694.72</v>
+        <v>10437314.16</v>
       </c>
       <c r="I46" t="n">
-        <v>520848.74</v>
+        <v>1573915.38</v>
       </c>
       <c r="J46" t="n">
-        <v>854543.46</v>
+        <v>12011229.54</v>
       </c>
     </row>
     <row r="47">
@@ -2088,34 +2082,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2011</v>
+        <v>2371</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1536739486.14</v>
+        <v>265147788.61</v>
       </c>
       <c r="F47" t="n">
-        <v>1341247986.54</v>
+        <v>260504964.97</v>
       </c>
       <c r="G47" t="n">
-        <v>1307994655.9</v>
+        <v>260025427.44</v>
       </c>
       <c r="H47" t="n">
-        <v>423878.41</v>
+        <v>11259.94</v>
       </c>
       <c r="I47" t="n">
-        <v>127022888.49</v>
+        <v>7021591.43</v>
       </c>
       <c r="J47" t="n">
-        <v>127446766.9</v>
+        <v>7032851.37</v>
       </c>
     </row>
     <row r="48">
@@ -2124,34 +2118,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2121</v>
+        <v>2331</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2732447147.53</v>
+        <v>26902206.65</v>
       </c>
       <c r="F48" t="n">
-        <v>2675654178.82</v>
+        <v>26685069.71</v>
       </c>
       <c r="G48" t="n">
-        <v>2000806584.11</v>
+        <v>26064598.71</v>
       </c>
       <c r="H48" t="n">
-        <v>94866365.34999999</v>
+        <v>333694.72</v>
       </c>
       <c r="I48" t="n">
-        <v>67386629.63</v>
+        <v>520848.74</v>
       </c>
       <c r="J48" t="n">
-        <v>162252994.98</v>
+        <v>854543.46</v>
       </c>
     </row>
     <row r="49">
@@ -2160,34 +2154,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2251</v>
+        <v>2011</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>32289616.85</v>
+        <v>1536739486.14</v>
       </c>
       <c r="F49" t="n">
-        <v>30153432.18</v>
+        <v>1341247986.54</v>
       </c>
       <c r="G49" t="n">
-        <v>29578426.34</v>
+        <v>1307994655.9</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>423878.41</v>
       </c>
       <c r="I49" t="n">
-        <v>671682.59</v>
+        <v>127022888.49</v>
       </c>
       <c r="J49" t="n">
-        <v>671682.59</v>
+        <v>127446766.9</v>
       </c>
     </row>
     <row r="50">
@@ -2196,34 +2190,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2041</v>
+        <v>2121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6761105.25</v>
+        <v>2732447147.53</v>
       </c>
       <c r="F50" t="n">
-        <v>5938379.6</v>
+        <v>2675654178.82</v>
       </c>
       <c r="G50" t="n">
-        <v>5925515.6</v>
+        <v>2000806584.11</v>
       </c>
       <c r="H50" t="n">
-        <v>4598.79</v>
+        <v>94866365.34999999</v>
       </c>
       <c r="I50" t="n">
-        <v>1296981.73</v>
+        <v>67386629.63</v>
       </c>
       <c r="J50" t="n">
-        <v>1301580.52</v>
+        <v>162252994.98</v>
       </c>
     </row>
     <row r="51">
@@ -2232,34 +2226,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1101</v>
+        <v>2251</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>12148887.19</v>
+        <v>32289616.85</v>
       </c>
       <c r="F51" t="n">
-        <v>11844528.2</v>
+        <v>30153432.18</v>
       </c>
       <c r="G51" t="n">
-        <v>11757162.48</v>
+        <v>29578426.34</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>36247.74</v>
+        <v>671682.59</v>
       </c>
       <c r="J51" t="n">
-        <v>36247.74</v>
+        <v>671682.59</v>
       </c>
     </row>
     <row r="52">
@@ -2268,34 +2262,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1915</v>
+        <v>2041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1045679146.33</v>
+        <v>6761105.25</v>
       </c>
       <c r="F52" t="n">
-        <v>525455877.98</v>
+        <v>5938379.6</v>
       </c>
       <c r="G52" t="n">
-        <v>525455877.98</v>
+        <v>5925515.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>4598.79</v>
       </c>
       <c r="I52" t="n">
-        <v>28198078.12</v>
+        <v>1296981.73</v>
       </c>
       <c r="J52" t="n">
-        <v>28198078.12</v>
+        <v>1301580.52</v>
       </c>
     </row>
     <row r="53">
@@ -2304,35 +2298,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>MG INVESTE</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1511</v>
+        <v>4621</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3185868726.65</v>
+        <v>88898823.3</v>
       </c>
       <c r="F53" t="n">
-        <v>3092549019.47</v>
+        <v>88898823.3</v>
       </c>
       <c r="G53" t="n">
-        <v>3072423500.15</v>
-      </c>
-      <c r="H53" t="n">
-        <v>18094662.5</v>
-      </c>
-      <c r="I53" t="n">
-        <v>61379561.55</v>
-      </c>
-      <c r="J53" t="n">
-        <v>79474224.05</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2340,34 +2328,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1251</v>
+        <v>1101</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12979474804.25</v>
+        <v>12148887.19</v>
       </c>
       <c r="F54" t="n">
-        <v>12773110420.68</v>
+        <v>11844528.2</v>
       </c>
       <c r="G54" t="n">
-        <v>12732571407.31</v>
+        <v>11757162.48</v>
       </c>
       <c r="H54" t="n">
-        <v>41558515.4</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>216807656.75</v>
+        <v>36247.74</v>
       </c>
       <c r="J54" t="n">
-        <v>258366172.15</v>
+        <v>36247.74</v>
       </c>
     </row>
     <row r="55">
@@ -2376,34 +2364,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1231</v>
+        <v>1915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>196292319.51</v>
+        <v>1045679146.33</v>
       </c>
       <c r="F55" t="n">
-        <v>192693183.61</v>
+        <v>525455877.98</v>
       </c>
       <c r="G55" t="n">
-        <v>183911092.06</v>
+        <v>525455877.98</v>
       </c>
       <c r="H55" t="n">
-        <v>926349.9300000001</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>4138969.75</v>
+        <v>28198078.12</v>
       </c>
       <c r="J55" t="n">
-        <v>5065319.68</v>
+        <v>28198078.12</v>
       </c>
     </row>
     <row r="56">
@@ -2412,34 +2400,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1631</v>
+        <v>1511</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>63665749.64</v>
+        <v>3185868726.65</v>
       </c>
       <c r="F56" t="n">
-        <v>39924754.94</v>
+        <v>3092549019.47</v>
       </c>
       <c r="G56" t="n">
-        <v>39409640.61</v>
+        <v>3072423500.15</v>
       </c>
       <c r="H56" t="n">
-        <v>475922.2</v>
+        <v>18094662.5</v>
       </c>
       <c r="I56" t="n">
-        <v>24058202.1</v>
+        <v>61379561.55</v>
       </c>
       <c r="J56" t="n">
-        <v>24534124.3</v>
+        <v>79474224.05</v>
       </c>
     </row>
     <row r="57">
@@ -2448,34 +2436,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1271</v>
+        <v>1251</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>71925491.40000001</v>
+        <v>12979474804.25</v>
       </c>
       <c r="F57" t="n">
-        <v>70589799.61</v>
+        <v>12773110420.68</v>
       </c>
       <c r="G57" t="n">
-        <v>69678332.78</v>
+        <v>12732571407.31</v>
       </c>
       <c r="H57" t="n">
-        <v>20181416.68</v>
+        <v>41558515.4</v>
       </c>
       <c r="I57" t="n">
-        <v>10134142.55</v>
+        <v>216807656.75</v>
       </c>
       <c r="J57" t="n">
-        <v>30315559.23</v>
+        <v>258366172.15</v>
       </c>
     </row>
     <row r="58">
@@ -2484,34 +2472,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1221</v>
+        <v>1231</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>91983736.40000001</v>
+        <v>196292319.51</v>
       </c>
       <c r="F58" t="n">
-        <v>76448925.22</v>
+        <v>192693183.61</v>
       </c>
       <c r="G58" t="n">
-        <v>75856018.97</v>
+        <v>183911092.06</v>
       </c>
       <c r="H58" t="n">
-        <v>467.76</v>
+        <v>926349.9300000001</v>
       </c>
       <c r="I58" t="n">
-        <v>10588548.64</v>
+        <v>4138969.75</v>
       </c>
       <c r="J58" t="n">
-        <v>10589016.4</v>
+        <v>5065319.68</v>
       </c>
     </row>
     <row r="59">
@@ -2520,34 +2508,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1481</v>
+        <v>1631</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>152723547.84</v>
+        <v>63665749.64</v>
       </c>
       <c r="F59" t="n">
-        <v>140202461.6</v>
+        <v>39924754.94</v>
       </c>
       <c r="G59" t="n">
-        <v>128851499.22</v>
+        <v>39409640.61</v>
       </c>
       <c r="H59" t="n">
-        <v>5411868.7</v>
+        <v>475922.2</v>
       </c>
       <c r="I59" t="n">
-        <v>11509155.9</v>
+        <v>24058202.1</v>
       </c>
       <c r="J59" t="n">
-        <v>16921024.6</v>
+        <v>24534124.3</v>
       </c>
     </row>
     <row r="60">
@@ -2556,34 +2544,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1261</v>
+        <v>1271</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>16633018692.76</v>
+        <v>71925491.40000001</v>
       </c>
       <c r="F60" t="n">
-        <v>16079912253.18</v>
+        <v>70589799.61</v>
       </c>
       <c r="G60" t="n">
-        <v>15837680952.16</v>
+        <v>69678332.78</v>
       </c>
       <c r="H60" t="n">
-        <v>585170446.71</v>
+        <v>20181416.68</v>
       </c>
       <c r="I60" t="n">
-        <v>757153016.96</v>
+        <v>10134142.55</v>
       </c>
       <c r="J60" t="n">
-        <v>1342323463.67</v>
+        <v>30315559.23</v>
       </c>
     </row>
     <row r="61">
@@ -2592,34 +2580,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1191</v>
+        <v>1221</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1539130234.2</v>
+        <v>91983736.40000001</v>
       </c>
       <c r="F61" t="n">
-        <v>1488234890.69</v>
+        <v>76448925.22</v>
       </c>
       <c r="G61" t="n">
-        <v>1475159288.69</v>
+        <v>75856018.97</v>
       </c>
       <c r="H61" t="n">
-        <v>10728442.75</v>
+        <v>467.76</v>
       </c>
       <c r="I61" t="n">
-        <v>69971290.95999999</v>
+        <v>10588548.64</v>
       </c>
       <c r="J61" t="n">
-        <v>80699733.70999999</v>
+        <v>10589016.4</v>
       </c>
     </row>
     <row r="62">
@@ -2628,34 +2616,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1491</v>
+        <v>1481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1612507669.42</v>
+        <v>152723547.84</v>
       </c>
       <c r="F62" t="n">
-        <v>1582583713.78</v>
+        <v>140202461.6</v>
       </c>
       <c r="G62" t="n">
-        <v>1572502930.45</v>
+        <v>128851499.22</v>
       </c>
       <c r="H62" t="n">
-        <v>1541639.23</v>
+        <v>5411868.7</v>
       </c>
       <c r="I62" t="n">
-        <v>16627368.43</v>
+        <v>11509155.9</v>
       </c>
       <c r="J62" t="n">
-        <v>18169007.66</v>
+        <v>16921024.6</v>
       </c>
     </row>
     <row r="63">
@@ -2664,34 +2652,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1301</v>
+        <v>1261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>600547625.35</v>
+        <v>16633018692.76</v>
       </c>
       <c r="F63" t="n">
-        <v>522164709.56</v>
+        <v>16079912253.18</v>
       </c>
       <c r="G63" t="n">
-        <v>444238275.33</v>
+        <v>15837680952.16</v>
       </c>
       <c r="H63" t="n">
-        <v>18353119.53</v>
+        <v>585170446.71</v>
       </c>
       <c r="I63" t="n">
-        <v>36819044.67</v>
+        <v>757153016.96</v>
       </c>
       <c r="J63" t="n">
-        <v>55172164.2</v>
+        <v>1342323463.67</v>
       </c>
     </row>
     <row r="64">
@@ -2700,34 +2688,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1451</v>
+        <v>1191</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3393511812.13</v>
+        <v>1539130234.2</v>
       </c>
       <c r="F64" t="n">
-        <v>3264360914.02</v>
+        <v>1488234890.69</v>
       </c>
       <c r="G64" t="n">
-        <v>3238880805.17</v>
+        <v>1475159288.69</v>
       </c>
       <c r="H64" t="n">
-        <v>13141756.77</v>
+        <v>10728442.75</v>
       </c>
       <c r="I64" t="n">
-        <v>89952770.89</v>
+        <v>69971290.95999999</v>
       </c>
       <c r="J64" t="n">
-        <v>103094527.66</v>
+        <v>80699733.70999999</v>
       </c>
     </row>
     <row r="65">
@@ -2736,34 +2724,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1371</v>
+        <v>1491</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>181795255.1</v>
+        <v>1612507669.42</v>
       </c>
       <c r="F65" t="n">
-        <v>176679835.12</v>
+        <v>1582583713.78</v>
       </c>
       <c r="G65" t="n">
-        <v>172435676.13</v>
+        <v>1572502930.45</v>
       </c>
       <c r="H65" t="n">
-        <v>4368130.43</v>
+        <v>1541639.23</v>
       </c>
       <c r="I65" t="n">
-        <v>4287377.26</v>
+        <v>16627368.43</v>
       </c>
       <c r="J65" t="n">
-        <v>8655507.689999999</v>
+        <v>18169007.66</v>
       </c>
     </row>
     <row r="66">
@@ -2772,34 +2760,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1501</v>
+        <v>1301</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>352650653.12</v>
+        <v>600547625.35</v>
       </c>
       <c r="F66" t="n">
-        <v>315037665.91</v>
+        <v>522164709.56</v>
       </c>
       <c r="G66" t="n">
-        <v>301346762.92</v>
+        <v>444238275.33</v>
       </c>
       <c r="H66" t="n">
-        <v>19114485.82</v>
+        <v>18353119.53</v>
       </c>
       <c r="I66" t="n">
-        <v>77403990.66</v>
+        <v>36819044.67</v>
       </c>
       <c r="J66" t="n">
-        <v>96518476.48</v>
+        <v>55172164.2</v>
       </c>
     </row>
     <row r="67">
@@ -2808,34 +2796,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2211</v>
+        <v>1451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>20189976.4</v>
+        <v>3393511812.13</v>
       </c>
       <c r="F67" t="n">
-        <v>19470842.74</v>
+        <v>3264360914.02</v>
       </c>
       <c r="G67" t="n">
-        <v>18947352.89</v>
+        <v>3238880805.17</v>
       </c>
       <c r="H67" t="n">
-        <v>140686.89</v>
+        <v>13141756.77</v>
       </c>
       <c r="I67" t="n">
-        <v>756689.71</v>
+        <v>89952770.89</v>
       </c>
       <c r="J67" t="n">
-        <v>897376.6</v>
+        <v>103094527.66</v>
       </c>
     </row>
     <row r="68">
@@ -2844,34 +2832,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2351</v>
+        <v>1371</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>464167620.3</v>
+        <v>181795255.1</v>
       </c>
       <c r="F68" t="n">
-        <v>430024005.97</v>
+        <v>176679835.12</v>
       </c>
       <c r="G68" t="n">
-        <v>419107102.61</v>
+        <v>172435676.13</v>
       </c>
       <c r="H68" t="n">
-        <v>380901.69</v>
+        <v>4368130.43</v>
       </c>
       <c r="I68" t="n">
-        <v>13513330.29</v>
+        <v>4287377.26</v>
       </c>
       <c r="J68" t="n">
-        <v>13894231.98</v>
+        <v>8655507.689999999</v>
       </c>
     </row>
     <row r="69">
@@ -2880,34 +2868,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2311</v>
+        <v>1501</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>434351243.77</v>
+        <v>352650653.12</v>
       </c>
       <c r="F69" t="n">
-        <v>412467573.12</v>
+        <v>315037665.91</v>
       </c>
       <c r="G69" t="n">
-        <v>403987795.94</v>
+        <v>301346762.92</v>
       </c>
       <c r="H69" t="n">
-        <v>1669347.22</v>
+        <v>19114485.82</v>
       </c>
       <c r="I69" t="n">
-        <v>67683789.95999999</v>
+        <v>77403990.66</v>
       </c>
       <c r="J69" t="n">
-        <v>69353137.18000001</v>
+        <v>96518476.48</v>
       </c>
     </row>
     <row r="70">
@@ -2916,33 +2904,141 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>TV MINAS</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2211</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>20189976.4</v>
+      </c>
+      <c r="F70" t="n">
+        <v>19470842.74</v>
+      </c>
+      <c r="G70" t="n">
+        <v>18947352.89</v>
+      </c>
+      <c r="H70" t="n">
+        <v>140686.89</v>
+      </c>
+      <c r="I70" t="n">
+        <v>756689.71</v>
+      </c>
+      <c r="J70" t="n">
+        <v>897376.6</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>464167620.3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>430024005.97</v>
+      </c>
+      <c r="G71" t="n">
+        <v>419107102.61</v>
+      </c>
+      <c r="H71" t="n">
+        <v>380901.69</v>
+      </c>
+      <c r="I71" t="n">
+        <v>13513330.29</v>
+      </c>
+      <c r="J71" t="n">
+        <v>13894231.98</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>434351243.77</v>
+      </c>
+      <c r="F72" t="n">
+        <v>412467573.12</v>
+      </c>
+      <c r="G72" t="n">
+        <v>403987795.94</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1669347.22</v>
+      </c>
+      <c r="I72" t="n">
+        <v>67683789.95999999</v>
+      </c>
+      <c r="J72" t="n">
+        <v>69353137.18000001</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C70" t="n">
+      <c r="C73" t="n">
         <v>2281</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E73" t="n">
         <v>7453421.77</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F73" t="n">
         <v>7042060.99</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G73" t="n">
         <v>6627633.67</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H73" t="n">
         <v>7006</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I73" t="n">
         <v>1513188.14</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J73" t="n">
         <v>1520194.14</v>
       </c>
     </row>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,34 +558,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARMVA</t>
+          <t>ALMG</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2461</v>
+        <v>1011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
+          <t>ASSEMBLEIA LEGISLATIVA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3998282.31</v>
+        <v>1702987288.68</v>
       </c>
       <c r="F4" t="n">
-        <v>2913330.3</v>
+        <v>1579534767.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2891473.26</v>
+        <v>1572939663.08</v>
       </c>
       <c r="H4" t="n">
-        <v>114.72</v>
+        <v>2089.8</v>
       </c>
       <c r="I4" t="n">
-        <v>64611.25</v>
+        <v>61835606.82</v>
       </c>
       <c r="J4" t="n">
-        <v>64725.97</v>
+        <v>61837696.62</v>
       </c>
     </row>
     <row r="5">
@@ -594,34 +594,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARSAE -MG</t>
+          <t>ARMVA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2441</v>
+        <v>2461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
+          <t>AGENCIA DE DESENVOLVIMENTO DA REGIAO METROPOLITANA DO VALE DO ACO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15948670.24</v>
+        <v>3998282.31</v>
       </c>
       <c r="F5" t="n">
-        <v>15099248.76</v>
+        <v>2913330.3</v>
       </c>
       <c r="G5" t="n">
-        <v>15008695.06</v>
+        <v>2891473.26</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>114.72</v>
       </c>
       <c r="I5" t="n">
-        <v>744776.36</v>
+        <v>64611.25</v>
       </c>
       <c r="J5" t="n">
-        <v>744776.36</v>
+        <v>64725.97</v>
       </c>
     </row>
     <row r="6">
@@ -630,34 +630,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CBMMG</t>
+          <t>ARSAE -MG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1401</v>
+        <v>2441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>AGENCIA REGULADORA DE SERVICOS DE ABASTECIMENTO DE AGUA E DE ESGOTAMENTO SANITARIO DO ESTADO DE MINA</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1617069712.19</v>
+        <v>15948670.24</v>
       </c>
       <c r="F6" t="n">
-        <v>1550882048.63</v>
+        <v>15099248.76</v>
       </c>
       <c r="G6" t="n">
-        <v>1547930780.08</v>
+        <v>15008695.06</v>
       </c>
       <c r="H6" t="n">
-        <v>4065273.59</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>42151132.62</v>
+        <v>744776.36</v>
       </c>
       <c r="J6" t="n">
-        <v>46216406.21</v>
+        <v>744776.36</v>
       </c>
     </row>
     <row r="7">
@@ -666,34 +666,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CGE</t>
+          <t>CBMMG</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1521</v>
+        <v>1401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CONTROLADORIA-GERAL DO ESTADO</t>
+          <t>CORPO DE BOMBEIROS MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>55665667.37</v>
+        <v>1617069712.19</v>
       </c>
       <c r="F7" t="n">
-        <v>55392655.65</v>
+        <v>1550882048.63</v>
       </c>
       <c r="G7" t="n">
-        <v>55212108.02</v>
+        <v>1547930780.08</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4065273.59</v>
       </c>
       <c r="I7" t="n">
-        <v>239632.61</v>
+        <v>42151132.62</v>
       </c>
       <c r="J7" t="n">
-        <v>239632.61</v>
+        <v>46216406.21</v>
       </c>
     </row>
     <row r="8">
@@ -702,34 +702,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DER-MG</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2301</v>
+        <v>1521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+          <t>CONTROLADORIA-GERAL DO ESTADO</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2009831554.49</v>
+        <v>55665667.37</v>
       </c>
       <c r="F8" t="n">
-        <v>1273629898.99</v>
+        <v>55392655.65</v>
       </c>
       <c r="G8" t="n">
-        <v>1248196121.6</v>
+        <v>55212108.02</v>
       </c>
       <c r="H8" t="n">
-        <v>3419688.86</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>168251149.94</v>
+        <v>239632.61</v>
       </c>
       <c r="J8" t="n">
-        <v>171670838.8</v>
+        <v>239632.61</v>
       </c>
     </row>
     <row r="9">
@@ -738,34 +738,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EGE - SEF</t>
+          <t>DEF PUB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1911</v>
+        <v>1441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
+          <t>DEFENSORIA PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12201752803.83</v>
+        <v>736345633.02</v>
       </c>
       <c r="F9" t="n">
-        <v>11477276512.18</v>
+        <v>718847331.48</v>
       </c>
       <c r="G9" t="n">
-        <v>11477261273.86</v>
+        <v>714589715.37</v>
       </c>
       <c r="H9" t="n">
-        <v>557959.5699999999</v>
+        <v>39893.69</v>
       </c>
       <c r="I9" t="n">
-        <v>85266341.89</v>
+        <v>8604588.82</v>
       </c>
       <c r="J9" t="n">
-        <v>85824301.45999999</v>
+        <v>8644482.51</v>
       </c>
     </row>
     <row r="10">
@@ -774,34 +774,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EGE-SEPLAG</t>
+          <t>DER-MG</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1941</v>
+        <v>2301</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>DEPARTAMENTO DE EDIFICACOES E ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>201288736.28</v>
+        <v>2009831554.49</v>
       </c>
       <c r="F10" t="n">
-        <v>201288736.28</v>
+        <v>1273629898.99</v>
       </c>
       <c r="G10" t="n">
-        <v>201288736.28</v>
+        <v>1248196121.6</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3419688.86</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>168251149.94</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>171670838.8</v>
       </c>
     </row>
     <row r="11">
@@ -810,29 +810,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>EGE - SEF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3041</v>
+        <v>1911</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
+          <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>368437125.57</v>
+        <v>12201752803.83</v>
       </c>
       <c r="F11" t="n">
-        <v>368437125.57</v>
+        <v>11477276512.18</v>
       </c>
       <c r="G11" t="n">
-        <v>368437125.57</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>11477261273.86</v>
+      </c>
+      <c r="H11" t="n">
+        <v>557959.5699999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>85266341.89</v>
+      </c>
+      <c r="J11" t="n">
+        <v>85824301.45999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -840,29 +846,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EMC</t>
+          <t>EGE-SEPLAG</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3151</v>
+        <v>1941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
+          <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15789557.36</v>
+        <v>201288736.28</v>
       </c>
       <c r="F12" t="n">
-        <v>15789557.36</v>
+        <v>201288736.28</v>
       </c>
       <c r="G12" t="n">
-        <v>15789557.36</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>201288736.28</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -870,25 +882,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3051</v>
+        <v>3041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
+          <t>EMPRESA DE ASSISTENCIA TECNICA E EXTENSAO RURAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>119899404.19</v>
+        <v>368437125.57</v>
       </c>
       <c r="F13" t="n">
-        <v>119899404.19</v>
+        <v>368437125.57</v>
       </c>
       <c r="G13" t="n">
-        <v>119899404.19</v>
+        <v>368437125.57</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -900,35 +912,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EMC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1541</v>
+        <v>3151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA MINEIRA DE COMUNICACAO</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17601666.31</v>
+        <v>15789557.36</v>
       </c>
       <c r="F14" t="n">
-        <v>17148601.56</v>
+        <v>15789557.36</v>
       </c>
       <c r="G14" t="n">
-        <v>16887894.92</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>256633.48</v>
-      </c>
-      <c r="J14" t="n">
-        <v>256633.48</v>
-      </c>
+        <v>15789557.36</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -936,35 +942,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4541</v>
+        <v>3051</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>315895.03</v>
+        <v>119899404.19</v>
       </c>
       <c r="F15" t="n">
-        <v>315480.44</v>
+        <v>119899404.19</v>
       </c>
       <c r="G15" t="n">
-        <v>315480.44</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
+        <v>119899404.19</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,34 +972,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2171</v>
+        <v>1541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4662678.05</v>
+        <v>17601666.31</v>
       </c>
       <c r="F16" t="n">
-        <v>4296034.19</v>
+        <v>17148601.56</v>
       </c>
       <c r="G16" t="n">
-        <v>4144793.59</v>
+        <v>16887894.92</v>
       </c>
       <c r="H16" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>13446.09</v>
+        <v>256633.48</v>
       </c>
       <c r="J16" t="n">
-        <v>13513.59</v>
+        <v>256633.48</v>
       </c>
     </row>
     <row r="17">
@@ -1008,34 +1008,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2071</v>
+        <v>4541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>455083279.96</v>
+        <v>315895.03</v>
       </c>
       <c r="F17" t="n">
-        <v>442616854.91</v>
+        <v>315480.44</v>
       </c>
       <c r="G17" t="n">
-        <v>429159889.95</v>
+        <v>315480.44</v>
       </c>
       <c r="H17" t="n">
-        <v>50484697.07</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>12791969.37</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>63276666.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +1044,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2181</v>
+        <v>2171</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>44939828.32</v>
+        <v>4662678.05</v>
       </c>
       <c r="F18" t="n">
-        <v>43912375.76</v>
+        <v>4296034.19</v>
       </c>
       <c r="G18" t="n">
-        <v>43171411.16</v>
+        <v>4144793.59</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>67.5</v>
       </c>
       <c r="I18" t="n">
-        <v>418535.58</v>
+        <v>13446.09</v>
       </c>
       <c r="J18" t="n">
-        <v>418535.58</v>
+        <v>13513.59</v>
       </c>
     </row>
     <row r="19">
@@ -1080,29 +1080,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4331</v>
+        <v>2071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>147406.89</v>
+        <v>455083279.96</v>
       </c>
       <c r="F19" t="n">
-        <v>147406.89</v>
+        <v>442616854.91</v>
       </c>
       <c r="G19" t="n">
-        <v>143721.71</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+        <v>429159889.95</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50484697.07</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12791969.37</v>
+      </c>
+      <c r="J19" t="n">
+        <v>63276666.44</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1110,34 +1116,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2091</v>
+        <v>2181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>41540382.17</v>
+        <v>44939828.32</v>
       </c>
       <c r="F20" t="n">
-        <v>41283632.97</v>
+        <v>43912375.76</v>
       </c>
       <c r="G20" t="n">
-        <v>40766476.92</v>
+        <v>43171411.16</v>
       </c>
       <c r="H20" t="n">
-        <v>27692.5</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>11647.71</v>
+        <v>418535.58</v>
       </c>
       <c r="J20" t="n">
-        <v>39340.21</v>
+        <v>418535.58</v>
       </c>
     </row>
     <row r="21">
@@ -1146,35 +1152,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4251</v>
+        <v>4331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>207531660.9</v>
+        <v>147406.89</v>
       </c>
       <c r="F21" t="n">
-        <v>189241489.7</v>
+        <v>147406.89</v>
       </c>
       <c r="G21" t="n">
-        <v>187462418.98</v>
-      </c>
-      <c r="H21" t="n">
-        <v>98887758.56999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4684458.53</v>
-      </c>
-      <c r="J21" t="n">
-        <v>103572217.1</v>
-      </c>
+        <v>143721.71</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1182,34 +1182,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4491</v>
+        <v>2091</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12198756.32</v>
+        <v>41540382.17</v>
       </c>
       <c r="F22" t="n">
-        <v>12198756.32</v>
+        <v>41283632.97</v>
       </c>
       <c r="G22" t="n">
-        <v>9336561.16</v>
+        <v>40766476.92</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>27692.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>11647.71</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>39340.21</v>
       </c>
     </row>
     <row r="23">
@@ -1218,34 +1218,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4101</v>
+        <v>4251</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17493925.29</v>
+        <v>207531660.9</v>
       </c>
       <c r="F23" t="n">
-        <v>16080240.21</v>
+        <v>189241489.7</v>
       </c>
       <c r="G23" t="n">
-        <v>16080240.21</v>
+        <v>187462418.98</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>98887758.56999999</v>
       </c>
       <c r="I23" t="n">
-        <v>517189.73</v>
+        <v>4684458.53</v>
       </c>
       <c r="J23" t="n">
-        <v>517189.73</v>
+        <v>103572217.1</v>
       </c>
     </row>
     <row r="24">
@@ -1254,34 +1254,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4601</v>
+        <v>4491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>464551.64</v>
+        <v>12198756.32</v>
       </c>
       <c r="F24" t="n">
-        <v>419551.64</v>
+        <v>12198756.32</v>
       </c>
       <c r="G24" t="n">
-        <v>239551.64</v>
+        <v>9336561.16</v>
       </c>
       <c r="H24" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>80000</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>160000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1290,34 +1290,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4291</v>
+        <v>4101</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>10255262090.27</v>
+        <v>17493925.29</v>
       </c>
       <c r="F25" t="n">
-        <v>9575510065.219999</v>
+        <v>16080240.21</v>
       </c>
       <c r="G25" t="n">
-        <v>9231614379.459999</v>
+        <v>16080240.21</v>
       </c>
       <c r="H25" t="n">
-        <v>554014631.28</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>786454402.1799999</v>
+        <v>517189.73</v>
       </c>
       <c r="J25" t="n">
-        <v>1340469033.46</v>
+        <v>517189.73</v>
       </c>
     </row>
     <row r="26">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4691</v>
+        <v>4601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25338987.88</v>
+        <v>464551.64</v>
       </c>
       <c r="F26" t="n">
-        <v>11474135.71</v>
+        <v>419551.64</v>
       </c>
       <c r="G26" t="n">
-        <v>9347783.02</v>
+        <v>239551.64</v>
       </c>
       <c r="H26" t="n">
-        <v>1094891.98</v>
+        <v>80000</v>
       </c>
       <c r="I26" t="n">
-        <v>4039900.86</v>
+        <v>80000</v>
       </c>
       <c r="J26" t="n">
-        <v>5134792.84</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="27">
@@ -1362,34 +1362,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4701</v>
+        <v>4451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3542540.26</v>
+        <v>11107774.68</v>
       </c>
       <c r="F27" t="n">
-        <v>4264.26</v>
+        <v>10032800.23</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>9730140.449999999</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2888273.21</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2888273.21</v>
       </c>
     </row>
     <row r="28">
@@ -1398,34 +1398,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4711</v>
+        <v>4031</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>15325406751.49</v>
+        <v>1386896516.13</v>
       </c>
       <c r="F28" t="n">
-        <v>15323499427.6</v>
+        <v>1145911266.98</v>
       </c>
       <c r="G28" t="n">
-        <v>15328734230.09</v>
+        <v>1050692519.56</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1272370.64</v>
       </c>
       <c r="I28" t="n">
-        <v>79198.5</v>
+        <v>93340728.53</v>
       </c>
       <c r="J28" t="n">
-        <v>79198.5</v>
+        <v>94613099.17</v>
       </c>
     </row>
     <row r="29">
@@ -1434,34 +1434,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2151</v>
+        <v>4291</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>54848300.42</v>
+        <v>10255262090.27</v>
       </c>
       <c r="F29" t="n">
-        <v>50479779.7</v>
+        <v>9575510065.219999</v>
       </c>
       <c r="G29" t="n">
-        <v>50120409.8</v>
+        <v>9231614379.459999</v>
       </c>
       <c r="H29" t="n">
-        <v>4125</v>
+        <v>554014631.28</v>
       </c>
       <c r="I29" t="n">
-        <v>6086840.51</v>
+        <v>786454402.1799999</v>
       </c>
       <c r="J29" t="n">
-        <v>6090965.51</v>
+        <v>1340469033.46</v>
       </c>
     </row>
     <row r="30">
@@ -1470,34 +1470,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2271</v>
+        <v>4691</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2277629071.19</v>
+        <v>25338987.88</v>
       </c>
       <c r="F30" t="n">
-        <v>2165324017.21</v>
+        <v>11474135.71</v>
       </c>
       <c r="G30" t="n">
-        <v>2143497567.57</v>
+        <v>9347783.02</v>
       </c>
       <c r="H30" t="n">
-        <v>3753299.71</v>
+        <v>1094891.98</v>
       </c>
       <c r="I30" t="n">
-        <v>42680567.96</v>
+        <v>4039900.86</v>
       </c>
       <c r="J30" t="n">
-        <v>46433867.67</v>
+        <v>5134792.84</v>
       </c>
     </row>
     <row r="31">
@@ -1506,34 +1506,34 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4341</v>
+        <v>4701</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2866852.09</v>
+        <v>3542540.26</v>
       </c>
       <c r="F31" t="n">
-        <v>2778584.69</v>
+        <v>4264.26</v>
       </c>
       <c r="G31" t="n">
-        <v>2557135.68</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>129135.76</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>129135.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1542,34 +1542,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2061</v>
+        <v>4711</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>64511960.77</v>
+        <v>15325406751.49</v>
       </c>
       <c r="F32" t="n">
-        <v>58152640.77</v>
+        <v>15323499427.6</v>
       </c>
       <c r="G32" t="n">
-        <v>56790483.53</v>
+        <v>15328734230.09</v>
       </c>
       <c r="H32" t="n">
-        <v>141507.05</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1655021.81</v>
+        <v>79198.5</v>
       </c>
       <c r="J32" t="n">
-        <v>1796528.86</v>
+        <v>79198.5</v>
       </c>
     </row>
     <row r="33">
@@ -1578,34 +1578,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4141</v>
+        <v>2151</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>31245732.35</v>
+        <v>54848300.42</v>
       </c>
       <c r="F33" t="n">
-        <v>13353865.57</v>
+        <v>50479779.7</v>
       </c>
       <c r="G33" t="n">
-        <v>13353865.57</v>
+        <v>50120409.8</v>
       </c>
       <c r="H33" t="n">
-        <v>1574.5</v>
+        <v>4125</v>
       </c>
       <c r="I33" t="n">
-        <v>5560409.71</v>
+        <v>6086840.51</v>
       </c>
       <c r="J33" t="n">
-        <v>5561984.21</v>
+        <v>6090965.51</v>
       </c>
     </row>
     <row r="34">
@@ -1614,34 +1614,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4631</v>
+        <v>2271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>386159674.85</v>
+        <v>2277629071.19</v>
       </c>
       <c r="F34" t="n">
-        <v>248996997.66</v>
+        <v>2165324017.21</v>
       </c>
       <c r="G34" t="n">
-        <v>238193664.04</v>
+        <v>2143497567.57</v>
       </c>
       <c r="H34" t="n">
-        <v>275729.74</v>
+        <v>3753299.71</v>
       </c>
       <c r="I34" t="n">
-        <v>15778864.88</v>
+        <v>42680567.96</v>
       </c>
       <c r="J34" t="n">
-        <v>16054594.62</v>
+        <v>46433867.67</v>
       </c>
     </row>
     <row r="35">
@@ -1650,34 +1650,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2161</v>
+        <v>4341</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16628991.48</v>
+        <v>2866852.09</v>
       </c>
       <c r="F35" t="n">
-        <v>15101587.53</v>
+        <v>2778584.69</v>
       </c>
       <c r="G35" t="n">
-        <v>14946425.03</v>
+        <v>2557135.68</v>
       </c>
       <c r="H35" t="n">
-        <v>15535.07</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2608678.68</v>
+        <v>129135.76</v>
       </c>
       <c r="J35" t="n">
-        <v>2624213.75</v>
+        <v>129135.76</v>
       </c>
     </row>
     <row r="36">
@@ -1686,34 +1686,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4551</v>
+        <v>2061</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>161975565.86</v>
+        <v>64511960.77</v>
       </c>
       <c r="F36" t="n">
-        <v>161973985.31</v>
+        <v>58152640.77</v>
       </c>
       <c r="G36" t="n">
-        <v>155079704.45</v>
+        <v>56790483.53</v>
       </c>
       <c r="H36" t="n">
-        <v>12273523.84</v>
+        <v>141507.05</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1655021.81</v>
       </c>
       <c r="J36" t="n">
-        <v>12273523.84</v>
+        <v>1796528.86</v>
       </c>
     </row>
     <row r="37">
@@ -1722,34 +1722,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FUNDIF</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4421</v>
+        <v>4141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1278479.27</v>
+        <v>31245732.35</v>
       </c>
       <c r="F37" t="n">
-        <v>1278479.27</v>
+        <v>13353865.57</v>
       </c>
       <c r="G37" t="n">
-        <v>1278479.27</v>
+        <v>13353865.57</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1574.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>5560409.71</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>5561984.21</v>
       </c>
     </row>
     <row r="38">
@@ -1758,34 +1758,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FUNED</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2261</v>
+        <v>4631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDACAO EZEQUIEL DIAS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>319786910.28</v>
+        <v>386159674.85</v>
       </c>
       <c r="F38" t="n">
-        <v>263858227.88</v>
+        <v>248996997.66</v>
       </c>
       <c r="G38" t="n">
-        <v>252638336.78</v>
+        <v>238193664.04</v>
       </c>
       <c r="H38" t="n">
-        <v>101930917.99</v>
+        <v>275729.74</v>
       </c>
       <c r="I38" t="n">
-        <v>47063914.03</v>
+        <v>15778864.88</v>
       </c>
       <c r="J38" t="n">
-        <v>148994832.02</v>
+        <v>16054594.62</v>
       </c>
     </row>
     <row r="39">
@@ -1794,34 +1794,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUNTRANS</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4381</v>
+        <v>2161</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>140227334.65</v>
+        <v>16628991.48</v>
       </c>
       <c r="F39" t="n">
-        <v>53251682.01</v>
+        <v>15101587.53</v>
       </c>
       <c r="G39" t="n">
-        <v>52665792.69</v>
+        <v>14946425.03</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>15535.07</v>
       </c>
       <c r="I39" t="n">
-        <v>5954269.9</v>
+        <v>2608678.68</v>
       </c>
       <c r="J39" t="n">
-        <v>5954269.9</v>
+        <v>2624213.75</v>
       </c>
     </row>
     <row r="40">
@@ -1830,34 +1830,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1071</v>
+        <v>4551</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>41468457.48</v>
+        <v>161975565.86</v>
       </c>
       <c r="F40" t="n">
-        <v>36393685.24</v>
+        <v>161973985.31</v>
       </c>
       <c r="G40" t="n">
-        <v>35762406.77</v>
+        <v>155079704.45</v>
       </c>
       <c r="H40" t="n">
-        <v>4065417.18</v>
+        <v>12273523.84</v>
       </c>
       <c r="I40" t="n">
-        <v>2244249.52</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>6309666.7</v>
+        <v>12273523.84</v>
       </c>
     </row>
     <row r="41">
@@ -1866,35 +1866,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GDPE - SEF</t>
+          <t>FUNCONTAS</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1916</v>
+        <v>4611</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
+          <t>FUNDO DO TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5700229349.95</v>
+        <v>24587.7</v>
       </c>
       <c r="F41" t="n">
-        <v>5577199638.67</v>
+        <v>24587.7</v>
       </c>
       <c r="G41" t="n">
-        <v>5517860023.27</v>
-      </c>
-      <c r="H41" t="n">
-        <v>28843343.77</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>28843343.77</v>
-      </c>
+        <v>24587.7</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1902,35 +1896,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HEMOMINAS</t>
+          <t>FUNDHAB</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2321</v>
+        <v>4121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
+          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>333195770.76</v>
+        <v>4983186.54</v>
       </c>
       <c r="F42" t="n">
-        <v>296763683.46</v>
+        <v>3723186.54</v>
       </c>
       <c r="G42" t="n">
-        <v>290862823.02</v>
-      </c>
-      <c r="H42" t="n">
-        <v>255386.81</v>
-      </c>
-      <c r="I42" t="n">
-        <v>25746888.77</v>
-      </c>
-      <c r="J42" t="n">
-        <v>26002275.58</v>
-      </c>
+        <v>3456207.79</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1938,34 +1926,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>IDENE</t>
+          <t>FUNDIF</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2421</v>
+        <v>4421</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53060472.47</v>
+        <v>1278479.27</v>
       </c>
       <c r="F43" t="n">
-        <v>46263655.96</v>
+        <v>1278479.27</v>
       </c>
       <c r="G43" t="n">
-        <v>45692556.63</v>
+        <v>1278479.27</v>
       </c>
       <c r="H43" t="n">
-        <v>976681.46</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>14019630.84</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>14996312.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1974,34 +1962,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>FUNED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2101</v>
+        <v>2261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
+          <t>FUNDACAO EZEQUIEL DIAS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>195536444.95</v>
+        <v>319786910.28</v>
       </c>
       <c r="F44" t="n">
-        <v>190876690.89</v>
+        <v>263858227.88</v>
       </c>
       <c r="G44" t="n">
-        <v>183865965.58</v>
+        <v>252638336.78</v>
       </c>
       <c r="H44" t="n">
-        <v>1981216.45</v>
+        <v>101930917.99</v>
       </c>
       <c r="I44" t="n">
-        <v>3389073.5</v>
+        <v>47063914.03</v>
       </c>
       <c r="J44" t="n">
-        <v>5370289.95</v>
+        <v>148994832.02</v>
       </c>
     </row>
     <row r="45">
@@ -2010,34 +1998,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>IEPHA</t>
+          <t>FUNEMP</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2201</v>
+        <v>4441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
+          <t>FUNDO ESPECIAL DO MINISTERIO PUBLICO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>24595717.43</v>
+        <v>24443811.21</v>
       </c>
       <c r="F45" t="n">
-        <v>20047336.04</v>
+        <v>13265445.69</v>
       </c>
       <c r="G45" t="n">
-        <v>19187028.92</v>
+        <v>13119045.05</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>99860.64</v>
       </c>
       <c r="I45" t="n">
-        <v>934662.77</v>
+        <v>7087195.69</v>
       </c>
       <c r="J45" t="n">
-        <v>934662.77</v>
+        <v>7187056.33</v>
       </c>
     </row>
     <row r="46">
@@ -2046,34 +2034,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IGAM</t>
+          <t>FUNTRANS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2241</v>
+        <v>4381</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+          <t>FUNDO ESTADUAL DE DESENVOLVIMENTO DE TRANSPORTES</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>69270924.79000001</v>
+        <v>140227334.65</v>
       </c>
       <c r="F46" t="n">
-        <v>64810240.33</v>
+        <v>53251682.01</v>
       </c>
       <c r="G46" t="n">
-        <v>64595191.74</v>
+        <v>52665792.69</v>
       </c>
       <c r="H46" t="n">
-        <v>10437314.16</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1573915.38</v>
+        <v>5954269.9</v>
       </c>
       <c r="J46" t="n">
-        <v>12011229.54</v>
+        <v>5954269.9</v>
       </c>
     </row>
     <row r="47">
@@ -2082,34 +2070,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IMA</t>
+          <t>GABINETE MILITAR</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2371</v>
+        <v>1071</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
+          <t>GABINETE MILITAR DO GOVERNADOR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>265147788.61</v>
+        <v>41468457.48</v>
       </c>
       <c r="F47" t="n">
-        <v>260504964.97</v>
+        <v>36393685.24</v>
       </c>
       <c r="G47" t="n">
-        <v>260025427.44</v>
+        <v>35762406.77</v>
       </c>
       <c r="H47" t="n">
-        <v>11259.94</v>
+        <v>4065417.18</v>
       </c>
       <c r="I47" t="n">
-        <v>7021591.43</v>
+        <v>2244249.52</v>
       </c>
       <c r="J47" t="n">
-        <v>7032851.37</v>
+        <v>6309666.7</v>
       </c>
     </row>
     <row r="48">
@@ -2118,34 +2106,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IPEMMG</t>
+          <t>GDPE - SEF</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2331</v>
+        <v>1916</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>26902206.65</v>
+        <v>5700229349.95</v>
       </c>
       <c r="F48" t="n">
-        <v>26685069.71</v>
+        <v>5577199638.67</v>
       </c>
       <c r="G48" t="n">
-        <v>26064598.71</v>
+        <v>5517860023.27</v>
       </c>
       <c r="H48" t="n">
-        <v>333694.72</v>
+        <v>28843343.77</v>
       </c>
       <c r="I48" t="n">
-        <v>520848.74</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>854543.46</v>
+        <v>28843343.77</v>
       </c>
     </row>
     <row r="49">
@@ -2154,34 +2142,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IPSEMG</t>
+          <t>HEMOMINAS</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2011</v>
+        <v>2321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO CENTRO DE HEMATOLOGIA E HEMOTERAPIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1536739486.14</v>
+        <v>333195770.76</v>
       </c>
       <c r="F49" t="n">
-        <v>1341247986.54</v>
+        <v>296763683.46</v>
       </c>
       <c r="G49" t="n">
-        <v>1307994655.9</v>
+        <v>290862823.02</v>
       </c>
       <c r="H49" t="n">
-        <v>423878.41</v>
+        <v>255386.81</v>
       </c>
       <c r="I49" t="n">
-        <v>127022888.49</v>
+        <v>25746888.77</v>
       </c>
       <c r="J49" t="n">
-        <v>127446766.9</v>
+        <v>26002275.58</v>
       </c>
     </row>
     <row r="50">
@@ -2190,34 +2178,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IPSM</t>
+          <t>IDENE</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2121</v>
+        <v>2421</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE DESENVOLVIMENTO DO NORTE E NORDESTE DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2732447147.53</v>
+        <v>53060472.47</v>
       </c>
       <c r="F50" t="n">
-        <v>2675654178.82</v>
+        <v>46263655.96</v>
       </c>
       <c r="G50" t="n">
-        <v>2000806584.11</v>
+        <v>45692556.63</v>
       </c>
       <c r="H50" t="n">
-        <v>94866365.34999999</v>
+        <v>976681.46</v>
       </c>
       <c r="I50" t="n">
-        <v>67386629.63</v>
+        <v>14019630.84</v>
       </c>
       <c r="J50" t="n">
-        <v>162252994.98</v>
+        <v>14996312.3</v>
       </c>
     </row>
     <row r="51">
@@ -2226,34 +2214,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JUCEMG</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2251</v>
+        <v>2101</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DE FLORESTAS</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>32289616.85</v>
+        <v>195536444.95</v>
       </c>
       <c r="F51" t="n">
-        <v>30153432.18</v>
+        <v>190876690.89</v>
       </c>
       <c r="G51" t="n">
-        <v>29578426.34</v>
+        <v>183865965.58</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1981216.45</v>
       </c>
       <c r="I51" t="n">
-        <v>671682.59</v>
+        <v>3389073.5</v>
       </c>
       <c r="J51" t="n">
-        <v>671682.59</v>
+        <v>5370289.95</v>
       </c>
     </row>
     <row r="52">
@@ -2262,34 +2250,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LEMG</t>
+          <t>IEPHA</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2041</v>
+        <v>2201</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO ESTADUAL DO PATRIMONIO HISTORICO E ARTISTICO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6761105.25</v>
+        <v>24595717.43</v>
       </c>
       <c r="F52" t="n">
-        <v>5938379.6</v>
+        <v>20047336.04</v>
       </c>
       <c r="G52" t="n">
-        <v>5925515.6</v>
+        <v>19187028.92</v>
       </c>
       <c r="H52" t="n">
-        <v>4598.79</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1296981.73</v>
+        <v>934662.77</v>
       </c>
       <c r="J52" t="n">
-        <v>1301580.52</v>
+        <v>934662.77</v>
       </c>
     </row>
     <row r="53">
@@ -2298,29 +2286,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MG INVESTE</t>
+          <t>IGAM</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>4621</v>
+        <v>2241</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>88898823.3</v>
+        <v>69270924.79000001</v>
       </c>
       <c r="F53" t="n">
-        <v>88898823.3</v>
+        <v>64810240.33</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+        <v>64595191.74</v>
+      </c>
+      <c r="H53" t="n">
+        <v>10437314.16</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1573915.38</v>
+      </c>
+      <c r="J53" t="n">
+        <v>12011229.54</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2328,34 +2322,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>IMA</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1101</v>
+        <v>2371</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO MINEIRO DE AGROPECUARIA</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>12148887.19</v>
+        <v>265147788.61</v>
       </c>
       <c r="F54" t="n">
-        <v>11844528.2</v>
+        <v>260504964.97</v>
       </c>
       <c r="G54" t="n">
-        <v>11757162.48</v>
+        <v>260025427.44</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>11259.94</v>
       </c>
       <c r="I54" t="n">
-        <v>36247.74</v>
+        <v>7021591.43</v>
       </c>
       <c r="J54" t="n">
-        <v>36247.74</v>
+        <v>7032851.37</v>
       </c>
     </row>
     <row r="55">
@@ -2364,34 +2358,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>IPEMMG</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1915</v>
+        <v>2331</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>INSTITUTO DE METROLOGIA E QUALIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1045679146.33</v>
+        <v>26902206.65</v>
       </c>
       <c r="F55" t="n">
-        <v>525455877.98</v>
+        <v>26685069.71</v>
       </c>
       <c r="G55" t="n">
-        <v>525455877.98</v>
+        <v>26064598.71</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>333694.72</v>
       </c>
       <c r="I55" t="n">
-        <v>28198078.12</v>
+        <v>520848.74</v>
       </c>
       <c r="J55" t="n">
-        <v>28198078.12</v>
+        <v>854543.46</v>
       </c>
     </row>
     <row r="56">
@@ -2400,35 +2394,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>IPLEMG</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1511</v>
+        <v>2361</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DO LEGISLATIVO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3185868726.65</v>
+        <v>48561261.9</v>
       </c>
       <c r="F56" t="n">
-        <v>3092549019.47</v>
+        <v>48561261.9</v>
       </c>
       <c r="G56" t="n">
-        <v>3072423500.15</v>
-      </c>
-      <c r="H56" t="n">
-        <v>18094662.5</v>
-      </c>
-      <c r="I56" t="n">
-        <v>61379561.55</v>
-      </c>
-      <c r="J56" t="n">
-        <v>79474224.05</v>
-      </c>
+        <v>48561261.9</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2436,34 +2424,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>IPSEMG</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1251</v>
+        <v>2011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>12979474804.25</v>
+        <v>1536739486.14</v>
       </c>
       <c r="F57" t="n">
-        <v>12773110420.68</v>
+        <v>1341247986.54</v>
       </c>
       <c r="G57" t="n">
-        <v>12732571407.31</v>
+        <v>1307994655.9</v>
       </c>
       <c r="H57" t="n">
-        <v>41558515.4</v>
+        <v>423878.41</v>
       </c>
       <c r="I57" t="n">
-        <v>216807656.75</v>
+        <v>127022888.49</v>
       </c>
       <c r="J57" t="n">
-        <v>258366172.15</v>
+        <v>127446766.9</v>
       </c>
     </row>
     <row r="58">
@@ -2472,34 +2460,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>IPSM</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1231</v>
+        <v>2121</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+          <t>INSTITUTO DE PREVIDENCIA DOS SERVIDORES MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>196292319.51</v>
+        <v>2732447147.53</v>
       </c>
       <c r="F58" t="n">
-        <v>192693183.61</v>
+        <v>2675654178.82</v>
       </c>
       <c r="G58" t="n">
-        <v>183911092.06</v>
+        <v>2000806584.11</v>
       </c>
       <c r="H58" t="n">
-        <v>926349.9300000001</v>
+        <v>94866365.34999999</v>
       </c>
       <c r="I58" t="n">
-        <v>4138969.75</v>
+        <v>67386629.63</v>
       </c>
       <c r="J58" t="n">
-        <v>5065319.68</v>
+        <v>162252994.98</v>
       </c>
     </row>
     <row r="59">
@@ -2508,34 +2496,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>JUCEMG</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1631</v>
+        <v>2251</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>JUNTA COMERCIAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>63665749.64</v>
+        <v>32289616.85</v>
       </c>
       <c r="F59" t="n">
-        <v>39924754.94</v>
+        <v>30153432.18</v>
       </c>
       <c r="G59" t="n">
-        <v>39409640.61</v>
+        <v>29578426.34</v>
       </c>
       <c r="H59" t="n">
-        <v>475922.2</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>24058202.1</v>
+        <v>671682.59</v>
       </c>
       <c r="J59" t="n">
-        <v>24534124.3</v>
+        <v>671682.59</v>
       </c>
     </row>
     <row r="60">
@@ -2544,34 +2532,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>LEMG</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1271</v>
+        <v>2041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>LOTERIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>71925491.40000001</v>
+        <v>6761105.25</v>
       </c>
       <c r="F60" t="n">
-        <v>70589799.61</v>
+        <v>5938379.6</v>
       </c>
       <c r="G60" t="n">
-        <v>69678332.78</v>
+        <v>5925515.6</v>
       </c>
       <c r="H60" t="n">
-        <v>20181416.68</v>
+        <v>4598.79</v>
       </c>
       <c r="I60" t="n">
-        <v>10134142.55</v>
+        <v>1296981.73</v>
       </c>
       <c r="J60" t="n">
-        <v>30315559.23</v>
+        <v>1301580.52</v>
       </c>
     </row>
     <row r="61">
@@ -2580,35 +2568,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>MG INVESTE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1221</v>
+        <v>4621</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>91983736.40000001</v>
+        <v>88898823.3</v>
       </c>
       <c r="F61" t="n">
-        <v>76448925.22</v>
+        <v>88898823.3</v>
       </c>
       <c r="G61" t="n">
-        <v>75856018.97</v>
-      </c>
-      <c r="H61" t="n">
-        <v>467.76</v>
-      </c>
-      <c r="I61" t="n">
-        <v>10588548.64</v>
-      </c>
-      <c r="J61" t="n">
-        <v>10589016.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2616,34 +2598,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1481</v>
+        <v>1101</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>152723547.84</v>
+        <v>12148887.19</v>
       </c>
       <c r="F62" t="n">
-        <v>140202461.6</v>
+        <v>11844528.2</v>
       </c>
       <c r="G62" t="n">
-        <v>128851499.22</v>
+        <v>11757162.48</v>
       </c>
       <c r="H62" t="n">
-        <v>5411868.7</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>11509155.9</v>
+        <v>36247.74</v>
       </c>
       <c r="J62" t="n">
-        <v>16921024.6</v>
+        <v>36247.74</v>
       </c>
     </row>
     <row r="63">
@@ -2652,34 +2634,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1261</v>
+        <v>1915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>16633018692.76</v>
+        <v>1045679146.33</v>
       </c>
       <c r="F63" t="n">
-        <v>16079912253.18</v>
+        <v>525455877.98</v>
       </c>
       <c r="G63" t="n">
-        <v>15837680952.16</v>
+        <v>525455877.98</v>
       </c>
       <c r="H63" t="n">
-        <v>585170446.71</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>757153016.96</v>
+        <v>28198078.12</v>
       </c>
       <c r="J63" t="n">
-        <v>1342323463.67</v>
+        <v>28198078.12</v>
       </c>
     </row>
     <row r="64">
@@ -2688,34 +2670,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1191</v>
+        <v>1511</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1539130234.2</v>
+        <v>3185868726.65</v>
       </c>
       <c r="F64" t="n">
-        <v>1488234890.69</v>
+        <v>3092549019.47</v>
       </c>
       <c r="G64" t="n">
-        <v>1475159288.69</v>
+        <v>3072423500.15</v>
       </c>
       <c r="H64" t="n">
-        <v>10728442.75</v>
+        <v>18094662.5</v>
       </c>
       <c r="I64" t="n">
-        <v>69971290.95999999</v>
+        <v>61379561.55</v>
       </c>
       <c r="J64" t="n">
-        <v>80699733.70999999</v>
+        <v>79474224.05</v>
       </c>
     </row>
     <row r="65">
@@ -2724,34 +2706,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1491</v>
+        <v>1091</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1612507669.42</v>
+        <v>2663990411.98</v>
       </c>
       <c r="F65" t="n">
-        <v>1582583713.78</v>
+        <v>2583438879.85</v>
       </c>
       <c r="G65" t="n">
-        <v>1572502930.45</v>
+        <v>2565663144.25</v>
       </c>
       <c r="H65" t="n">
-        <v>1541639.23</v>
+        <v>1729718.15</v>
       </c>
       <c r="I65" t="n">
-        <v>16627368.43</v>
+        <v>67797066.25</v>
       </c>
       <c r="J65" t="n">
-        <v>18169007.66</v>
+        <v>69526784.40000001</v>
       </c>
     </row>
     <row r="66">
@@ -2760,34 +2742,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1301</v>
+        <v>1251</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>600547625.35</v>
+        <v>12979474804.25</v>
       </c>
       <c r="F66" t="n">
-        <v>522164709.56</v>
+        <v>12773110420.68</v>
       </c>
       <c r="G66" t="n">
-        <v>444238275.33</v>
+        <v>12732571407.31</v>
       </c>
       <c r="H66" t="n">
-        <v>18353119.53</v>
+        <v>41558515.4</v>
       </c>
       <c r="I66" t="n">
-        <v>36819044.67</v>
+        <v>216807656.75</v>
       </c>
       <c r="J66" t="n">
-        <v>55172164.2</v>
+        <v>258366172.15</v>
       </c>
     </row>
     <row r="67">
@@ -2796,34 +2778,34 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1451</v>
+        <v>1231</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3393511812.13</v>
+        <v>196292319.51</v>
       </c>
       <c r="F67" t="n">
-        <v>3264360914.02</v>
+        <v>192693183.61</v>
       </c>
       <c r="G67" t="n">
-        <v>3238880805.17</v>
+        <v>183911092.06</v>
       </c>
       <c r="H67" t="n">
-        <v>13141756.77</v>
+        <v>926349.9300000001</v>
       </c>
       <c r="I67" t="n">
-        <v>89952770.89</v>
+        <v>4138969.75</v>
       </c>
       <c r="J67" t="n">
-        <v>103094527.66</v>
+        <v>5065319.68</v>
       </c>
     </row>
     <row r="68">
@@ -2832,34 +2814,34 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1371</v>
+        <v>1631</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>181795255.1</v>
+        <v>63665749.64</v>
       </c>
       <c r="F68" t="n">
-        <v>176679835.12</v>
+        <v>39924754.94</v>
       </c>
       <c r="G68" t="n">
-        <v>172435676.13</v>
+        <v>39409640.61</v>
       </c>
       <c r="H68" t="n">
-        <v>4368130.43</v>
+        <v>475922.2</v>
       </c>
       <c r="I68" t="n">
-        <v>4287377.26</v>
+        <v>24058202.1</v>
       </c>
       <c r="J68" t="n">
-        <v>8655507.689999999</v>
+        <v>24534124.3</v>
       </c>
     </row>
     <row r="69">
@@ -2868,34 +2850,34 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1501</v>
+        <v>1271</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>352650653.12</v>
+        <v>71925491.40000001</v>
       </c>
       <c r="F69" t="n">
-        <v>315037665.91</v>
+        <v>70589799.61</v>
       </c>
       <c r="G69" t="n">
-        <v>301346762.92</v>
+        <v>69678332.78</v>
       </c>
       <c r="H69" t="n">
-        <v>19114485.82</v>
+        <v>20181416.68</v>
       </c>
       <c r="I69" t="n">
-        <v>77403990.66</v>
+        <v>10134142.55</v>
       </c>
       <c r="J69" t="n">
-        <v>96518476.48</v>
+        <v>30315559.23</v>
       </c>
     </row>
     <row r="70">
@@ -2904,34 +2886,34 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2211</v>
+        <v>1221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>20189976.4</v>
+        <v>91983736.40000001</v>
       </c>
       <c r="F70" t="n">
-        <v>19470842.74</v>
+        <v>76448925.22</v>
       </c>
       <c r="G70" t="n">
-        <v>18947352.89</v>
+        <v>75856018.97</v>
       </c>
       <c r="H70" t="n">
-        <v>140686.89</v>
+        <v>467.76</v>
       </c>
       <c r="I70" t="n">
-        <v>756689.71</v>
+        <v>10588548.64</v>
       </c>
       <c r="J70" t="n">
-        <v>897376.6</v>
+        <v>10589016.4</v>
       </c>
     </row>
     <row r="71">
@@ -2940,34 +2922,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2351</v>
+        <v>1481</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>464167620.3</v>
+        <v>152723547.84</v>
       </c>
       <c r="F71" t="n">
-        <v>430024005.97</v>
+        <v>140202461.6</v>
       </c>
       <c r="G71" t="n">
-        <v>419107102.61</v>
+        <v>128851499.22</v>
       </c>
       <c r="H71" t="n">
-        <v>380901.69</v>
+        <v>5411868.7</v>
       </c>
       <c r="I71" t="n">
-        <v>13513330.29</v>
+        <v>11509155.9</v>
       </c>
       <c r="J71" t="n">
-        <v>13894231.98</v>
+        <v>16921024.6</v>
       </c>
     </row>
     <row r="72">
@@ -2976,34 +2958,34 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2311</v>
+        <v>1261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>434351243.77</v>
+        <v>16633018692.76</v>
       </c>
       <c r="F72" t="n">
-        <v>412467573.12</v>
+        <v>16079912253.18</v>
       </c>
       <c r="G72" t="n">
-        <v>403987795.94</v>
+        <v>15837680952.16</v>
       </c>
       <c r="H72" t="n">
-        <v>1669347.22</v>
+        <v>585170446.71</v>
       </c>
       <c r="I72" t="n">
-        <v>67683789.95999999</v>
+        <v>757153016.96</v>
       </c>
       <c r="J72" t="n">
-        <v>69353137.18000001</v>
+        <v>1342323463.67</v>
       </c>
     </row>
     <row r="73">
@@ -3012,33 +2994,465 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>SEF</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1191</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1539130234.2</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1488234890.69</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1475159288.69</v>
+      </c>
+      <c r="H73" t="n">
+        <v>10728442.75</v>
+      </c>
+      <c r="I73" t="n">
+        <v>69971290.95999999</v>
+      </c>
+      <c r="J73" t="n">
+        <v>80699733.70999999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SEGOV</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1612507669.42</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1582583713.78</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1572502930.45</v>
+      </c>
+      <c r="H74" t="n">
+        <v>1541639.23</v>
+      </c>
+      <c r="I74" t="n">
+        <v>16627368.43</v>
+      </c>
+      <c r="J74" t="n">
+        <v>18169007.66</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SEINFRA</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>600547625.35</v>
+      </c>
+      <c r="F75" t="n">
+        <v>522164709.56</v>
+      </c>
+      <c r="G75" t="n">
+        <v>444238275.33</v>
+      </c>
+      <c r="H75" t="n">
+        <v>18353119.53</v>
+      </c>
+      <c r="I75" t="n">
+        <v>36819044.67</v>
+      </c>
+      <c r="J75" t="n">
+        <v>55172164.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SEJUSP</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1451</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>3393511812.13</v>
+      </c>
+      <c r="F76" t="n">
+        <v>3264360914.02</v>
+      </c>
+      <c r="G76" t="n">
+        <v>3238880805.17</v>
+      </c>
+      <c r="H76" t="n">
+        <v>13141756.77</v>
+      </c>
+      <c r="I76" t="n">
+        <v>89952770.89</v>
+      </c>
+      <c r="J76" t="n">
+        <v>103094527.66</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SEMAD</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>181795255.1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>176679835.12</v>
+      </c>
+      <c r="G77" t="n">
+        <v>172435676.13</v>
+      </c>
+      <c r="H77" t="n">
+        <v>4368130.43</v>
+      </c>
+      <c r="I77" t="n">
+        <v>4287377.26</v>
+      </c>
+      <c r="J77" t="n">
+        <v>8655507.689999999</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SEPLAG</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>352650653.12</v>
+      </c>
+      <c r="F78" t="n">
+        <v>315037665.91</v>
+      </c>
+      <c r="G78" t="n">
+        <v>301346762.92</v>
+      </c>
+      <c r="H78" t="n">
+        <v>19114485.82</v>
+      </c>
+      <c r="I78" t="n">
+        <v>77403990.66</v>
+      </c>
+      <c r="J78" t="n">
+        <v>96518476.48</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TCEMG</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>946650282.84</v>
+      </c>
+      <c r="F79" t="n">
+        <v>929954367.4</v>
+      </c>
+      <c r="G79" t="n">
+        <v>920990600.27</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>9104244.1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>9104244.1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TJMG</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>7024837395.9</v>
+      </c>
+      <c r="F80" t="n">
+        <v>7024837395.9</v>
+      </c>
+      <c r="G80" t="n">
+        <v>7025414410.5</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>23412.46</v>
+      </c>
+      <c r="J80" t="n">
+        <v>23412.46</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TJMMG</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>86251920.37</v>
+      </c>
+      <c r="F81" t="n">
+        <v>81658327.34999999</v>
+      </c>
+      <c r="G81" t="n">
+        <v>81083119.16</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2549048.16</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2549048.16</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TV MINAS</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2211</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>20189976.4</v>
+      </c>
+      <c r="F82" t="n">
+        <v>19470842.74</v>
+      </c>
+      <c r="G82" t="n">
+        <v>18947352.89</v>
+      </c>
+      <c r="H82" t="n">
+        <v>140686.89</v>
+      </c>
+      <c r="I82" t="n">
+        <v>756689.71</v>
+      </c>
+      <c r="J82" t="n">
+        <v>897376.6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>UEMG</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2351</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>464167620.3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>430024005.97</v>
+      </c>
+      <c r="G83" t="n">
+        <v>419107102.61</v>
+      </c>
+      <c r="H83" t="n">
+        <v>380901.69</v>
+      </c>
+      <c r="I83" t="n">
+        <v>13513330.29</v>
+      </c>
+      <c r="J83" t="n">
+        <v>13894231.98</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>UNIMONTES</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2311</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>434351243.77</v>
+      </c>
+      <c r="F84" t="n">
+        <v>412467573.12</v>
+      </c>
+      <c r="G84" t="n">
+        <v>403987795.94</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1669347.22</v>
+      </c>
+      <c r="I84" t="n">
+        <v>67683789.95999999</v>
+      </c>
+      <c r="J84" t="n">
+        <v>69353137.18000001</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>UTRAMIG</t>
         </is>
       </c>
-      <c r="C73" t="n">
+      <c r="C85" t="n">
         <v>2281</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E85" t="n">
         <v>7453421.77</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F85" t="n">
         <v>7042060.99</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G85" t="n">
         <v>6627633.67</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H85" t="n">
         <v>7006</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I85" t="n">
         <v>1513188.14</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J85" t="n">
         <v>1520194.14</v>
       </c>
     </row>

--- a/upload/orgao2022.xlsx
+++ b/upload/orgao2022.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,10 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Valor Pago Processado</t>
+          <t>Valor Liquidado RP</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Valor Pago Não Processado</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Valor Pago RP</t>
         </is>
@@ -498,21 +493,18 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1222668188.43</v>
+        <v>23765636.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1218515083.13</v>
+        <v>20400012.09</v>
       </c>
       <c r="G2" t="n">
-        <v>998941873.86</v>
+        <v>18849791.93</v>
       </c>
       <c r="H2" t="n">
-        <v>14711108.9</v>
+        <v>5398783.68</v>
       </c>
       <c r="I2" t="n">
-        <v>5367326.43</v>
-      </c>
-      <c r="J2" t="n">
         <v>20078435.33</v>
       </c>
     </row>
@@ -534,23 +526,20 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6030203.98</v>
+        <v>1351766.05</v>
       </c>
       <c r="F3" t="n">
-        <v>5910378.02</v>
+        <v>1239219.05</v>
       </c>
       <c r="G3" t="n">
-        <v>5805259.67</v>
+        <v>1134100.7</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>23923.39</v>
       </c>
       <c r="I3" t="n">
         <v>23921.89</v>
       </c>
-      <c r="J3" t="n">
-        <v>23921.89</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -570,21 +559,18 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1702987288.68</v>
+        <v>133237098.75</v>
       </c>
       <c r="F4" t="n">
-        <v>1579534767.88</v>
+        <v>109680977.95</v>
       </c>
       <c r="G4" t="n">
-        <v>1572939663.08</v>
+        <v>104971231.36</v>
       </c>
       <c r="H4" t="n">
-        <v>2089.8</v>
+        <v>62286664.58</v>
       </c>
       <c r="I4" t="n">
-        <v>61835606.82</v>
-      </c>
-      <c r="J4" t="n">
         <v>61837696.62</v>
       </c>
     </row>
@@ -606,21 +592,18 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3998282.31</v>
+        <v>1912107.1</v>
       </c>
       <c r="F5" t="n">
-        <v>2913330.3</v>
+        <v>837928.8199999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2891473.26</v>
+        <v>815662.5</v>
       </c>
       <c r="H5" t="n">
-        <v>114.72</v>
+        <v>64611.25</v>
       </c>
       <c r="I5" t="n">
-        <v>64611.25</v>
-      </c>
-      <c r="J5" t="n">
         <v>64725.97</v>
       </c>
     </row>
@@ -642,23 +625,20 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15948670.24</v>
+        <v>2798712.83</v>
       </c>
       <c r="F6" t="n">
-        <v>15099248.76</v>
+        <v>1960156.35</v>
       </c>
       <c r="G6" t="n">
-        <v>15008695.06</v>
+        <v>1868426.37</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>745441.99</v>
       </c>
       <c r="I6" t="n">
         <v>744776.36</v>
       </c>
-      <c r="J6" t="n">
-        <v>744776.36</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -678,21 +658,18 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1617069712.19</v>
+        <v>100013319.2</v>
       </c>
       <c r="F7" t="n">
-        <v>1550882048.63</v>
+        <v>34243144.41</v>
       </c>
       <c r="G7" t="n">
-        <v>1547930780.08</v>
+        <v>31439008.83</v>
       </c>
       <c r="H7" t="n">
-        <v>4065273.59</v>
+        <v>46645604.58</v>
       </c>
       <c r="I7" t="n">
-        <v>42151132.62</v>
-      </c>
-      <c r="J7" t="n">
         <v>46216406.21</v>
       </c>
     </row>
@@ -714,23 +691,20 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>55665667.37</v>
+        <v>2135311.92</v>
       </c>
       <c r="F8" t="n">
-        <v>55392655.65</v>
+        <v>1895097.87</v>
       </c>
       <c r="G8" t="n">
-        <v>55212108.02</v>
+        <v>1747322.52</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>244548.03</v>
       </c>
       <c r="I8" t="n">
         <v>239632.61</v>
       </c>
-      <c r="J8" t="n">
-        <v>239632.61</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -750,21 +724,18 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>736345633.02</v>
+        <v>78399388.63</v>
       </c>
       <c r="F9" t="n">
-        <v>718847331.48</v>
+        <v>62941059.59</v>
       </c>
       <c r="G9" t="n">
-        <v>714589715.37</v>
+        <v>58553011.49</v>
       </c>
       <c r="H9" t="n">
-        <v>39893.69</v>
+        <v>8962525.48</v>
       </c>
       <c r="I9" t="n">
-        <v>8604588.82</v>
-      </c>
-      <c r="J9" t="n">
         <v>8644482.51</v>
       </c>
     </row>
@@ -786,21 +757,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2009831554.49</v>
+        <v>1689989737.59</v>
       </c>
       <c r="F10" t="n">
-        <v>1273629898.99</v>
+        <v>956289673.51</v>
       </c>
       <c r="G10" t="n">
-        <v>1248196121.6</v>
+        <v>951559919.87</v>
       </c>
       <c r="H10" t="n">
-        <v>3419688.86</v>
+        <v>168681477.15</v>
       </c>
       <c r="I10" t="n">
-        <v>168251149.94</v>
-      </c>
-      <c r="J10" t="n">
         <v>171670838.8</v>
       </c>
     </row>
@@ -821,22 +789,13 @@
           <t>EGE SEC.FAZENDA-ENCARGOS DIVERSOS</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>12201752803.83</v>
-      </c>
-      <c r="F11" t="n">
-        <v>11477276512.18</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11477261273.86</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>557959.5699999999</v>
+        <v>85722190.14</v>
       </c>
       <c r="I11" t="n">
-        <v>85266341.89</v>
-      </c>
-      <c r="J11" t="n">
         <v>85824301.45999999</v>
       </c>
     </row>
@@ -857,24 +816,15 @@
           <t>EGE-SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>201288736.28</v>
-      </c>
-      <c r="F12" t="n">
-        <v>201288736.28</v>
-      </c>
-      <c r="G12" t="n">
-        <v>201288736.28</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -904,7 +854,6 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -934,7 +883,6 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -942,29 +890,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPAMIG</t>
+          <t>EMG - ADM. DIRETA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3051</v>
+        <v>9999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>119899404.19</v>
-      </c>
-      <c r="F15" t="n">
-        <v>119899404.19</v>
-      </c>
-      <c r="G15" t="n">
-        <v>119899404.19</v>
-      </c>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -972,35 +913,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ESP MG</t>
+          <t>EPAMIG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1541</v>
+        <v>3051</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
+          <t>EMPRESA DE PESQUISA AGROPECUARIA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17601666.31</v>
+        <v>119899404.19</v>
       </c>
       <c r="F16" t="n">
-        <v>17148601.56</v>
+        <v>119899404.19</v>
       </c>
       <c r="G16" t="n">
-        <v>16887894.92</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>256633.48</v>
-      </c>
-      <c r="J16" t="n">
-        <v>256633.48</v>
-      </c>
+        <v>119899404.19</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1008,34 +942,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAHMEMG</t>
+          <t>ESP MG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4541</v>
+        <v>1541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
+          <t>ESCOLA DE SAUDE PUBLICA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>315895.03</v>
+        <v>3569749.45</v>
       </c>
       <c r="F17" t="n">
-        <v>315480.44</v>
+        <v>3128439.7</v>
       </c>
       <c r="G17" t="n">
-        <v>315480.44</v>
+        <v>2867741.32</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>276416.92</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
+        <v>256633.48</v>
       </c>
     </row>
     <row r="18">
@@ -1044,34 +975,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FAOP</t>
+          <t>FAHMEMG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2171</v>
+        <v>4541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
+          <t>FUNDO DE APOIO HABITACIONAL AOS MILITARES DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4662678.05</v>
+        <v>315895.03</v>
       </c>
       <c r="F18" t="n">
-        <v>4296034.19</v>
+        <v>315480.44</v>
       </c>
       <c r="G18" t="n">
-        <v>4144793.59</v>
+        <v>315480.44</v>
       </c>
       <c r="H18" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>13446.09</v>
-      </c>
-      <c r="J18" t="n">
-        <v>13513.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1080,34 +1008,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FAPEMIG</t>
+          <t>FAOP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2071</v>
+        <v>2171</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO DE ARTE DE OURO PRETO</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>455083279.96</v>
+        <v>1283870.09</v>
       </c>
       <c r="F19" t="n">
-        <v>442616854.91</v>
+        <v>1112298.27</v>
       </c>
       <c r="G19" t="n">
-        <v>429159889.95</v>
+        <v>978942.47</v>
       </c>
       <c r="H19" t="n">
-        <v>50484697.07</v>
+        <v>13446.09</v>
       </c>
       <c r="I19" t="n">
-        <v>12791969.37</v>
-      </c>
-      <c r="J19" t="n">
-        <v>63276666.44</v>
+        <v>13513.59</v>
       </c>
     </row>
     <row r="20">
@@ -1116,34 +1041,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>FAPEMIG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2181</v>
+        <v>2071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FUNDACAO CLOVIS SALGADO</t>
+          <t>FUNDACAO DE AMPARO A PESQUISA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>44939828.32</v>
+        <v>23231608.24</v>
       </c>
       <c r="F20" t="n">
-        <v>43912375.76</v>
+        <v>21540373.48</v>
       </c>
       <c r="G20" t="n">
-        <v>43171411.16</v>
+        <v>20555687.85</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>12810372.02</v>
       </c>
       <c r="I20" t="n">
-        <v>418535.58</v>
-      </c>
-      <c r="J20" t="n">
-        <v>418535.58</v>
+        <v>63276666.44</v>
       </c>
     </row>
     <row r="21">
@@ -1152,29 +1074,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FDM</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4331</v>
+        <v>2181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
+          <t>FUNDACAO CLOVIS SALGADO</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>147406.89</v>
+        <v>8994021.960000001</v>
       </c>
       <c r="F21" t="n">
-        <v>147406.89</v>
+        <v>8122065.16</v>
       </c>
       <c r="G21" t="n">
-        <v>143721.71</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>7401477.83</v>
+      </c>
+      <c r="H21" t="n">
+        <v>423614.13</v>
+      </c>
+      <c r="I21" t="n">
+        <v>418535.58</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1182,35 +1107,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FEAM</t>
+          <t>FDM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2091</v>
+        <v>4331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
+          <t>FUNDO DE DESENVOLVIMENTO METROPOLITANO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>41540382.17</v>
+        <v>147406.89</v>
       </c>
       <c r="F22" t="n">
-        <v>41283632.97</v>
+        <v>147406.89</v>
       </c>
       <c r="G22" t="n">
-        <v>40766476.92</v>
-      </c>
-      <c r="H22" t="n">
-        <v>27692.5</v>
-      </c>
-      <c r="I22" t="n">
-        <v>11647.71</v>
-      </c>
-      <c r="J22" t="n">
-        <v>39340.21</v>
-      </c>
+        <v>143721.71</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1218,34 +1136,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FEAS</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4251</v>
+        <v>2091</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+          <t>FUNDACAO ESTADUAL DO MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>207531660.9</v>
+        <v>3925374.57</v>
       </c>
       <c r="F23" t="n">
-        <v>189241489.7</v>
+        <v>3674244.79</v>
       </c>
       <c r="G23" t="n">
-        <v>187462418.98</v>
+        <v>3480939.71</v>
       </c>
       <c r="H23" t="n">
-        <v>98887758.56999999</v>
+        <v>11668.51</v>
       </c>
       <c r="I23" t="n">
-        <v>4684458.53</v>
-      </c>
-      <c r="J23" t="n">
-        <v>103572217.1</v>
+        <v>39340.21</v>
       </c>
     </row>
     <row r="24">
@@ -1254,34 +1169,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FEC</t>
+          <t>FEAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4491</v>
+        <v>4251</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE CULTURA</t>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>12198756.32</v>
+        <v>4763896.86</v>
       </c>
       <c r="F24" t="n">
-        <v>12198756.32</v>
+        <v>3922365.6</v>
       </c>
       <c r="G24" t="n">
-        <v>9336561.16</v>
+        <v>3280099.73</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4718486.66</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
+        <v>103572217.1</v>
       </c>
     </row>
     <row r="25">
@@ -1290,34 +1202,25 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FEH</t>
+          <t>FEC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4101</v>
+        <v>4491</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE HABITACAO</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>17493925.29</v>
-      </c>
-      <c r="F25" t="n">
-        <v>16080240.21</v>
-      </c>
-      <c r="G25" t="n">
-        <v>16080240.21</v>
-      </c>
+          <t>FUNDO ESTADUAL DE CULTURA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>517189.73</v>
-      </c>
-      <c r="J25" t="n">
-        <v>517189.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1326,34 +1229,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FEI</t>
+          <t>FEH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4601</v>
+        <v>4101</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>464551.64</v>
-      </c>
-      <c r="F26" t="n">
-        <v>419551.64</v>
-      </c>
-      <c r="G26" t="n">
-        <v>239551.64</v>
-      </c>
+          <t>FUNDO ESTADUAL DE HABITACAO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>80000</v>
+        <v>517189.73</v>
       </c>
       <c r="I26" t="n">
-        <v>80000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>160000</v>
+        <v>517189.73</v>
       </c>
     </row>
     <row r="27">
@@ -1362,34 +1256,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FEPDC</t>
+          <t>FEI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4451</v>
+        <v>4601</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>11107774.68</v>
-      </c>
-      <c r="F27" t="n">
-        <v>10032800.23</v>
-      </c>
-      <c r="G27" t="n">
-        <v>9730140.449999999</v>
-      </c>
+          <t>FUNDO ESTADUAL DOS DIREITOS DO IDOSO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="I27" t="n">
-        <v>2888273.21</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2888273.21</v>
+        <v>160000</v>
       </c>
     </row>
     <row r="28">
@@ -1398,34 +1283,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FEPJ</t>
+          <t>FEPDC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4031</v>
+        <v>4451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE PROTECAO E DEFESA DO CONSUMIDOR</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1386896516.13</v>
+        <v>4755569.47</v>
       </c>
       <c r="F28" t="n">
-        <v>1145911266.98</v>
+        <v>3877498.44</v>
       </c>
       <c r="G28" t="n">
-        <v>1050692519.56</v>
+        <v>3567017.8</v>
       </c>
       <c r="H28" t="n">
-        <v>1272370.64</v>
+        <v>2913082.12</v>
       </c>
       <c r="I28" t="n">
-        <v>93340728.53</v>
-      </c>
-      <c r="J28" t="n">
-        <v>94613099.17</v>
+        <v>2888273.21</v>
       </c>
     </row>
     <row r="29">
@@ -1434,34 +1316,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FES</t>
+          <t>FEPJ</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4291</v>
+        <v>4031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SAUDE</t>
+          <t>FUNDO ESPECIAL DO PODER JUDICIARIO DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>10255262090.27</v>
+        <v>1097243253.81</v>
       </c>
       <c r="F29" t="n">
-        <v>9575510065.219999</v>
+        <v>892588504.35</v>
       </c>
       <c r="G29" t="n">
-        <v>9231614379.459999</v>
+        <v>798435706.1799999</v>
       </c>
       <c r="H29" t="n">
-        <v>554014631.28</v>
+        <v>102316856.45</v>
       </c>
       <c r="I29" t="n">
-        <v>786454402.1799999</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1340469033.46</v>
+        <v>94613099.17</v>
       </c>
     </row>
     <row r="30">
@@ -1470,34 +1349,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FESP-MG</t>
+          <t>FES</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4691</v>
+        <v>4291</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>25338987.88</v>
+        <v>1032259597.29</v>
       </c>
       <c r="F30" t="n">
-        <v>11474135.71</v>
+        <v>553007551.9</v>
       </c>
       <c r="G30" t="n">
-        <v>9347783.02</v>
+        <v>508694819.65</v>
       </c>
       <c r="H30" t="n">
-        <v>1094891.98</v>
+        <v>793236335.1</v>
       </c>
       <c r="I30" t="n">
-        <v>4039900.86</v>
-      </c>
-      <c r="J30" t="n">
-        <v>5134792.84</v>
+        <v>1340469033.46</v>
       </c>
     </row>
     <row r="31">
@@ -1506,34 +1382,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FET-MG</t>
+          <t>FESP-MG</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4701</v>
+        <v>4691</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DE SEGURANCA PUBLICA DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3542540.26</v>
+        <v>25338987.88</v>
       </c>
       <c r="F31" t="n">
-        <v>4264.26</v>
+        <v>11474135.71</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>9347783.02</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4068541.03</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
+        <v>5134792.84</v>
       </c>
     </row>
     <row r="32">
@@ -1542,34 +1415,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FFP - MG</t>
+          <t>FET-MG</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4711</v>
+        <v>4701</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO ESTADUAL DO TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>15325406751.49</v>
+        <v>3542540.26</v>
       </c>
       <c r="F32" t="n">
-        <v>15323499427.6</v>
+        <v>4264.26</v>
       </c>
       <c r="G32" t="n">
-        <v>15328734230.09</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>79198.5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>79198.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1578,34 +1448,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FHA</t>
+          <t>FFP - MG</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2151</v>
+        <v>4711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FUNDACAO HELENA ANTIPOFF</t>
+          <t>FUNDO FINANCEIRO DE PREVIDENCIA DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>54848300.42</v>
+        <v>6396230.71</v>
       </c>
       <c r="F33" t="n">
-        <v>50479779.7</v>
+        <v>4630617.95</v>
       </c>
       <c r="G33" t="n">
-        <v>50120409.8</v>
+        <v>4345094.44</v>
       </c>
       <c r="H33" t="n">
-        <v>4125</v>
+        <v>79198.5</v>
       </c>
       <c r="I33" t="n">
-        <v>6086840.51</v>
-      </c>
-      <c r="J33" t="n">
-        <v>6090965.51</v>
+        <v>79198.5</v>
       </c>
     </row>
     <row r="34">
@@ -1614,34 +1481,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FHEMIG</t>
+          <t>FHA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2271</v>
+        <v>2151</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO HELENA ANTIPOFF</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2277629071.19</v>
+        <v>17060683.72</v>
       </c>
       <c r="F34" t="n">
-        <v>2165324017.21</v>
+        <v>12898785.62</v>
       </c>
       <c r="G34" t="n">
-        <v>2143497567.57</v>
+        <v>12538798.11</v>
       </c>
       <c r="H34" t="n">
-        <v>3753299.71</v>
+        <v>6179376.53</v>
       </c>
       <c r="I34" t="n">
-        <v>42680567.96</v>
-      </c>
-      <c r="J34" t="n">
-        <v>46433867.67</v>
+        <v>6090965.51</v>
       </c>
     </row>
     <row r="35">
@@ -1650,34 +1514,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FHIDRO</t>
+          <t>FHEMIG</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4341</v>
+        <v>2271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
+          <t>FUNDACAO HOSPITALAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2866852.09</v>
+        <v>561221285.0700001</v>
       </c>
       <c r="F35" t="n">
-        <v>2778584.69</v>
+        <v>452006475.89</v>
       </c>
       <c r="G35" t="n">
-        <v>2557135.68</v>
+        <v>431501613.65</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>43084138.41</v>
       </c>
       <c r="I35" t="n">
-        <v>129135.76</v>
-      </c>
-      <c r="J35" t="n">
-        <v>129135.76</v>
+        <v>46433867.67</v>
       </c>
     </row>
     <row r="36">
@@ -1686,34 +1547,31 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FJP</t>
+          <t>FHIDRO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2061</v>
+        <v>4341</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FUNDACAO JOAO PINHEIRO</t>
+          <t>FUNDO DE RECUPERACAO, PROTECAO E DESENVOLVIMENTO SUSTENTAVEL DAS BACIAS HIDROGRAFICAS DO ESTADO DE M</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>64511960.77</v>
+        <v>2235564.89</v>
       </c>
       <c r="F36" t="n">
-        <v>58152640.77</v>
+        <v>2147315.97</v>
       </c>
       <c r="G36" t="n">
-        <v>56790483.53</v>
+        <v>1978171.96</v>
       </c>
       <c r="H36" t="n">
-        <v>141507.05</v>
+        <v>143743.13</v>
       </c>
       <c r="I36" t="n">
-        <v>1655021.81</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1796528.86</v>
+        <v>129135.76</v>
       </c>
     </row>
     <row r="37">
@@ -1722,34 +1580,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FPE</t>
+          <t>FIA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4141</v>
+        <v>4091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FUNDO PENITENCIARIO ESTADUAL</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>31245732.35</v>
-      </c>
-      <c r="F37" t="n">
-        <v>13353865.57</v>
-      </c>
-      <c r="G37" t="n">
-        <v>13353865.57</v>
-      </c>
+          <t>FUNDO PARA A INFANCIA E A ADOLESCENCIA</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>1574.5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>5560409.71</v>
-      </c>
-      <c r="J37" t="n">
-        <v>5561984.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1758,34 +1607,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FPP - MG</t>
+          <t>FJP</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4631</v>
+        <v>2061</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
+          <t>FUNDACAO JOAO PINHEIRO</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>386159674.85</v>
+        <v>13727664.04</v>
       </c>
       <c r="F38" t="n">
-        <v>248996997.66</v>
+        <v>7589126.46</v>
       </c>
       <c r="G38" t="n">
-        <v>238193664.04</v>
+        <v>6317822.9</v>
       </c>
       <c r="H38" t="n">
-        <v>275729.74</v>
+        <v>1678268.39</v>
       </c>
       <c r="I38" t="n">
-        <v>15778864.88</v>
-      </c>
-      <c r="J38" t="n">
-        <v>16054594.62</v>
+        <v>1796528.86</v>
       </c>
     </row>
     <row r="39">
@@ -1794,34 +1640,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FUCAM</t>
+          <t>FPE</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2161</v>
+        <v>4141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
+          <t>FUNDO PENITENCIARIO ESTADUAL</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>16628991.48</v>
+        <v>28805721.36</v>
       </c>
       <c r="F39" t="n">
-        <v>15101587.53</v>
+        <v>10923395.75</v>
       </c>
       <c r="G39" t="n">
-        <v>14946425.03</v>
+        <v>10923395.75</v>
       </c>
       <c r="H39" t="n">
-        <v>15535.07</v>
+        <v>5560409.71</v>
       </c>
       <c r="I39" t="n">
-        <v>2608678.68</v>
-      </c>
-      <c r="J39" t="n">
-        <v>2624213.75</v>
+        <v>5561984.21</v>
       </c>
     </row>
     <row r="40">
@@ -1830,34 +1673,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FUNAPEC</t>
+          <t>FPP - MG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4551</v>
+        <v>4631</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDO DE PAGAMENTO DE PARCERIAS PUBLICO - PRIVADAS DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>161975565.86</v>
+        <v>377565140</v>
       </c>
       <c r="F40" t="n">
-        <v>161973985.31</v>
+        <v>240402462.81</v>
       </c>
       <c r="G40" t="n">
-        <v>155079704.45</v>
+        <v>229599129.19</v>
       </c>
       <c r="H40" t="n">
-        <v>12273523.84</v>
+        <v>18724455.95</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>12273523.84</v>
+        <v>16054594.62</v>
       </c>
     </row>
     <row r="41">
@@ -1866,29 +1706,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FUNCONTAS</t>
+          <t>FUCAM</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4611</v>
+        <v>2161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FUNDO DO TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO EDUCACIONAL CAIO MARTINS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>24587.7</v>
+        <v>6501656.71</v>
       </c>
       <c r="F41" t="n">
-        <v>24587.7</v>
+        <v>5022654.53</v>
       </c>
       <c r="G41" t="n">
-        <v>24587.7</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+        <v>4866587.56</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2609180</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2624213.75</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1896,29 +1739,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FUNDHAB</t>
+          <t>FUNAPEC</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4121</v>
+        <v>4551</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FUNDO DE APOIO HABITACIONAL DA ASSEMBLEIA LEGISLATIVA DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>4983186.54</v>
-      </c>
-      <c r="F42" t="n">
-        <v>3723186.54</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3456207.79</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>FUNDO DE ASSISTENCIA AO PECULIO DOS SERVIDORES DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>12273523.84</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1937,24 +1777,15 @@
           <t>FUNDO ESTADUAL DE DEFESA DE DIREITOS DIFUSOS</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>1278479.27</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1278479.27</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1278479.27</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1974,21 +1805,18 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>319786910.28</v>
+        <v>177641088.74</v>
       </c>
       <c r="F44" t="n">
-        <v>263858227.88</v>
+        <v>121802374.36</v>
       </c>
       <c r="G44" t="n">
-        <v>252638336.78</v>
+        <v>110701730.99</v>
       </c>
       <c r="H44" t="n">
-        <v>101930917.99</v>
+        <v>47392367.92</v>
       </c>
       <c r="I44" t="n">
-        <v>47063914.03</v>
-      </c>
-      <c r="J44" t="n">
         <v>148994832.02</v>
       </c>
     </row>
@@ -2010,21 +1838,18 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>24443811.21</v>
+        <v>17705705.22</v>
       </c>
       <c r="F45" t="n">
-        <v>13265445.69</v>
+        <v>7401992.66</v>
       </c>
       <c r="G45" t="n">
-        <v>13119045.05</v>
+        <v>7367137.4</v>
       </c>
       <c r="H45" t="n">
-        <v>99860.64</v>
+        <v>7150934.82</v>
       </c>
       <c r="I45" t="n">
-        <v>7087195.69</v>
-      </c>
-      <c r="J45" t="n">
         <v>7187056.33</v>
       </c>
     </row>
@@ -2046,23 +1871,20 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>140227334.65</v>
+        <v>125599975.61</v>
       </c>
       <c r="F46" t="n">
-        <v>53251682.01</v>
+        <v>39021493.78</v>
       </c>
       <c r="G46" t="n">
-        <v>52665792.69</v>
+        <v>38435604.46</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>6046080.35</v>
       </c>
       <c r="I46" t="n">
         <v>5954269.9</v>
       </c>
-      <c r="J46" t="n">
-        <v>5954269.9</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2082,21 +1904,18 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>41468457.48</v>
+        <v>28253309.75</v>
       </c>
       <c r="F47" t="n">
-        <v>36393685.24</v>
+        <v>23220547.45</v>
       </c>
       <c r="G47" t="n">
-        <v>35762406.77</v>
+        <v>22507529.52</v>
       </c>
       <c r="H47" t="n">
-        <v>4065417.18</v>
+        <v>2247684.09</v>
       </c>
       <c r="I47" t="n">
-        <v>2244249.52</v>
-      </c>
-      <c r="J47" t="n">
         <v>6309666.7</v>
       </c>
     </row>
@@ -2117,22 +1936,13 @@
           <t>GESTAO DA DIVIDA PUBLICA ESTADUAL</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>5700229349.95</v>
-      </c>
-      <c r="F48" t="n">
-        <v>5577199638.67</v>
-      </c>
-      <c r="G48" t="n">
-        <v>5517860023.27</v>
-      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>28843343.77</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
         <v>28843343.77</v>
       </c>
     </row>
@@ -2154,21 +1964,18 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>333195770.76</v>
+        <v>138574675.09</v>
       </c>
       <c r="F49" t="n">
-        <v>296763683.46</v>
+        <v>102782768.16</v>
       </c>
       <c r="G49" t="n">
-        <v>290862823.02</v>
+        <v>97173035.93000001</v>
       </c>
       <c r="H49" t="n">
-        <v>255386.81</v>
+        <v>25872902.05</v>
       </c>
       <c r="I49" t="n">
-        <v>25746888.77</v>
-      </c>
-      <c r="J49" t="n">
         <v>26002275.58</v>
       </c>
     </row>
@@ -2190,21 +1997,18 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53060472.47</v>
+        <v>31177960.43</v>
       </c>
       <c r="F50" t="n">
-        <v>46263655.96</v>
+        <v>24494770.26</v>
       </c>
       <c r="G50" t="n">
-        <v>45692556.63</v>
+        <v>23916904.58</v>
       </c>
       <c r="H50" t="n">
-        <v>976681.46</v>
+        <v>14112597.52</v>
       </c>
       <c r="I50" t="n">
-        <v>14019630.84</v>
-      </c>
-      <c r="J50" t="n">
         <v>14996312.3</v>
       </c>
     </row>
@@ -2226,21 +2030,18 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>195536444.95</v>
+        <v>55468092.22</v>
       </c>
       <c r="F51" t="n">
-        <v>190876690.89</v>
+        <v>51169391.17</v>
       </c>
       <c r="G51" t="n">
-        <v>183865965.58</v>
+        <v>44274699.3</v>
       </c>
       <c r="H51" t="n">
-        <v>1981216.45</v>
+        <v>3535910.73</v>
       </c>
       <c r="I51" t="n">
-        <v>3389073.5</v>
-      </c>
-      <c r="J51" t="n">
         <v>5370289.95</v>
       </c>
     </row>
@@ -2262,23 +2063,20 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>24595717.43</v>
+        <v>8326698.16</v>
       </c>
       <c r="F52" t="n">
-        <v>20047336.04</v>
+        <v>3834352.32</v>
       </c>
       <c r="G52" t="n">
-        <v>19187028.92</v>
+        <v>3507389.67</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>947597.29</v>
       </c>
       <c r="I52" t="n">
         <v>934662.77</v>
       </c>
-      <c r="J52" t="n">
-        <v>934662.77</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2298,21 +2096,18 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>69270924.79000001</v>
+        <v>10110511.33</v>
       </c>
       <c r="F53" t="n">
-        <v>64810240.33</v>
+        <v>5840125.37</v>
       </c>
       <c r="G53" t="n">
-        <v>64595191.74</v>
+        <v>5669993.32</v>
       </c>
       <c r="H53" t="n">
-        <v>10437314.16</v>
+        <v>1589539.57</v>
       </c>
       <c r="I53" t="n">
-        <v>1573915.38</v>
-      </c>
-      <c r="J53" t="n">
         <v>12011229.54</v>
       </c>
     </row>
@@ -2334,21 +2129,18 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>265147788.61</v>
+        <v>42302160.36</v>
       </c>
       <c r="F54" t="n">
-        <v>260504964.97</v>
+        <v>37971876.05</v>
       </c>
       <c r="G54" t="n">
-        <v>260025427.44</v>
+        <v>37132672.08</v>
       </c>
       <c r="H54" t="n">
-        <v>11259.94</v>
+        <v>7052658.61</v>
       </c>
       <c r="I54" t="n">
-        <v>7021591.43</v>
-      </c>
-      <c r="J54" t="n">
         <v>7032851.37</v>
       </c>
     </row>
@@ -2370,21 +2162,18 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>26902206.65</v>
+        <v>7963841.61</v>
       </c>
       <c r="F55" t="n">
-        <v>26685069.71</v>
+        <v>7766326.61</v>
       </c>
       <c r="G55" t="n">
-        <v>26064598.71</v>
+        <v>7008731.47</v>
       </c>
       <c r="H55" t="n">
-        <v>333694.72</v>
+        <v>524209.51</v>
       </c>
       <c r="I55" t="n">
-        <v>520848.74</v>
-      </c>
-      <c r="J55" t="n">
         <v>854543.46</v>
       </c>
     </row>
@@ -2416,7 +2205,6 @@
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2436,21 +2224,18 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1536739486.14</v>
+        <v>237644608.21</v>
       </c>
       <c r="F57" t="n">
-        <v>1341247986.54</v>
+        <v>190525637.34</v>
       </c>
       <c r="G57" t="n">
-        <v>1307994655.9</v>
+        <v>182524591.15</v>
       </c>
       <c r="H57" t="n">
-        <v>423878.41</v>
+        <v>129729704.01</v>
       </c>
       <c r="I57" t="n">
-        <v>127022888.49</v>
-      </c>
-      <c r="J57" t="n">
         <v>127446766.9</v>
       </c>
     </row>
@@ -2472,21 +2257,18 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2732447147.53</v>
+        <v>92192417.89</v>
       </c>
       <c r="F58" t="n">
-        <v>2675654178.82</v>
+        <v>84286846.88</v>
       </c>
       <c r="G58" t="n">
-        <v>2000806584.11</v>
+        <v>78731830.95</v>
       </c>
       <c r="H58" t="n">
-        <v>94866365.34999999</v>
+        <v>68752644.13</v>
       </c>
       <c r="I58" t="n">
-        <v>67386629.63</v>
-      </c>
-      <c r="J58" t="n">
         <v>162252994.98</v>
       </c>
     </row>
@@ -2508,23 +2290,20 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>32289616.85</v>
+        <v>7518121.57</v>
       </c>
       <c r="F59" t="n">
-        <v>30153432.18</v>
+        <v>5586308.31</v>
       </c>
       <c r="G59" t="n">
-        <v>29578426.34</v>
+        <v>5158102.1</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>696298.45</v>
       </c>
       <c r="I59" t="n">
         <v>671682.59</v>
       </c>
-      <c r="J59" t="n">
-        <v>671682.59</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2544,21 +2323,18 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6761105.25</v>
+        <v>137533.56</v>
       </c>
       <c r="F60" t="n">
-        <v>5938379.6</v>
+        <v>126277.57</v>
       </c>
       <c r="G60" t="n">
-        <v>5925515.6</v>
+        <v>125214.06</v>
       </c>
       <c r="H60" t="n">
-        <v>4598.79</v>
+        <v>1297056.39</v>
       </c>
       <c r="I60" t="n">
-        <v>1296981.73</v>
-      </c>
-      <c r="J60" t="n">
         <v>1301580.52</v>
       </c>
     </row>
@@ -2568,29 +2344,32 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MG INVESTE</t>
+          <t>OGE</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4621</v>
+        <v>1101</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FUNDO DE INVESTIMENTO DO ESTADO DE MINAS GERAIS</t>
+          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>88898823.3</v>
+        <v>1839414.66</v>
       </c>
       <c r="F61" t="n">
-        <v>88898823.3</v>
+        <v>1535055.67</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+        <v>1445994.39</v>
+      </c>
+      <c r="H61" t="n">
+        <v>37130.63</v>
+      </c>
+      <c r="I61" t="n">
+        <v>36247.74</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2598,34 +2377,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OGE</t>
+          <t>PARTICIPAÇÃO EMPRESAS</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1101</v>
+        <v>1915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>OUVIDORIA-GERAL DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>12148887.19</v>
-      </c>
-      <c r="F62" t="n">
-        <v>11844528.2</v>
-      </c>
-      <c r="G62" t="n">
-        <v>11757162.48</v>
-      </c>
+          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>28198078.12</v>
       </c>
       <c r="I62" t="n">
-        <v>36247.74</v>
-      </c>
-      <c r="J62" t="n">
-        <v>36247.74</v>
+        <v>28198078.12</v>
       </c>
     </row>
     <row r="63">
@@ -2634,34 +2404,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PARTICIPAÇÃO EMPRESAS</t>
+          <t>PCMG</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1915</v>
+        <v>1511</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PARTICIPACAO NO AUMENTO DO CAPITAL SOCIAL DE EMPRESAS</t>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1045679146.33</v>
+        <v>379867671.74</v>
       </c>
       <c r="F63" t="n">
-        <v>525455877.98</v>
+        <v>290951910.46</v>
       </c>
       <c r="G63" t="n">
-        <v>525455877.98</v>
+        <v>272762315.12</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>62889882.79</v>
       </c>
       <c r="I63" t="n">
-        <v>28198078.12</v>
-      </c>
-      <c r="J63" t="n">
-        <v>28198078.12</v>
+        <v>79474224.05</v>
       </c>
     </row>
     <row r="64">
@@ -2670,34 +2437,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PCMG</t>
+          <t>PGJ</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1511</v>
+        <v>1091</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+          <t>PROCURADORIA GERAL DE JUSTICA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3185868726.65</v>
+        <v>232242672.44</v>
       </c>
       <c r="F64" t="n">
-        <v>3092549019.47</v>
+        <v>166619237.73</v>
       </c>
       <c r="G64" t="n">
-        <v>3072423500.15</v>
+        <v>148991914.51</v>
       </c>
       <c r="H64" t="n">
-        <v>18094662.5</v>
+        <v>70766965.81</v>
       </c>
       <c r="I64" t="n">
-        <v>61379561.55</v>
-      </c>
-      <c r="J64" t="n">
-        <v>79474224.05</v>
+        <v>69526784.40000001</v>
       </c>
     </row>
     <row r="65">
@@ -2706,34 +2470,31 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PGJ</t>
+          <t>PMMG</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1091</v>
+        <v>1251</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PROCURADORIA GERAL DE JUSTICA</t>
+          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2663990411.98</v>
+        <v>555891431.41</v>
       </c>
       <c r="F65" t="n">
-        <v>2583438879.85</v>
+        <v>352216556.9</v>
       </c>
       <c r="G65" t="n">
-        <v>2565663144.25</v>
+        <v>311744475.76</v>
       </c>
       <c r="H65" t="n">
-        <v>1729718.15</v>
+        <v>219134121.2</v>
       </c>
       <c r="I65" t="n">
-        <v>67797066.25</v>
-      </c>
-      <c r="J65" t="n">
-        <v>69526784.40000001</v>
+        <v>258366172.15</v>
       </c>
     </row>
     <row r="66">
@@ -2742,34 +2503,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PMMG</t>
+          <t>SEAPA</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1251</v>
+        <v>1231</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>POLICIA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>12979474804.25</v>
+        <v>20670847.17</v>
       </c>
       <c r="F66" t="n">
-        <v>12773110420.68</v>
+        <v>17144350.93</v>
       </c>
       <c r="G66" t="n">
-        <v>12732571407.31</v>
+        <v>16145641.17</v>
       </c>
       <c r="H66" t="n">
-        <v>41558515.4</v>
+        <v>4159175.34</v>
       </c>
       <c r="I66" t="n">
-        <v>216807656.75</v>
-      </c>
-      <c r="J66" t="n">
-        <v>258366172.15</v>
+        <v>5065319.68</v>
       </c>
     </row>
     <row r="67">
@@ -2778,34 +2536,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SEAPA</t>
+          <t>SEC. GERAL</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1231</v>
+        <v>1631</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO - SEAPA</t>
+          <t>SECRETARIA-GERAL</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>196292319.51</v>
+        <v>49385698.22</v>
       </c>
       <c r="F67" t="n">
-        <v>192693183.61</v>
+        <v>25644703.52</v>
       </c>
       <c r="G67" t="n">
-        <v>183911092.06</v>
+        <v>25090164.81</v>
       </c>
       <c r="H67" t="n">
-        <v>926349.9300000001</v>
+        <v>24276861.98</v>
       </c>
       <c r="I67" t="n">
-        <v>4138969.75</v>
-      </c>
-      <c r="J67" t="n">
-        <v>5065319.68</v>
+        <v>24534124.3</v>
       </c>
     </row>
     <row r="68">
@@ -2814,34 +2569,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SEC. GERAL</t>
+          <t>SECULT</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1631</v>
+        <v>1271</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>SECRETARIA-GERAL</t>
+          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>63665749.64</v>
+        <v>12099399.85</v>
       </c>
       <c r="F68" t="n">
-        <v>39924754.94</v>
+        <v>10851357.37</v>
       </c>
       <c r="G68" t="n">
-        <v>39409640.61</v>
+        <v>10010247.73</v>
       </c>
       <c r="H68" t="n">
-        <v>475922.2</v>
+        <v>10351021.08</v>
       </c>
       <c r="I68" t="n">
-        <v>24058202.1</v>
-      </c>
-      <c r="J68" t="n">
-        <v>24534124.3</v>
+        <v>30315559.23</v>
       </c>
     </row>
     <row r="69">
@@ -2850,34 +2602,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SECULT</t>
+          <t>SEDE</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1271</v>
+        <v>1221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE CULTURA E TURISMO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>71925491.40000001</v>
+        <v>20002964.78</v>
       </c>
       <c r="F69" t="n">
-        <v>70589799.61</v>
+        <v>8502576.57</v>
       </c>
       <c r="G69" t="n">
-        <v>69678332.78</v>
+        <v>8191194.69</v>
       </c>
       <c r="H69" t="n">
-        <v>20181416.68</v>
+        <v>10628428</v>
       </c>
       <c r="I69" t="n">
-        <v>10134142.55</v>
-      </c>
-      <c r="J69" t="n">
-        <v>30315559.23</v>
+        <v>10589016.4</v>
       </c>
     </row>
     <row r="70">
@@ -2886,34 +2635,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SEDE</t>
+          <t>SEDESE</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1221</v>
+        <v>1481</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>91983736.40000001</v>
+        <v>24429089.33</v>
       </c>
       <c r="F70" t="n">
-        <v>76448925.22</v>
+        <v>14010597.51</v>
       </c>
       <c r="G70" t="n">
-        <v>75856018.97</v>
+        <v>12973326.96</v>
       </c>
       <c r="H70" t="n">
-        <v>467.76</v>
+        <v>11627564.1</v>
       </c>
       <c r="I70" t="n">
-        <v>10588548.64</v>
-      </c>
-      <c r="J70" t="n">
-        <v>10589016.4</v>
+        <v>16921024.6</v>
       </c>
     </row>
     <row r="71">
@@ -2922,34 +2668,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SEDESE</t>
+          <t>SEE</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1481</v>
+        <v>1261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>152723547.84</v>
+        <v>1239874173.32</v>
       </c>
       <c r="F71" t="n">
-        <v>140202461.6</v>
+        <v>821976509.21</v>
       </c>
       <c r="G71" t="n">
-        <v>128851499.22</v>
+        <v>794321116.6900001</v>
       </c>
       <c r="H71" t="n">
-        <v>5411868.7</v>
+        <v>787335318.1799999</v>
       </c>
       <c r="I71" t="n">
-        <v>11509155.9</v>
-      </c>
-      <c r="J71" t="n">
-        <v>16921024.6</v>
+        <v>1342323463.67</v>
       </c>
     </row>
     <row r="72">
@@ -2958,34 +2701,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SEE</t>
+          <t>SEF</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1261</v>
+        <v>1191</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE EDUCACAO</t>
+          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>16633018692.76</v>
+        <v>178037040.29</v>
       </c>
       <c r="F72" t="n">
-        <v>16079912253.18</v>
+        <v>137512463.11</v>
       </c>
       <c r="G72" t="n">
-        <v>15837680952.16</v>
+        <v>124831643.83</v>
       </c>
       <c r="H72" t="n">
-        <v>585170446.71</v>
+        <v>72365852.34</v>
       </c>
       <c r="I72" t="n">
-        <v>757153016.96</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1342323463.67</v>
+        <v>80699733.70999999</v>
       </c>
     </row>
     <row r="73">
@@ -2994,34 +2734,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SEF</t>
+          <t>SEGOV</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1191</v>
+        <v>1491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE FAZENDA</t>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1539130234.2</v>
+        <v>16735574.35</v>
       </c>
       <c r="F73" t="n">
-        <v>1488234890.69</v>
+        <v>15541855.4</v>
       </c>
       <c r="G73" t="n">
-        <v>1475159288.69</v>
+        <v>13739229.52</v>
       </c>
       <c r="H73" t="n">
-        <v>10728442.75</v>
+        <v>17454327.44</v>
       </c>
       <c r="I73" t="n">
-        <v>69971290.95999999</v>
-      </c>
-      <c r="J73" t="n">
-        <v>80699733.70999999</v>
+        <v>18169007.66</v>
       </c>
     </row>
     <row r="74">
@@ -3030,34 +2767,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SEGOV</t>
+          <t>SEINFRA</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1491</v>
+        <v>1301</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1612507669.42</v>
+        <v>113959402.06</v>
       </c>
       <c r="F74" t="n">
-        <v>1582583713.78</v>
+        <v>36926230.78</v>
       </c>
       <c r="G74" t="n">
-        <v>1572502930.45</v>
+        <v>36292697.86</v>
       </c>
       <c r="H74" t="n">
-        <v>1541639.23</v>
+        <v>36912995.05</v>
       </c>
       <c r="I74" t="n">
-        <v>16627368.43</v>
-      </c>
-      <c r="J74" t="n">
-        <v>18169007.66</v>
+        <v>55172164.2</v>
       </c>
     </row>
     <row r="75">
@@ -3066,34 +2800,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SEINFRA</t>
+          <t>SEJUSP</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1301</v>
+        <v>1451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE INFRAESTRUTURA E MOBILIDADE</t>
+          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>600547625.35</v>
+        <v>610419064.9400001</v>
       </c>
       <c r="F75" t="n">
-        <v>522164709.56</v>
+        <v>490595691.98</v>
       </c>
       <c r="G75" t="n">
-        <v>444238275.33</v>
+        <v>470872988.03</v>
       </c>
       <c r="H75" t="n">
-        <v>18353119.53</v>
+        <v>91172489.76000001</v>
       </c>
       <c r="I75" t="n">
-        <v>36819044.67</v>
-      </c>
-      <c r="J75" t="n">
-        <v>55172164.2</v>
+        <v>103094527.66</v>
       </c>
     </row>
     <row r="76">
@@ -3102,34 +2833,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SEJUSP</t>
+          <t>SEMAD</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1451</v>
+        <v>1371</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE JUSTICA E SEGURANCA PUBLICA</t>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3393511812.13</v>
+        <v>31084311.3</v>
       </c>
       <c r="F76" t="n">
-        <v>3264360914.02</v>
+        <v>26263544.73</v>
       </c>
       <c r="G76" t="n">
-        <v>3238880805.17</v>
+        <v>24809340.47</v>
       </c>
       <c r="H76" t="n">
-        <v>13141756.77</v>
+        <v>4381917.62</v>
       </c>
       <c r="I76" t="n">
-        <v>89952770.89</v>
-      </c>
-      <c r="J76" t="n">
-        <v>103094527.66</v>
+        <v>8655507.689999999</v>
       </c>
     </row>
     <row r="77">
@@ -3138,34 +2866,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SEMAD</t>
+          <t>SEPLAG</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1371</v>
+        <v>1501</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>181795255.1</v>
+        <v>183258005.26</v>
       </c>
       <c r="F77" t="n">
-        <v>176679835.12</v>
+        <v>147646876.58</v>
       </c>
       <c r="G77" t="n">
-        <v>172435676.13</v>
+        <v>133949299.41</v>
       </c>
       <c r="H77" t="n">
-        <v>4368130.43</v>
+        <v>78541196.31999999</v>
       </c>
       <c r="I77" t="n">
-        <v>4287377.26</v>
-      </c>
-      <c r="J77" t="n">
-        <v>8655507.689999999</v>
+        <v>96518476.48</v>
       </c>
     </row>
     <row r="78">
@@ -3174,34 +2899,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SEPLAG</t>
+          <t>TCEMG</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1501</v>
+        <v>1021</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>352650653.12</v>
+        <v>93690959.93000001</v>
       </c>
       <c r="F78" t="n">
-        <v>315037665.91</v>
+        <v>77157830.81999999</v>
       </c>
       <c r="G78" t="n">
-        <v>301346762.92</v>
+        <v>67241202.92</v>
       </c>
       <c r="H78" t="n">
-        <v>19114485.82</v>
+        <v>9962620.380000001</v>
       </c>
       <c r="I78" t="n">
-        <v>77403990.66</v>
-      </c>
-      <c r="J78" t="n">
-        <v>96518476.48</v>
+        <v>9104244.1</v>
       </c>
     </row>
     <row r="79">
@@ -3210,34 +2932,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TCEMG</t>
+          <t>TJMG</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1021</v>
+        <v>1031</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE CONTAS DO ESTADO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>946650282.84</v>
-      </c>
-      <c r="F79" t="n">
-        <v>929954367.4</v>
-      </c>
-      <c r="G79" t="n">
-        <v>920990600.27</v>
-      </c>
+          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>23412.46</v>
       </c>
       <c r="I79" t="n">
-        <v>9104244.1</v>
-      </c>
-      <c r="J79" t="n">
-        <v>9104244.1</v>
+        <v>23412.46</v>
       </c>
     </row>
     <row r="80">
@@ -3246,34 +2959,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TJMG</t>
+          <t>TJMMG</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1031</v>
+        <v>1051</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA DO ESTADO DE MINAS GERAIS</t>
+          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>7024837395.9</v>
+        <v>9028934.960000001</v>
       </c>
       <c r="F80" t="n">
-        <v>7024837395.9</v>
+        <v>4559669.78</v>
       </c>
       <c r="G80" t="n">
-        <v>7025414410.5</v>
+        <v>3980293.29</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>2653528.34</v>
       </c>
       <c r="I80" t="n">
-        <v>23412.46</v>
-      </c>
-      <c r="J80" t="n">
-        <v>23412.46</v>
+        <v>2549048.16</v>
       </c>
     </row>
     <row r="81">
@@ -3282,34 +2992,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TJMMG</t>
+          <t>TV MINAS</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1051</v>
+        <v>2211</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>TRIBUNAL DE JUSTICA MILITAR DO ESTADO DE MINAS GERAIS</t>
+          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>86251920.37</v>
+        <v>8261361.66</v>
       </c>
       <c r="F81" t="n">
-        <v>81658327.34999999</v>
+        <v>7617654.32</v>
       </c>
       <c r="G81" t="n">
-        <v>81083119.16</v>
+        <v>7179353.86</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>783866.91</v>
       </c>
       <c r="I81" t="n">
-        <v>2549048.16</v>
-      </c>
-      <c r="J81" t="n">
-        <v>2549048.16</v>
+        <v>897376.6</v>
       </c>
     </row>
     <row r="82">
@@ -3318,34 +3025,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TV MINAS</t>
+          <t>UEMG</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>2211</v>
+        <v>2351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>FUNDACAO TV MINAS CULTURAL E EDUCATIVA</t>
+          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>20189976.4</v>
+        <v>128095983.23</v>
       </c>
       <c r="F82" t="n">
-        <v>19470842.74</v>
+        <v>97339849.52</v>
       </c>
       <c r="G82" t="n">
-        <v>18947352.89</v>
+        <v>93354925.63</v>
       </c>
       <c r="H82" t="n">
-        <v>140686.89</v>
+        <v>13542313.91</v>
       </c>
       <c r="I82" t="n">
-        <v>756689.71</v>
-      </c>
-      <c r="J82" t="n">
-        <v>897376.6</v>
+        <v>13894231.98</v>
       </c>
     </row>
     <row r="83">
@@ -3354,34 +3058,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UEMG</t>
+          <t>UNIMONTES</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2351</v>
+        <v>2311</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE DO ESTADO DE MINAS GERAIS</t>
+          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>464167620.3</v>
+        <v>76926189.84999999</v>
       </c>
       <c r="F83" t="n">
-        <v>430024005.97</v>
+        <v>61961847.9</v>
       </c>
       <c r="G83" t="n">
-        <v>419107102.61</v>
+        <v>56902007.43</v>
       </c>
       <c r="H83" t="n">
-        <v>380901.69</v>
+        <v>69425837.84</v>
       </c>
       <c r="I83" t="n">
-        <v>13513330.29</v>
-      </c>
-      <c r="J83" t="n">
-        <v>13894231.98</v>
+        <v>69353137.18000001</v>
       </c>
     </row>
     <row r="84">
@@ -3390,69 +3091,30 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UNIMONTES</t>
+          <t>UTRAMIG</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>2311</v>
+        <v>2281</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>UNIVERSIDADE ESTADUAL DE MONTES CLAROS</t>
+          <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>434351243.77</v>
+        <v>2891346.72</v>
       </c>
       <c r="F84" t="n">
-        <v>412467573.12</v>
+        <v>2479985.94</v>
       </c>
       <c r="G84" t="n">
-        <v>403987795.94</v>
+        <v>2276267.03</v>
       </c>
       <c r="H84" t="n">
-        <v>1669347.22</v>
+        <v>1513445.94</v>
       </c>
       <c r="I84" t="n">
-        <v>67683789.95999999</v>
-      </c>
-      <c r="J84" t="n">
-        <v>69353137.18000001</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>UTRAMIG</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>2281</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>FUNDACAO DE EDUCACAO PARA O TRABALHO DE MINAS GERAIS</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>7453421.77</v>
-      </c>
-      <c r="F85" t="n">
-        <v>7042060.99</v>
-      </c>
-      <c r="G85" t="n">
-        <v>6627633.67</v>
-      </c>
-      <c r="H85" t="n">
-        <v>7006</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1513188.14</v>
-      </c>
-      <c r="J85" t="n">
         <v>1520194.14</v>
       </c>
     </row>
